--- a/PRO database esercizi.xlsx
+++ b/PRO database esercizi.xlsx
@@ -4246,30 +4246,13 @@
           <t>AREA46 TRAINING LAB - REGISTRO PERIODIZZAZIONE E LINEE GUIDA (LIVELLO PRO)</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3">
         <f>== SEZIONE 1: STATO ATTUALE DELLA PERIODIZZAZIONE ===</f>
         <v/>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4282,10 +4265,6 @@
           <t>Landmine Lab - Livello PRO</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4298,10 +4277,6 @@
           <t>Sviluppo Multicompetenze e Rotazione Catalogo PRO (163 esercizi)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4319,9 +4294,6 @@
           <t>(18 sedute complessive = 3 Cicli da 6 sedute)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4339,9 +4311,6 @@
           <t>&lt;- AVVIO UFFICIALE NUOVA METODOLOGIA</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4354,10 +4323,6 @@
           <t>Ciclo 1 (6 sedute) e Ciclo 2 (6 sedute) - Mantenuti per gli allievi attivi</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4370,10 +4335,6 @@
           <t>Amatori Evoluti (hanno completato Entry Level, L1, L2, Advanced)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4386,29 +4347,13 @@
           <t>3x/settimana = 2 settimane per ciclo (6 sett. mesociclo) | 2x/settimana = 3 settimane per ciclo (9 sett. mesociclo)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12">
         <f>== SEZIONE 2: GUARDRAILS E REGOLE METODOLOGICHE INVIOLABILI ===</f>
         <v/>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4421,10 +4366,6 @@
           <t>Nessun allenamento deve superare i 60 minuti reali. 4-5 esercizi per forza pesante; 8-10 per agilità/metcon. Zero defaticamento passivo.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4437,10 +4378,6 @@
           <t>La percezione di allenamento, divertimento, sudore e gratificazione dell'amatore ha la priorità sulla teoria rigida da laboratorio.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4453,10 +4390,6 @@
           <t>Sui Fondamentali: onda da RPE 7-8 (7-9 reps) a RPE 8.5-10 (1-3 reps). Complementari in controtendenza (volume più alto, RPE 6-7.5).</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4469,10 +4402,6 @@
           <t>Quando un fondamentale tocca il picco, entra in scarico: il gesto pesante esce per 1 ciclo e viene sostituito da destrezza/mobilità/qualità.</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4485,10 +4414,6 @@
           <t>55% Fondamentali, 35% Complementari, 10% Accessori calcolato sulle serie allenanti del Mesociclo con elasticità algoritmica.</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4501,10 +4426,6 @@
           <t>MAI sovraccaricare la cerniera d'anca/bassa schiena. Inserire SEMPRE stimoli diretti per braccia (bicipiti/tricipiti) e spalle.</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4517,29 +4438,13 @@
           <t>Parametri asimmetrici sempre con notazione '+' (es. 8+8). MAI scalette di velocità (speed ladder) all'interno di circuiti o AMRAP.</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21">
         <f>== SEZIONE 3: STATO DEI PATTERN MOTORI (STAFFETTA DEL CARICO) ===</f>
         <v/>
       </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4557,9 +4462,6 @@
           <t>Direttiva per il Ciclo 3</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4577,9 +4479,6 @@
           <t>Mantenere progressione / consolidamento carico</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4597,9 +4496,6 @@
           <t>Alternare angolazione / variante</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4617,9 +4513,6 @@
           <t>Mantenere stimolo di forza</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4637,9 +4530,6 @@
           <t>SCARICO SELETTIVO (Modalità B) nel Ciclo 3</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4657,28 +4547,13 @@
           <t>INSERIMENTO PRIORITARIO nel Ciclo 3</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29">
         <f>== SEZIONE 4: CONTATORE DI UTILIZZO DEL CATALOGO ESERCIZI ===</f>
         <v/>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4696,18 +4571,8 @@
           <t>Esercizi Ancora da Sperimentare: 131</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -25295,7 +25160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N149"/>
+  <dimension ref="A1:N249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25595,7 +25460,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/jqhow36DTdg</t>
+        </is>
+      </c>
       <c r="L6" s="4" t="inlineStr"/>
       <c r="M6" s="3" t="n"/>
       <c r="N6" s="3" t="n"/>
@@ -26129,7 +25998,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/OGEUeBvoKc0?si=v7LIiDqSnd71NyM4</t>
+        </is>
+      </c>
       <c r="L17" s="5" t="inlineStr"/>
       <c r="M17" s="3" t="n"/>
       <c r="N17" s="3" t="n"/>
@@ -26509,7 +26382,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/jqhow36DTdg</t>
+        </is>
+      </c>
       <c r="L25" s="4" t="inlineStr"/>
       <c r="M25" s="3" t="n"/>
       <c r="N25" s="3" t="n"/>
@@ -27043,7 +26920,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/OGEUeBvoKc0?si=v7LIiDqSnd71NyM4</t>
+        </is>
+      </c>
       <c r="L36" s="5" t="inlineStr"/>
       <c r="M36" s="3" t="n"/>
       <c r="N36" s="3" t="n"/>
@@ -27423,7 +27304,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K44" s="4" t="inlineStr"/>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/jqhow36DTdg</t>
+        </is>
+      </c>
       <c r="L44" s="4" t="inlineStr"/>
       <c r="M44" s="3" t="n"/>
       <c r="N44" s="3" t="n"/>
@@ -27957,7 +27842,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K55" s="5" t="inlineStr"/>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/OGEUeBvoKc0?si=v7LIiDqSnd71NyM4</t>
+        </is>
+      </c>
       <c r="L55" s="5" t="inlineStr"/>
       <c r="M55" s="3" t="n"/>
       <c r="N55" s="3" t="n"/>
@@ -28245,7 +28134,11 @@
           <t>RPE 8</t>
         </is>
       </c>
-      <c r="K61" s="4" t="inlineStr"/>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/q_OfuLjIMFI</t>
+        </is>
+      </c>
       <c r="L61" s="4" t="inlineStr"/>
       <c r="M61" s="3" t="n"/>
       <c r="N61" s="3" t="n"/>
@@ -28345,7 +28238,11 @@
           <t>jump set | RPE 8</t>
         </is>
       </c>
-      <c r="K63" s="4" t="inlineStr"/>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/jqhow36DTdg</t>
+        </is>
+      </c>
       <c r="L63" s="4" t="inlineStr"/>
       <c r="M63" s="3" t="n"/>
       <c r="N63" s="3" t="n"/>
@@ -29067,7 +28964,11 @@
           <t>RPE 8</t>
         </is>
       </c>
-      <c r="K78" s="4" t="inlineStr"/>
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/q_OfuLjIMFI</t>
+        </is>
+      </c>
       <c r="L78" s="4" t="inlineStr"/>
       <c r="M78" s="3" t="n"/>
       <c r="N78" s="3" t="n"/>
@@ -29167,7 +29068,11 @@
           <t>jump set | RPE 8</t>
         </is>
       </c>
-      <c r="K80" s="4" t="inlineStr"/>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/jqhow36DTdg</t>
+        </is>
+      </c>
       <c r="L80" s="4" t="inlineStr"/>
       <c r="M80" s="3" t="n"/>
       <c r="N80" s="3" t="n"/>
@@ -29889,7 +29794,11 @@
           <t>RPE 8</t>
         </is>
       </c>
-      <c r="K95" s="4" t="inlineStr"/>
+      <c r="K95" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/q_OfuLjIMFI</t>
+        </is>
+      </c>
       <c r="L95" s="4" t="inlineStr"/>
       <c r="M95" s="3" t="n"/>
       <c r="N95" s="3" t="n"/>
@@ -29989,7 +29898,11 @@
           <t>jump set | RPE 8</t>
         </is>
       </c>
-      <c r="K97" s="4" t="inlineStr"/>
+      <c r="K97" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/jqhow36DTdg</t>
+        </is>
+      </c>
       <c r="L97" s="4" t="inlineStr"/>
       <c r="M97" s="3" t="n"/>
       <c r="N97" s="3" t="n"/>
@@ -30571,644 +30484,4062 @@
       <c r="N109" s="3" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="n"/>
-      <c r="B110" s="3" t="n"/>
-      <c r="C110" s="3" t="n"/>
-      <c r="D110" s="3" t="n"/>
-      <c r="E110" s="3" t="n"/>
-      <c r="F110" s="3" t="n"/>
-      <c r="G110" s="3" t="n"/>
-      <c r="H110" s="3" t="n"/>
-      <c r="I110" s="3" t="n"/>
-      <c r="J110" s="3" t="n"/>
-      <c r="K110" s="3" t="n"/>
-      <c r="L110" s="3" t="n"/>
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>13 allenamento A</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>1a</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>Pallof Press con elastico</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t>3x10+10</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr"/>
+      <c r="I110" s="4" t="inlineStr"/>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>jump set</t>
+        </is>
+      </c>
+      <c r="K110" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/aJ98KT13FtE?si=Li6fp-kbyh4wCnfT</t>
+        </is>
+      </c>
+      <c r="L110" s="4" t="inlineStr"/>
       <c r="M110" s="3" t="n"/>
       <c r="N110" s="3" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="3" t="n"/>
-      <c r="B111" s="3" t="n"/>
-      <c r="C111" s="3" t="n"/>
-      <c r="D111" s="3" t="n"/>
-      <c r="E111" s="3" t="n"/>
-      <c r="F111" s="3" t="n"/>
-      <c r="G111" s="3" t="n"/>
-      <c r="H111" s="3" t="n"/>
-      <c r="I111" s="3" t="n"/>
-      <c r="J111" s="3" t="n"/>
-      <c r="K111" s="3" t="n"/>
-      <c r="L111" s="3" t="n"/>
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>13 allenamento A</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>1b</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="n">
+        <v>163</v>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>Arm basic DB pendulum</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="inlineStr">
+        <is>
+          <t>3x10+10</t>
+        </is>
+      </c>
+      <c r="H111" s="4" t="inlineStr">
+        <is>
+          <t>45"</t>
+        </is>
+      </c>
+      <c r="I111" s="4" t="inlineStr"/>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>jump set</t>
+        </is>
+      </c>
+      <c r="K111" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/WL2Gbf9klSI?si=R-4lfDqWZo7_yc9B</t>
+        </is>
+      </c>
+      <c r="L111" s="4" t="inlineStr"/>
       <c r="M111" s="3" t="n"/>
       <c r="N111" s="3" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="3" t="n"/>
-      <c r="B112" s="3" t="n"/>
-      <c r="C112" s="3" t="n"/>
-      <c r="D112" s="3" t="n"/>
-      <c r="E112" s="3" t="n"/>
-      <c r="F112" s="3" t="n"/>
-      <c r="G112" s="3" t="n"/>
-      <c r="H112" s="3" t="n"/>
-      <c r="I112" s="3" t="n"/>
-      <c r="J112" s="3" t="n"/>
-      <c r="K112" s="3" t="n"/>
-      <c r="L112" s="3" t="n"/>
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>13 allenamento A</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>Bench press</t>
+        </is>
+      </c>
+      <c r="G112" s="4" t="inlineStr">
+        <is>
+          <t>4x6</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>90"</t>
+        </is>
+      </c>
+      <c r="I112" s="4" t="inlineStr"/>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>RPE 8.5</t>
+        </is>
+      </c>
+      <c r="K112" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/q_OfuLjIMFI</t>
+        </is>
+      </c>
+      <c r="L112" s="4" t="inlineStr"/>
       <c r="M112" s="3" t="n"/>
       <c r="N112" s="3" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="n"/>
-      <c r="B113" s="3" t="n"/>
-      <c r="C113" s="3" t="n"/>
-      <c r="D113" s="3" t="n"/>
-      <c r="E113" s="3" t="n"/>
-      <c r="F113" s="3" t="n"/>
-      <c r="G113" s="3" t="n"/>
-      <c r="H113" s="3" t="n"/>
-      <c r="I113" s="3" t="n"/>
-      <c r="J113" s="3" t="n"/>
-      <c r="K113" s="3" t="n"/>
-      <c r="L113" s="3" t="n"/>
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>13 allenamento A</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>3a</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>pull up Progressioni</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>4x6-8</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="inlineStr"/>
+      <c r="I113" s="4" t="inlineStr"/>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>jump set | RPE 8</t>
+        </is>
+      </c>
+      <c r="K113" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/nSj7QKBbvWA?si=fGWg_soHjRYO0xex</t>
+        </is>
+      </c>
+      <c r="L113" s="4" t="inlineStr"/>
       <c r="M113" s="3" t="n"/>
       <c r="N113" s="3" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="3" t="n"/>
-      <c r="B114" s="3" t="n"/>
-      <c r="C114" s="3" t="n"/>
-      <c r="D114" s="3" t="n"/>
-      <c r="E114" s="3" t="n"/>
-      <c r="F114" s="3" t="n"/>
-      <c r="G114" s="3" t="n"/>
-      <c r="H114" s="3" t="n"/>
-      <c r="I114" s="3" t="n"/>
-      <c r="J114" s="3" t="n"/>
-      <c r="K114" s="3" t="n"/>
-      <c r="L114" s="3" t="n"/>
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>13 allenamento A</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>3b</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>One arm press</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>4x8+8</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>60"</t>
+        </is>
+      </c>
+      <c r="I114" s="4" t="inlineStr"/>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>jump set | RPE 8</t>
+        </is>
+      </c>
+      <c r="K114" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/V-5Q4l-SM20</t>
+        </is>
+      </c>
+      <c r="L114" s="4" t="inlineStr"/>
       <c r="M114" s="3" t="n"/>
       <c r="N114" s="3" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="3" t="n"/>
-      <c r="B115" s="3" t="n"/>
-      <c r="C115" s="3" t="n"/>
-      <c r="D115" s="3" t="n"/>
-      <c r="E115" s="3" t="n"/>
-      <c r="F115" s="3" t="n"/>
-      <c r="G115" s="3" t="n"/>
-      <c r="H115" s="3" t="n"/>
-      <c r="I115" s="3" t="n"/>
-      <c r="J115" s="3" t="n"/>
-      <c r="K115" s="3" t="n"/>
-      <c r="L115" s="3" t="n"/>
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>13 allenamento A</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>4a</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>Coiled Bench Row</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>3x10+10</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="inlineStr"/>
+      <c r="I115" s="4" t="inlineStr"/>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t>circuito (3 round)</t>
+        </is>
+      </c>
+      <c r="K115" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/2gCslk95r20</t>
+        </is>
+      </c>
+      <c r="L115" s="4" t="inlineStr"/>
       <c r="M115" s="3" t="n"/>
       <c r="N115" s="3" t="n"/>
     </row>
     <row r="116">
-      <c r="A116" s="3" t="n"/>
-      <c r="B116" s="3" t="n"/>
-      <c r="C116" s="3" t="n"/>
-      <c r="D116" s="3" t="n"/>
-      <c r="E116" s="3" t="n"/>
-      <c r="F116" s="3" t="n"/>
-      <c r="G116" s="3" t="n"/>
-      <c r="H116" s="3" t="n"/>
-      <c r="I116" s="3" t="n"/>
-      <c r="J116" s="3" t="n"/>
-      <c r="K116" s="3" t="n"/>
-      <c r="L116" s="3" t="n"/>
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>13 allenamento A</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>4b</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="n">
+        <v>234</v>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>rebound push up</t>
+        </is>
+      </c>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>3x8</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr"/>
+      <c r="I116" s="4" t="inlineStr"/>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>circuito (3 round)</t>
+        </is>
+      </c>
+      <c r="K116" s="4" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/iSipY1JCKdQ</t>
+        </is>
+      </c>
+      <c r="L116" s="4" t="inlineStr"/>
       <c r="M116" s="3" t="n"/>
       <c r="N116" s="3" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" s="3" t="n"/>
-      <c r="B117" s="3" t="n"/>
-      <c r="C117" s="3" t="n"/>
-      <c r="D117" s="3" t="n"/>
-      <c r="E117" s="3" t="n"/>
-      <c r="F117" s="3" t="n"/>
-      <c r="G117" s="3" t="n"/>
-      <c r="H117" s="3" t="n"/>
-      <c r="I117" s="3" t="n"/>
-      <c r="J117" s="3" t="n"/>
-      <c r="K117" s="3" t="n"/>
-      <c r="L117" s="3" t="n"/>
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>13 allenamento A</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>4c</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>air bike solo braccia</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>3x30"</t>
+        </is>
+      </c>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t>60"</t>
+        </is>
+      </c>
+      <c r="I117" s="4" t="inlineStr"/>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>circuito (3 round)</t>
+        </is>
+      </c>
+      <c r="K117" s="4" t="inlineStr"/>
+      <c r="L117" s="4" t="inlineStr"/>
       <c r="M117" s="3" t="n"/>
       <c r="N117" s="3" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="3" t="n"/>
-      <c r="B118" s="3" t="n"/>
-      <c r="C118" s="3" t="n"/>
-      <c r="D118" s="3" t="n"/>
-      <c r="E118" s="3" t="n"/>
-      <c r="F118" s="3" t="n"/>
-      <c r="G118" s="3" t="n"/>
-      <c r="H118" s="3" t="n"/>
-      <c r="I118" s="3" t="n"/>
-      <c r="J118" s="3" t="n"/>
-      <c r="K118" s="3" t="n"/>
-      <c r="L118" s="3" t="n"/>
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>14 allenamento B</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>1a</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="F118" s="5" t="inlineStr">
+        <is>
+          <t>Coiled Cobra</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>3x8+8</t>
+        </is>
+      </c>
+      <c r="H118" s="5" t="inlineStr"/>
+      <c r="I118" s="5" t="inlineStr"/>
+      <c r="J118" s="5" t="inlineStr">
+        <is>
+          <t>jump set</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/GU3ePuvJwMk</t>
+        </is>
+      </c>
+      <c r="L118" s="5" t="inlineStr"/>
       <c r="M118" s="3" t="n"/>
       <c r="N118" s="3" t="n"/>
     </row>
     <row r="119">
-      <c r="A119" s="3" t="n"/>
-      <c r="B119" s="3" t="n"/>
-      <c r="C119" s="3" t="n"/>
-      <c r="D119" s="3" t="n"/>
-      <c r="E119" s="3" t="n"/>
-      <c r="F119" s="3" t="n"/>
-      <c r="G119" s="3" t="n"/>
-      <c r="H119" s="3" t="n"/>
-      <c r="I119" s="3" t="n"/>
-      <c r="J119" s="3" t="n"/>
-      <c r="K119" s="3" t="n"/>
-      <c r="L119" s="3" t="n"/>
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>14 allenamento B</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>1b</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>Wall High Pull</t>
+        </is>
+      </c>
+      <c r="G119" s="5" t="inlineStr">
+        <is>
+          <t>3x10+10</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="inlineStr">
+        <is>
+          <t>45"</t>
+        </is>
+      </c>
+      <c r="I119" s="5" t="inlineStr"/>
+      <c r="J119" s="5" t="inlineStr">
+        <is>
+          <t>jump set</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/EBv0BjKhUlA?si=I07YNW02JWJF-oiD</t>
+        </is>
+      </c>
+      <c r="L119" s="5" t="inlineStr"/>
       <c r="M119" s="3" t="n"/>
       <c r="N119" s="3" t="n"/>
     </row>
     <row r="120">
-      <c r="A120" s="3" t="n"/>
-      <c r="B120" s="3" t="n"/>
-      <c r="C120" s="3" t="n"/>
-      <c r="D120" s="3" t="n"/>
-      <c r="E120" s="3" t="n"/>
-      <c r="F120" s="3" t="n"/>
-      <c r="G120" s="3" t="n"/>
-      <c r="H120" s="3" t="n"/>
-      <c r="I120" s="3" t="n"/>
-      <c r="J120" s="3" t="n"/>
-      <c r="K120" s="3" t="n"/>
-      <c r="L120" s="3" t="n"/>
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>14 allenamento B</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>2a</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="n">
+        <v>218</v>
+      </c>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>Landmine Jerk</t>
+        </is>
+      </c>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>4x5+5</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="inlineStr">
+        <is>
+          <t>RBS 60"</t>
+        </is>
+      </c>
+      <c r="I120" s="5" t="inlineStr"/>
+      <c r="J120" s="5" t="inlineStr">
+        <is>
+          <t>jump set | RPE 8.5</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/zIqsjVRtc5o</t>
+        </is>
+      </c>
+      <c r="L120" s="5" t="inlineStr"/>
       <c r="M120" s="3" t="n"/>
       <c r="N120" s="3" t="n"/>
     </row>
     <row r="121">
-      <c r="A121" s="3" t="n"/>
-      <c r="B121" s="3" t="n"/>
-      <c r="C121" s="3" t="n"/>
-      <c r="D121" s="3" t="n"/>
-      <c r="E121" s="3" t="n"/>
-      <c r="F121" s="3" t="n"/>
-      <c r="G121" s="3" t="n"/>
-      <c r="H121" s="3" t="n"/>
-      <c r="I121" s="3" t="n"/>
-      <c r="J121" s="3" t="n"/>
-      <c r="K121" s="3" t="n"/>
-      <c r="L121" s="3" t="n"/>
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>14 allenamento B</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>2b</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>Landmine Biker's Squat</t>
+        </is>
+      </c>
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>4x8</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="inlineStr">
+        <is>
+          <t>RBS 60"</t>
+        </is>
+      </c>
+      <c r="I121" s="5" t="inlineStr"/>
+      <c r="J121" s="5" t="inlineStr">
+        <is>
+          <t>jump set | RPE 8</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/jqhow36DTdg</t>
+        </is>
+      </c>
+      <c r="L121" s="5" t="inlineStr"/>
       <c r="M121" s="3" t="n"/>
       <c r="N121" s="3" t="n"/>
     </row>
     <row r="122">
-      <c r="A122" s="3" t="n"/>
-      <c r="B122" s="3" t="n"/>
-      <c r="C122" s="3" t="n"/>
-      <c r="D122" s="3" t="n"/>
-      <c r="E122" s="3" t="n"/>
-      <c r="F122" s="3" t="n"/>
-      <c r="G122" s="3" t="n"/>
-      <c r="H122" s="3" t="n"/>
-      <c r="I122" s="3" t="n"/>
-      <c r="J122" s="3" t="n"/>
-      <c r="K122" s="3" t="n"/>
-      <c r="L122" s="3" t="n"/>
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>14 allenamento B</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>3a</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="n">
+        <v>191</v>
+      </c>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>Endless rope Standing Power Pull</t>
+        </is>
+      </c>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>4x20"</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="inlineStr"/>
+      <c r="I122" s="5" t="inlineStr"/>
+      <c r="J122" s="5" t="inlineStr">
+        <is>
+          <t>jump set</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/rRgKOg0qaA4?si=aYRTcGburOhwv1a6</t>
+        </is>
+      </c>
+      <c r="L122" s="5" t="inlineStr"/>
       <c r="M122" s="3" t="n"/>
       <c r="N122" s="3" t="n"/>
     </row>
     <row r="123">
-      <c r="A123" s="3" t="n"/>
-      <c r="B123" s="3" t="n"/>
-      <c r="C123" s="3" t="n"/>
-      <c r="D123" s="3" t="n"/>
-      <c r="E123" s="3" t="n"/>
-      <c r="F123" s="3" t="n"/>
-      <c r="G123" s="3" t="n"/>
-      <c r="H123" s="3" t="n"/>
-      <c r="I123" s="3" t="n"/>
-      <c r="J123" s="3" t="n"/>
-      <c r="K123" s="3" t="n"/>
-      <c r="L123" s="3" t="n"/>
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>14 allenamento B</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>3b</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>Yin yang sit up press</t>
+        </is>
+      </c>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>4x8+8</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="inlineStr">
+        <is>
+          <t>45"</t>
+        </is>
+      </c>
+      <c r="I123" s="5" t="inlineStr"/>
+      <c r="J123" s="5" t="inlineStr">
+        <is>
+          <t>jump set</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/arECYW5JFeA</t>
+        </is>
+      </c>
+      <c r="L123" s="5" t="inlineStr"/>
       <c r="M123" s="3" t="n"/>
       <c r="N123" s="3" t="n"/>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="n"/>
-      <c r="B124" s="3" t="n"/>
-      <c r="C124" s="3" t="n"/>
-      <c r="D124" s="3" t="n"/>
-      <c r="E124" s="3" t="n"/>
-      <c r="F124" s="3" t="n"/>
-      <c r="G124" s="3" t="n"/>
-      <c r="H124" s="3" t="n"/>
-      <c r="I124" s="3" t="n"/>
-      <c r="J124" s="3" t="n"/>
-      <c r="K124" s="3" t="n"/>
-      <c r="L124" s="3" t="n"/>
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>14 allenamento B</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>4a</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>Aerial Jerk</t>
+        </is>
+      </c>
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>x 6+6</t>
+        </is>
+      </c>
+      <c r="H124" s="5" t="inlineStr"/>
+      <c r="I124" s="5" t="inlineStr"/>
+      <c r="J124" s="5" t="inlineStr">
+        <is>
+          <t>AMRAP 12'</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/0uI_9_0qR7k</t>
+        </is>
+      </c>
+      <c r="L124" s="5" t="inlineStr"/>
       <c r="M124" s="3" t="n"/>
       <c r="N124" s="3" t="n"/>
     </row>
     <row r="125">
-      <c r="A125" s="3" t="n"/>
-      <c r="B125" s="3" t="n"/>
-      <c r="C125" s="3" t="n"/>
-      <c r="D125" s="3" t="n"/>
-      <c r="E125" s="3" t="n"/>
-      <c r="F125" s="3" t="n"/>
-      <c r="G125" s="3" t="n"/>
-      <c r="H125" s="3" t="n"/>
-      <c r="I125" s="3" t="n"/>
-      <c r="J125" s="3" t="n"/>
-      <c r="K125" s="3" t="n"/>
-      <c r="L125" s="3" t="n"/>
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>14 allenamento B</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>4b</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="n">
+        <v>205</v>
+      </c>
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>Kick-through progression</t>
+        </is>
+      </c>
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>x 10</t>
+        </is>
+      </c>
+      <c r="H125" s="5" t="inlineStr"/>
+      <c r="I125" s="5" t="inlineStr"/>
+      <c r="J125" s="5" t="inlineStr">
+        <is>
+          <t>AMRAP 12'</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/OGEUeBvoKc0?si=v7LIiDqSnd71NyM4</t>
+        </is>
+      </c>
+      <c r="L125" s="5" t="inlineStr"/>
       <c r="M125" s="3" t="n"/>
       <c r="N125" s="3" t="n"/>
     </row>
     <row r="126">
-      <c r="A126" s="3" t="n"/>
-      <c r="B126" s="3" t="n"/>
-      <c r="C126" s="3" t="n"/>
-      <c r="D126" s="3" t="n"/>
-      <c r="E126" s="3" t="n"/>
-      <c r="F126" s="3" t="n"/>
-      <c r="G126" s="3" t="n"/>
-      <c r="H126" s="3" t="n"/>
-      <c r="I126" s="3" t="n"/>
-      <c r="J126" s="3" t="n"/>
-      <c r="K126" s="3" t="n"/>
-      <c r="L126" s="3" t="n"/>
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>14 allenamento B</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>4c</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t>Ball over shoulder</t>
+        </is>
+      </c>
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>x 8</t>
+        </is>
+      </c>
+      <c r="H126" s="5" t="inlineStr"/>
+      <c r="I126" s="5" t="inlineStr"/>
+      <c r="J126" s="5" t="inlineStr">
+        <is>
+          <t>AMRAP 12'</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Nwd-5fuLm3k?si=jGWxuH-RfvPTnkWN</t>
+        </is>
+      </c>
+      <c r="L126" s="5" t="inlineStr"/>
       <c r="M126" s="3" t="n"/>
       <c r="N126" s="3" t="n"/>
     </row>
     <row r="127">
-      <c r="A127" s="3" t="n"/>
-      <c r="B127" s="3" t="n"/>
-      <c r="C127" s="3" t="n"/>
-      <c r="D127" s="3" t="n"/>
-      <c r="E127" s="3" t="n"/>
-      <c r="F127" s="3" t="n"/>
-      <c r="G127" s="3" t="n"/>
-      <c r="H127" s="3" t="n"/>
-      <c r="I127" s="3" t="n"/>
-      <c r="J127" s="3" t="n"/>
-      <c r="K127" s="3" t="n"/>
-      <c r="L127" s="3" t="n"/>
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>15 allenamento A</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>1a</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>Pallof Press con elastico</t>
+        </is>
+      </c>
+      <c r="G127" s="4" t="inlineStr">
+        <is>
+          <t>3x10+10</t>
+        </is>
+      </c>
+      <c r="H127" s="4" t="inlineStr"/>
+      <c r="I127" s="4" t="inlineStr"/>
+      <c r="J127" s="4" t="inlineStr">
+        <is>
+          <t>jump set</t>
+        </is>
+      </c>
+      <c r="K127" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/aJ98KT13FtE?si=Li6fp-kbyh4wCnfT</t>
+        </is>
+      </c>
+      <c r="L127" s="4" t="inlineStr"/>
       <c r="M127" s="3" t="n"/>
       <c r="N127" s="3" t="n"/>
     </row>
     <row r="128">
-      <c r="A128" s="3" t="n"/>
-      <c r="B128" s="3" t="n"/>
-      <c r="C128" s="3" t="n"/>
-      <c r="D128" s="3" t="n"/>
-      <c r="E128" s="3" t="n"/>
-      <c r="F128" s="3" t="n"/>
-      <c r="G128" s="3" t="n"/>
-      <c r="H128" s="3" t="n"/>
-      <c r="I128" s="3" t="n"/>
-      <c r="J128" s="3" t="n"/>
-      <c r="K128" s="3" t="n"/>
-      <c r="L128" s="3" t="n"/>
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>15 allenamento A</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>1b</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="n">
+        <v>163</v>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>Arm basic DB pendulum</t>
+        </is>
+      </c>
+      <c r="G128" s="4" t="inlineStr">
+        <is>
+          <t>3x10+10</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="inlineStr">
+        <is>
+          <t>45"</t>
+        </is>
+      </c>
+      <c r="I128" s="4" t="inlineStr"/>
+      <c r="J128" s="4" t="inlineStr">
+        <is>
+          <t>jump set</t>
+        </is>
+      </c>
+      <c r="K128" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/WL2Gbf9klSI?si=R-4lfDqWZo7_yc9B</t>
+        </is>
+      </c>
+      <c r="L128" s="4" t="inlineStr"/>
       <c r="M128" s="3" t="n"/>
       <c r="N128" s="3" t="n"/>
     </row>
     <row r="129">
-      <c r="A129" s="3" t="n"/>
-      <c r="B129" s="3" t="n"/>
-      <c r="C129" s="3" t="n"/>
-      <c r="D129" s="3" t="n"/>
-      <c r="E129" s="3" t="n"/>
-      <c r="F129" s="3" t="n"/>
-      <c r="G129" s="3" t="n"/>
-      <c r="H129" s="3" t="n"/>
-      <c r="I129" s="3" t="n"/>
-      <c r="J129" s="3" t="n"/>
-      <c r="K129" s="3" t="n"/>
-      <c r="L129" s="3" t="n"/>
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>15 allenamento A</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>Bench press</t>
+        </is>
+      </c>
+      <c r="G129" s="4" t="inlineStr">
+        <is>
+          <t>4x6</t>
+        </is>
+      </c>
+      <c r="H129" s="4" t="inlineStr">
+        <is>
+          <t>90"</t>
+        </is>
+      </c>
+      <c r="I129" s="4" t="inlineStr"/>
+      <c r="J129" s="4" t="inlineStr">
+        <is>
+          <t>RPE 8.5</t>
+        </is>
+      </c>
+      <c r="K129" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/q_OfuLjIMFI</t>
+        </is>
+      </c>
+      <c r="L129" s="4" t="inlineStr"/>
       <c r="M129" s="3" t="n"/>
       <c r="N129" s="3" t="n"/>
     </row>
     <row r="130">
-      <c r="A130" s="3" t="n"/>
-      <c r="B130" s="3" t="n"/>
-      <c r="C130" s="3" t="n"/>
-      <c r="D130" s="3" t="n"/>
-      <c r="E130" s="3" t="n"/>
-      <c r="F130" s="3" t="n"/>
-      <c r="G130" s="3" t="n"/>
-      <c r="H130" s="3" t="n"/>
-      <c r="I130" s="3" t="n"/>
-      <c r="J130" s="3" t="n"/>
-      <c r="K130" s="3" t="n"/>
-      <c r="L130" s="3" t="n"/>
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>15 allenamento A</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>3a</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>pull up Progressioni</t>
+        </is>
+      </c>
+      <c r="G130" s="4" t="inlineStr">
+        <is>
+          <t>4x6-8</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="inlineStr"/>
+      <c r="I130" s="4" t="inlineStr"/>
+      <c r="J130" s="4" t="inlineStr">
+        <is>
+          <t>jump set | RPE 8</t>
+        </is>
+      </c>
+      <c r="K130" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/nSj7QKBbvWA?si=fGWg_soHjRYO0xex</t>
+        </is>
+      </c>
+      <c r="L130" s="4" t="inlineStr"/>
       <c r="M130" s="3" t="n"/>
       <c r="N130" s="3" t="n"/>
     </row>
     <row r="131">
-      <c r="A131" s="3" t="n"/>
-      <c r="B131" s="3" t="n"/>
-      <c r="C131" s="3" t="n"/>
-      <c r="D131" s="3" t="n"/>
-      <c r="E131" s="3" t="n"/>
-      <c r="F131" s="3" t="n"/>
-      <c r="G131" s="3" t="n"/>
-      <c r="H131" s="3" t="n"/>
-      <c r="I131" s="3" t="n"/>
-      <c r="J131" s="3" t="n"/>
-      <c r="K131" s="3" t="n"/>
-      <c r="L131" s="3" t="n"/>
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>15 allenamento A</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>3b</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>One arm press</t>
+        </is>
+      </c>
+      <c r="G131" s="4" t="inlineStr">
+        <is>
+          <t>4x8+8</t>
+        </is>
+      </c>
+      <c r="H131" s="4" t="inlineStr">
+        <is>
+          <t>60"</t>
+        </is>
+      </c>
+      <c r="I131" s="4" t="inlineStr"/>
+      <c r="J131" s="4" t="inlineStr">
+        <is>
+          <t>jump set | RPE 8</t>
+        </is>
+      </c>
+      <c r="K131" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/V-5Q4l-SM20</t>
+        </is>
+      </c>
+      <c r="L131" s="4" t="inlineStr"/>
       <c r="M131" s="3" t="n"/>
       <c r="N131" s="3" t="n"/>
     </row>
     <row r="132">
-      <c r="A132" s="3" t="n"/>
-      <c r="B132" s="3" t="n"/>
-      <c r="C132" s="3" t="n"/>
-      <c r="D132" s="3" t="n"/>
-      <c r="E132" s="3" t="n"/>
-      <c r="F132" s="3" t="n"/>
-      <c r="G132" s="3" t="n"/>
-      <c r="H132" s="3" t="n"/>
-      <c r="I132" s="3" t="n"/>
-      <c r="J132" s="3" t="n"/>
-      <c r="K132" s="3" t="n"/>
-      <c r="L132" s="3" t="n"/>
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>15 allenamento A</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>4a</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t>Coiled Bench Row</t>
+        </is>
+      </c>
+      <c r="G132" s="4" t="inlineStr">
+        <is>
+          <t>3x10+10</t>
+        </is>
+      </c>
+      <c r="H132" s="4" t="inlineStr"/>
+      <c r="I132" s="4" t="inlineStr"/>
+      <c r="J132" s="4" t="inlineStr">
+        <is>
+          <t>circuito (3 round)</t>
+        </is>
+      </c>
+      <c r="K132" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/2gCslk95r20</t>
+        </is>
+      </c>
+      <c r="L132" s="4" t="inlineStr"/>
       <c r="M132" s="3" t="n"/>
       <c r="N132" s="3" t="n"/>
     </row>
     <row r="133">
-      <c r="A133" s="3" t="n"/>
-      <c r="B133" s="3" t="n"/>
-      <c r="C133" s="3" t="n"/>
-      <c r="D133" s="3" t="n"/>
-      <c r="E133" s="3" t="n"/>
-      <c r="F133" s="3" t="n"/>
-      <c r="G133" s="3" t="n"/>
-      <c r="H133" s="3" t="n"/>
-      <c r="I133" s="3" t="n"/>
-      <c r="J133" s="3" t="n"/>
-      <c r="K133" s="3" t="n"/>
-      <c r="L133" s="3" t="n"/>
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>15 allenamento A</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>4b</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="n">
+        <v>234</v>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>rebound push up</t>
+        </is>
+      </c>
+      <c r="G133" s="4" t="inlineStr">
+        <is>
+          <t>3x8</t>
+        </is>
+      </c>
+      <c r="H133" s="4" t="inlineStr"/>
+      <c r="I133" s="4" t="inlineStr"/>
+      <c r="J133" s="4" t="inlineStr">
+        <is>
+          <t>circuito (3 round)</t>
+        </is>
+      </c>
+      <c r="K133" s="4" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/iSipY1JCKdQ</t>
+        </is>
+      </c>
+      <c r="L133" s="4" t="inlineStr"/>
       <c r="M133" s="3" t="n"/>
       <c r="N133" s="3" t="n"/>
     </row>
     <row r="134">
-      <c r="A134" s="3" t="n"/>
-      <c r="B134" s="3" t="n"/>
-      <c r="C134" s="3" t="n"/>
-      <c r="D134" s="3" t="n"/>
-      <c r="E134" s="3" t="n"/>
-      <c r="F134" s="3" t="n"/>
-      <c r="G134" s="3" t="n"/>
-      <c r="H134" s="3" t="n"/>
-      <c r="I134" s="3" t="n"/>
-      <c r="J134" s="3" t="n"/>
-      <c r="K134" s="3" t="n"/>
-      <c r="L134" s="3" t="n"/>
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>15 allenamento A</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>4c</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>air bike solo braccia</t>
+        </is>
+      </c>
+      <c r="G134" s="4" t="inlineStr">
+        <is>
+          <t>3x30"</t>
+        </is>
+      </c>
+      <c r="H134" s="4" t="inlineStr">
+        <is>
+          <t>60"</t>
+        </is>
+      </c>
+      <c r="I134" s="4" t="inlineStr"/>
+      <c r="J134" s="4" t="inlineStr">
+        <is>
+          <t>circuito (3 round)</t>
+        </is>
+      </c>
+      <c r="K134" s="4" t="inlineStr"/>
+      <c r="L134" s="4" t="inlineStr"/>
       <c r="M134" s="3" t="n"/>
       <c r="N134" s="3" t="n"/>
     </row>
     <row r="135">
-      <c r="A135" s="3" t="n"/>
-      <c r="B135" s="3" t="n"/>
-      <c r="C135" s="3" t="n"/>
-      <c r="D135" s="3" t="n"/>
-      <c r="E135" s="3" t="n"/>
-      <c r="F135" s="3" t="n"/>
-      <c r="G135" s="3" t="n"/>
-      <c r="H135" s="3" t="n"/>
-      <c r="I135" s="3" t="n"/>
-      <c r="J135" s="3" t="n"/>
-      <c r="K135" s="3" t="n"/>
-      <c r="L135" s="3" t="n"/>
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>16 allenamento B</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>1a</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>Coiled Cobra</t>
+        </is>
+      </c>
+      <c r="G135" s="5" t="inlineStr">
+        <is>
+          <t>3x8+8</t>
+        </is>
+      </c>
+      <c r="H135" s="5" t="inlineStr"/>
+      <c r="I135" s="5" t="inlineStr"/>
+      <c r="J135" s="5" t="inlineStr">
+        <is>
+          <t>jump set</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/GU3ePuvJwMk</t>
+        </is>
+      </c>
+      <c r="L135" s="5" t="inlineStr"/>
       <c r="M135" s="3" t="n"/>
       <c r="N135" s="3" t="n"/>
     </row>
     <row r="136">
-      <c r="A136" s="3" t="n"/>
-      <c r="B136" s="3" t="n"/>
-      <c r="C136" s="3" t="n"/>
-      <c r="D136" s="3" t="n"/>
-      <c r="E136" s="3" t="n"/>
-      <c r="F136" s="3" t="n"/>
-      <c r="G136" s="3" t="n"/>
-      <c r="H136" s="3" t="n"/>
-      <c r="I136" s="3" t="n"/>
-      <c r="J136" s="3" t="n"/>
-      <c r="K136" s="3" t="n"/>
-      <c r="L136" s="3" t="n"/>
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>16 allenamento B</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>1b</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>Wall High Pull</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="inlineStr">
+        <is>
+          <t>3x10+10</t>
+        </is>
+      </c>
+      <c r="H136" s="5" t="inlineStr">
+        <is>
+          <t>45"</t>
+        </is>
+      </c>
+      <c r="I136" s="5" t="inlineStr"/>
+      <c r="J136" s="5" t="inlineStr">
+        <is>
+          <t>jump set</t>
+        </is>
+      </c>
+      <c r="K136" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/EBv0BjKhUlA?si=I07YNW02JWJF-oiD</t>
+        </is>
+      </c>
+      <c r="L136" s="5" t="inlineStr"/>
       <c r="M136" s="3" t="n"/>
       <c r="N136" s="3" t="n"/>
     </row>
     <row r="137">
-      <c r="A137" s="3" t="n"/>
-      <c r="B137" s="3" t="n"/>
-      <c r="C137" s="3" t="n"/>
-      <c r="D137" s="3" t="n"/>
-      <c r="E137" s="3" t="n"/>
-      <c r="F137" s="3" t="n"/>
-      <c r="G137" s="3" t="n"/>
-      <c r="H137" s="3" t="n"/>
-      <c r="I137" s="3" t="n"/>
-      <c r="J137" s="3" t="n"/>
-      <c r="K137" s="3" t="n"/>
-      <c r="L137" s="3" t="n"/>
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>16 allenamento B</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>2a</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="n">
+        <v>218</v>
+      </c>
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>Landmine Jerk</t>
+        </is>
+      </c>
+      <c r="G137" s="5" t="inlineStr">
+        <is>
+          <t>4x5+5</t>
+        </is>
+      </c>
+      <c r="H137" s="5" t="inlineStr">
+        <is>
+          <t>RBS 60"</t>
+        </is>
+      </c>
+      <c r="I137" s="5" t="inlineStr"/>
+      <c r="J137" s="5" t="inlineStr">
+        <is>
+          <t>jump set | RPE 8.5</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/zIqsjVRtc5o</t>
+        </is>
+      </c>
+      <c r="L137" s="5" t="inlineStr"/>
       <c r="M137" s="3" t="n"/>
       <c r="N137" s="3" t="n"/>
     </row>
     <row r="138">
-      <c r="A138" s="3" t="n"/>
-      <c r="B138" s="3" t="n"/>
-      <c r="C138" s="3" t="n"/>
-      <c r="D138" s="3" t="n"/>
-      <c r="E138" s="3" t="n"/>
-      <c r="F138" s="3" t="n"/>
-      <c r="G138" s="3" t="n"/>
-      <c r="H138" s="3" t="n"/>
-      <c r="I138" s="3" t="n"/>
-      <c r="J138" s="3" t="n"/>
-      <c r="K138" s="3" t="n"/>
-      <c r="L138" s="3" t="n"/>
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>16 allenamento B</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>2b</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="F138" s="5" t="inlineStr">
+        <is>
+          <t>Landmine Biker's Squat</t>
+        </is>
+      </c>
+      <c r="G138" s="5" t="inlineStr">
+        <is>
+          <t>4x8</t>
+        </is>
+      </c>
+      <c r="H138" s="5" t="inlineStr">
+        <is>
+          <t>RBS 60"</t>
+        </is>
+      </c>
+      <c r="I138" s="5" t="inlineStr"/>
+      <c r="J138" s="5" t="inlineStr">
+        <is>
+          <t>jump set | RPE 8</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/jqhow36DTdg</t>
+        </is>
+      </c>
+      <c r="L138" s="5" t="inlineStr"/>
       <c r="M138" s="3" t="n"/>
       <c r="N138" s="3" t="n"/>
     </row>
     <row r="139">
-      <c r="A139" s="3" t="n"/>
-      <c r="B139" s="3" t="n"/>
-      <c r="C139" s="3" t="n"/>
-      <c r="D139" s="3" t="n"/>
-      <c r="E139" s="3" t="n"/>
-      <c r="F139" s="3" t="n"/>
-      <c r="G139" s="3" t="n"/>
-      <c r="H139" s="3" t="n"/>
-      <c r="I139" s="3" t="n"/>
-      <c r="J139" s="3" t="n"/>
-      <c r="K139" s="3" t="n"/>
-      <c r="L139" s="3" t="n"/>
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>16 allenamento B</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t>3a</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="n">
+        <v>191</v>
+      </c>
+      <c r="F139" s="5" t="inlineStr">
+        <is>
+          <t>Endless rope Standing Power Pull</t>
+        </is>
+      </c>
+      <c r="G139" s="5" t="inlineStr">
+        <is>
+          <t>4x20"</t>
+        </is>
+      </c>
+      <c r="H139" s="5" t="inlineStr"/>
+      <c r="I139" s="5" t="inlineStr"/>
+      <c r="J139" s="5" t="inlineStr">
+        <is>
+          <t>jump set</t>
+        </is>
+      </c>
+      <c r="K139" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/rRgKOg0qaA4?si=aYRTcGburOhwv1a6</t>
+        </is>
+      </c>
+      <c r="L139" s="5" t="inlineStr"/>
       <c r="M139" s="3" t="n"/>
       <c r="N139" s="3" t="n"/>
     </row>
     <row r="140">
-      <c r="A140" s="3" t="n"/>
-      <c r="B140" s="3" t="n"/>
-      <c r="C140" s="3" t="n"/>
-      <c r="D140" s="3" t="n"/>
-      <c r="E140" s="3" t="n"/>
-      <c r="F140" s="3" t="n"/>
-      <c r="G140" s="3" t="n"/>
-      <c r="H140" s="3" t="n"/>
-      <c r="I140" s="3" t="n"/>
-      <c r="J140" s="3" t="n"/>
-      <c r="K140" s="3" t="n"/>
-      <c r="L140" s="3" t="n"/>
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>16 allenamento B</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>3b</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="F140" s="5" t="inlineStr">
+        <is>
+          <t>Yin yang sit up press</t>
+        </is>
+      </c>
+      <c r="G140" s="5" t="inlineStr">
+        <is>
+          <t>4x8+8</t>
+        </is>
+      </c>
+      <c r="H140" s="5" t="inlineStr">
+        <is>
+          <t>45"</t>
+        </is>
+      </c>
+      <c r="I140" s="5" t="inlineStr"/>
+      <c r="J140" s="5" t="inlineStr">
+        <is>
+          <t>jump set</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/arECYW5JFeA</t>
+        </is>
+      </c>
+      <c r="L140" s="5" t="inlineStr"/>
       <c r="M140" s="3" t="n"/>
       <c r="N140" s="3" t="n"/>
     </row>
     <row r="141">
-      <c r="A141" s="3" t="n"/>
-      <c r="B141" s="3" t="n"/>
-      <c r="C141" s="3" t="n"/>
-      <c r="D141" s="3" t="n"/>
-      <c r="E141" s="3" t="n"/>
-      <c r="F141" s="3" t="n"/>
-      <c r="G141" s="3" t="n"/>
-      <c r="H141" s="3" t="n"/>
-      <c r="I141" s="3" t="n"/>
-      <c r="J141" s="3" t="n"/>
-      <c r="K141" s="3" t="n"/>
-      <c r="L141" s="3" t="n"/>
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>16 allenamento B</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="inlineStr">
+        <is>
+          <t>4a</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="F141" s="5" t="inlineStr">
+        <is>
+          <t>Aerial Jerk</t>
+        </is>
+      </c>
+      <c r="G141" s="5" t="inlineStr">
+        <is>
+          <t>x 6+6</t>
+        </is>
+      </c>
+      <c r="H141" s="5" t="inlineStr"/>
+      <c r="I141" s="5" t="inlineStr"/>
+      <c r="J141" s="5" t="inlineStr">
+        <is>
+          <t>AMRAP 12'</t>
+        </is>
+      </c>
+      <c r="K141" s="5" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/0uI_9_0qR7k</t>
+        </is>
+      </c>
+      <c r="L141" s="5" t="inlineStr"/>
       <c r="M141" s="3" t="n"/>
       <c r="N141" s="3" t="n"/>
     </row>
     <row r="142">
-      <c r="A142" s="3" t="n"/>
-      <c r="B142" s="3" t="n"/>
-      <c r="C142" s="3" t="n"/>
-      <c r="D142" s="3" t="n"/>
-      <c r="E142" s="3" t="n"/>
-      <c r="F142" s="3" t="n"/>
-      <c r="G142" s="3" t="n"/>
-      <c r="H142" s="3" t="n"/>
-      <c r="I142" s="3" t="n"/>
-      <c r="J142" s="3" t="n"/>
-      <c r="K142" s="3" t="n"/>
-      <c r="L142" s="3" t="n"/>
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>16 allenamento B</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr">
+        <is>
+          <t>4b</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="n">
+        <v>205</v>
+      </c>
+      <c r="F142" s="5" t="inlineStr">
+        <is>
+          <t>Kick-through progression</t>
+        </is>
+      </c>
+      <c r="G142" s="5" t="inlineStr">
+        <is>
+          <t>x 10</t>
+        </is>
+      </c>
+      <c r="H142" s="5" t="inlineStr"/>
+      <c r="I142" s="5" t="inlineStr"/>
+      <c r="J142" s="5" t="inlineStr">
+        <is>
+          <t>AMRAP 12'</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/OGEUeBvoKc0?si=v7LIiDqSnd71NyM4</t>
+        </is>
+      </c>
+      <c r="L142" s="5" t="inlineStr"/>
       <c r="M142" s="3" t="n"/>
       <c r="N142" s="3" t="n"/>
     </row>
     <row r="143">
-      <c r="A143" s="3" t="n"/>
-      <c r="B143" s="3" t="n"/>
-      <c r="C143" s="3" t="n"/>
-      <c r="D143" s="3" t="n"/>
-      <c r="E143" s="3" t="n"/>
-      <c r="F143" s="3" t="n"/>
-      <c r="G143" s="3" t="n"/>
-      <c r="H143" s="3" t="n"/>
-      <c r="I143" s="3" t="n"/>
-      <c r="J143" s="3" t="n"/>
-      <c r="K143" s="3" t="n"/>
-      <c r="L143" s="3" t="n"/>
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>16 allenamento B</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="inlineStr">
+        <is>
+          <t>4c</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="F143" s="5" t="inlineStr">
+        <is>
+          <t>Ball over shoulder</t>
+        </is>
+      </c>
+      <c r="G143" s="5" t="inlineStr">
+        <is>
+          <t>x 8</t>
+        </is>
+      </c>
+      <c r="H143" s="5" t="inlineStr"/>
+      <c r="I143" s="5" t="inlineStr"/>
+      <c r="J143" s="5" t="inlineStr">
+        <is>
+          <t>AMRAP 12'</t>
+        </is>
+      </c>
+      <c r="K143" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Nwd-5fuLm3k?si=jGWxuH-RfvPTnkWN</t>
+        </is>
+      </c>
+      <c r="L143" s="5" t="inlineStr"/>
       <c r="M143" s="3" t="n"/>
       <c r="N143" s="3" t="n"/>
     </row>
     <row r="144">
-      <c r="A144" s="3" t="n"/>
-      <c r="B144" s="3" t="n"/>
-      <c r="C144" s="3" t="n"/>
-      <c r="D144" s="3" t="n"/>
-      <c r="E144" s="3" t="n"/>
-      <c r="F144" s="3" t="n"/>
-      <c r="G144" s="3" t="n"/>
-      <c r="H144" s="3" t="n"/>
-      <c r="I144" s="3" t="n"/>
-      <c r="J144" s="3" t="n"/>
-      <c r="K144" s="3" t="n"/>
-      <c r="L144" s="3" t="n"/>
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>17 allenamento A</t>
+        </is>
+      </c>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>1a</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>Pallof Press con elastico</t>
+        </is>
+      </c>
+      <c r="G144" s="4" t="inlineStr">
+        <is>
+          <t>3x10+10</t>
+        </is>
+      </c>
+      <c r="H144" s="4" t="inlineStr"/>
+      <c r="I144" s="4" t="inlineStr"/>
+      <c r="J144" s="4" t="inlineStr">
+        <is>
+          <t>jump set</t>
+        </is>
+      </c>
+      <c r="K144" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/aJ98KT13FtE?si=Li6fp-kbyh4wCnfT</t>
+        </is>
+      </c>
+      <c r="L144" s="4" t="inlineStr"/>
       <c r="M144" s="3" t="n"/>
       <c r="N144" s="3" t="n"/>
     </row>
     <row r="145">
-      <c r="A145" s="3" t="n"/>
-      <c r="B145" s="3" t="n"/>
-      <c r="C145" s="3" t="n"/>
-      <c r="D145" s="3" t="n"/>
-      <c r="E145" s="3" t="n"/>
-      <c r="F145" s="3" t="n"/>
-      <c r="G145" s="3" t="n"/>
-      <c r="H145" s="3" t="n"/>
-      <c r="I145" s="3" t="n"/>
-      <c r="J145" s="3" t="n"/>
-      <c r="K145" s="3" t="n"/>
-      <c r="L145" s="3" t="n"/>
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>17 allenamento A</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>1b</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="n">
+        <v>163</v>
+      </c>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>Arm basic DB pendulum</t>
+        </is>
+      </c>
+      <c r="G145" s="4" t="inlineStr">
+        <is>
+          <t>3x10+10</t>
+        </is>
+      </c>
+      <c r="H145" s="4" t="inlineStr">
+        <is>
+          <t>45"</t>
+        </is>
+      </c>
+      <c r="I145" s="4" t="inlineStr"/>
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t>jump set</t>
+        </is>
+      </c>
+      <c r="K145" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/WL2Gbf9klSI?si=R-4lfDqWZo7_yc9B</t>
+        </is>
+      </c>
+      <c r="L145" s="4" t="inlineStr"/>
       <c r="M145" s="3" t="n"/>
       <c r="N145" s="3" t="n"/>
     </row>
     <row r="146">
-      <c r="A146" s="3" t="n"/>
-      <c r="B146" s="3" t="n"/>
-      <c r="C146" s="3" t="n"/>
-      <c r="D146" s="3" t="n"/>
-      <c r="E146" s="3" t="n"/>
-      <c r="F146" s="3" t="n"/>
-      <c r="G146" s="3" t="n"/>
-      <c r="H146" s="3" t="n"/>
-      <c r="I146" s="3" t="n"/>
-      <c r="J146" s="3" t="n"/>
-      <c r="K146" s="3" t="n"/>
-      <c r="L146" s="3" t="n"/>
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>17 allenamento A</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>Bench press</t>
+        </is>
+      </c>
+      <c r="G146" s="4" t="inlineStr">
+        <is>
+          <t>4x6</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>90"</t>
+        </is>
+      </c>
+      <c r="I146" s="4" t="inlineStr"/>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>RPE 8.5</t>
+        </is>
+      </c>
+      <c r="K146" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/q_OfuLjIMFI</t>
+        </is>
+      </c>
+      <c r="L146" s="4" t="inlineStr"/>
       <c r="M146" s="3" t="n"/>
       <c r="N146" s="3" t="n"/>
     </row>
     <row r="147">
-      <c r="A147" s="3" t="n"/>
-      <c r="B147" s="3" t="n"/>
-      <c r="C147" s="3" t="n"/>
-      <c r="D147" s="3" t="n"/>
-      <c r="E147" s="3" t="n"/>
-      <c r="F147" s="3" t="n"/>
-      <c r="G147" s="3" t="n"/>
-      <c r="H147" s="3" t="n"/>
-      <c r="I147" s="3" t="n"/>
-      <c r="J147" s="3" t="n"/>
-      <c r="K147" s="3" t="n"/>
-      <c r="L147" s="3" t="n"/>
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>17 allenamento A</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>3a</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>pull up Progressioni</t>
+        </is>
+      </c>
+      <c r="G147" s="4" t="inlineStr">
+        <is>
+          <t>4x6-8</t>
+        </is>
+      </c>
+      <c r="H147" s="4" t="inlineStr"/>
+      <c r="I147" s="4" t="inlineStr"/>
+      <c r="J147" s="4" t="inlineStr">
+        <is>
+          <t>jump set | RPE 8</t>
+        </is>
+      </c>
+      <c r="K147" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/nSj7QKBbvWA?si=fGWg_soHjRYO0xex</t>
+        </is>
+      </c>
+      <c r="L147" s="4" t="inlineStr"/>
       <c r="M147" s="3" t="n"/>
       <c r="N147" s="3" t="n"/>
     </row>
     <row r="148">
-      <c r="A148" s="3" t="n"/>
-      <c r="B148" s="3" t="n"/>
-      <c r="C148" s="3" t="n"/>
-      <c r="D148" s="3" t="n"/>
-      <c r="E148" s="3" t="n"/>
-      <c r="F148" s="3" t="n"/>
-      <c r="G148" s="3" t="n"/>
-      <c r="H148" s="3" t="n"/>
-      <c r="I148" s="3" t="n"/>
-      <c r="J148" s="3" t="n"/>
-      <c r="K148" s="3" t="n"/>
-      <c r="L148" s="3" t="n"/>
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>17 allenamento A</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t>3b</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>One arm press</t>
+        </is>
+      </c>
+      <c r="G148" s="4" t="inlineStr">
+        <is>
+          <t>4x8+8</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="inlineStr">
+        <is>
+          <t>60"</t>
+        </is>
+      </c>
+      <c r="I148" s="4" t="inlineStr"/>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t>jump set | RPE 8</t>
+        </is>
+      </c>
+      <c r="K148" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/V-5Q4l-SM20</t>
+        </is>
+      </c>
+      <c r="L148" s="4" t="inlineStr"/>
       <c r="M148" s="3" t="n"/>
       <c r="N148" s="3" t="n"/>
     </row>
     <row r="149">
-      <c r="A149" s="3" t="n"/>
-      <c r="B149" s="3" t="n"/>
-      <c r="C149" s="3" t="n"/>
-      <c r="D149" s="3" t="n"/>
-      <c r="E149" s="3" t="n"/>
-      <c r="F149" s="3" t="n"/>
-      <c r="G149" s="3" t="n"/>
-      <c r="H149" s="3" t="n"/>
-      <c r="I149" s="3" t="n"/>
-      <c r="J149" s="3" t="n"/>
-      <c r="K149" s="3" t="n"/>
-      <c r="L149" s="3" t="n"/>
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>17 allenamento A</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>4a</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>Coiled Bench Row</t>
+        </is>
+      </c>
+      <c r="G149" s="4" t="inlineStr">
+        <is>
+          <t>3x10+10</t>
+        </is>
+      </c>
+      <c r="H149" s="4" t="inlineStr"/>
+      <c r="I149" s="4" t="inlineStr"/>
+      <c r="J149" s="4" t="inlineStr">
+        <is>
+          <t>circuito (3 round)</t>
+        </is>
+      </c>
+      <c r="K149" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/2gCslk95r20</t>
+        </is>
+      </c>
+      <c r="L149" s="4" t="inlineStr"/>
       <c r="M149" s="3" t="n"/>
       <c r="N149" s="3" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>17 allenamento A</t>
+        </is>
+      </c>
+      <c r="D150" s="4" t="inlineStr">
+        <is>
+          <t>4b</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="n">
+        <v>234</v>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>rebound push up</t>
+        </is>
+      </c>
+      <c r="G150" s="4" t="inlineStr">
+        <is>
+          <t>3x8</t>
+        </is>
+      </c>
+      <c r="H150" s="4" t="inlineStr"/>
+      <c r="I150" s="4" t="inlineStr"/>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>circuito (3 round)</t>
+        </is>
+      </c>
+      <c r="K150" s="4" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/iSipY1JCKdQ</t>
+        </is>
+      </c>
+      <c r="L150" s="4" t="inlineStr"/>
+      <c r="M150" s="3" t="n"/>
+      <c r="N150" s="3" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>17 allenamento A</t>
+        </is>
+      </c>
+      <c r="D151" s="4" t="inlineStr">
+        <is>
+          <t>4c</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>air bike solo braccia</t>
+        </is>
+      </c>
+      <c r="G151" s="4" t="inlineStr">
+        <is>
+          <t>3x30"</t>
+        </is>
+      </c>
+      <c r="H151" s="4" t="inlineStr">
+        <is>
+          <t>60"</t>
+        </is>
+      </c>
+      <c r="I151" s="4" t="inlineStr"/>
+      <c r="J151" s="4" t="inlineStr">
+        <is>
+          <t>circuito (3 round)</t>
+        </is>
+      </c>
+      <c r="K151" s="4" t="inlineStr"/>
+      <c r="L151" s="4" t="inlineStr"/>
+      <c r="M151" s="3" t="n"/>
+      <c r="N151" s="3" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B152" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>18 allenamento B</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="inlineStr">
+        <is>
+          <t>1a</t>
+        </is>
+      </c>
+      <c r="E152" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="F152" s="5" t="inlineStr">
+        <is>
+          <t>Coiled Cobra</t>
+        </is>
+      </c>
+      <c r="G152" s="5" t="inlineStr">
+        <is>
+          <t>3x8+8</t>
+        </is>
+      </c>
+      <c r="H152" s="5" t="inlineStr"/>
+      <c r="I152" s="5" t="inlineStr"/>
+      <c r="J152" s="5" t="inlineStr">
+        <is>
+          <t>jump set</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/GU3ePuvJwMk</t>
+        </is>
+      </c>
+      <c r="L152" s="5" t="inlineStr"/>
+      <c r="M152" s="3" t="n"/>
+      <c r="N152" s="3" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="inlineStr">
+        <is>
+          <t>18 allenamento B</t>
+        </is>
+      </c>
+      <c r="D153" s="5" t="inlineStr">
+        <is>
+          <t>1b</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="F153" s="5" t="inlineStr">
+        <is>
+          <t>Wall High Pull</t>
+        </is>
+      </c>
+      <c r="G153" s="5" t="inlineStr">
+        <is>
+          <t>3x10+10</t>
+        </is>
+      </c>
+      <c r="H153" s="5" t="inlineStr">
+        <is>
+          <t>45"</t>
+        </is>
+      </c>
+      <c r="I153" s="5" t="inlineStr"/>
+      <c r="J153" s="5" t="inlineStr">
+        <is>
+          <t>jump set</t>
+        </is>
+      </c>
+      <c r="K153" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/EBv0BjKhUlA?si=I07YNW02JWJF-oiD</t>
+        </is>
+      </c>
+      <c r="L153" s="5" t="inlineStr"/>
+      <c r="M153" s="3" t="n"/>
+      <c r="N153" s="3" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>18 allenamento B</t>
+        </is>
+      </c>
+      <c r="D154" s="5" t="inlineStr">
+        <is>
+          <t>2a</t>
+        </is>
+      </c>
+      <c r="E154" s="5" t="n">
+        <v>218</v>
+      </c>
+      <c r="F154" s="5" t="inlineStr">
+        <is>
+          <t>Landmine Jerk</t>
+        </is>
+      </c>
+      <c r="G154" s="5" t="inlineStr">
+        <is>
+          <t>4x5+5</t>
+        </is>
+      </c>
+      <c r="H154" s="5" t="inlineStr">
+        <is>
+          <t>RBS 60"</t>
+        </is>
+      </c>
+      <c r="I154" s="5" t="inlineStr"/>
+      <c r="J154" s="5" t="inlineStr">
+        <is>
+          <t>jump set | RPE 8.5</t>
+        </is>
+      </c>
+      <c r="K154" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/zIqsjVRtc5o</t>
+        </is>
+      </c>
+      <c r="L154" s="5" t="inlineStr"/>
+      <c r="M154" s="3" t="n"/>
+      <c r="N154" s="3" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="inlineStr">
+        <is>
+          <t>18 allenamento B</t>
+        </is>
+      </c>
+      <c r="D155" s="5" t="inlineStr">
+        <is>
+          <t>2b</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="F155" s="5" t="inlineStr">
+        <is>
+          <t>Landmine Biker's Squat</t>
+        </is>
+      </c>
+      <c r="G155" s="5" t="inlineStr">
+        <is>
+          <t>4x8</t>
+        </is>
+      </c>
+      <c r="H155" s="5" t="inlineStr">
+        <is>
+          <t>RBS 60"</t>
+        </is>
+      </c>
+      <c r="I155" s="5" t="inlineStr"/>
+      <c r="J155" s="5" t="inlineStr">
+        <is>
+          <t>jump set | RPE 8</t>
+        </is>
+      </c>
+      <c r="K155" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/jqhow36DTdg</t>
+        </is>
+      </c>
+      <c r="L155" s="5" t="inlineStr"/>
+      <c r="M155" s="3" t="n"/>
+      <c r="N155" s="3" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B156" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C156" s="5" t="inlineStr">
+        <is>
+          <t>18 allenamento B</t>
+        </is>
+      </c>
+      <c r="D156" s="5" t="inlineStr">
+        <is>
+          <t>3a</t>
+        </is>
+      </c>
+      <c r="E156" s="5" t="n">
+        <v>191</v>
+      </c>
+      <c r="F156" s="5" t="inlineStr">
+        <is>
+          <t>Endless rope Standing Power Pull</t>
+        </is>
+      </c>
+      <c r="G156" s="5" t="inlineStr">
+        <is>
+          <t>4x20"</t>
+        </is>
+      </c>
+      <c r="H156" s="5" t="inlineStr"/>
+      <c r="I156" s="5" t="inlineStr"/>
+      <c r="J156" s="5" t="inlineStr">
+        <is>
+          <t>jump set</t>
+        </is>
+      </c>
+      <c r="K156" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/rRgKOg0qaA4?si=aYRTcGburOhwv1a6</t>
+        </is>
+      </c>
+      <c r="L156" s="5" t="inlineStr"/>
+      <c r="M156" s="3" t="n"/>
+      <c r="N156" s="3" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B157" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="inlineStr">
+        <is>
+          <t>18 allenamento B</t>
+        </is>
+      </c>
+      <c r="D157" s="5" t="inlineStr">
+        <is>
+          <t>3b</t>
+        </is>
+      </c>
+      <c r="E157" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="F157" s="5" t="inlineStr">
+        <is>
+          <t>Yin yang sit up press</t>
+        </is>
+      </c>
+      <c r="G157" s="5" t="inlineStr">
+        <is>
+          <t>4x8+8</t>
+        </is>
+      </c>
+      <c r="H157" s="5" t="inlineStr">
+        <is>
+          <t>45"</t>
+        </is>
+      </c>
+      <c r="I157" s="5" t="inlineStr"/>
+      <c r="J157" s="5" t="inlineStr">
+        <is>
+          <t>jump set</t>
+        </is>
+      </c>
+      <c r="K157" s="5" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/arECYW5JFeA</t>
+        </is>
+      </c>
+      <c r="L157" s="5" t="inlineStr"/>
+      <c r="M157" s="3" t="n"/>
+      <c r="N157" s="3" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B158" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="inlineStr">
+        <is>
+          <t>18 allenamento B</t>
+        </is>
+      </c>
+      <c r="D158" s="5" t="inlineStr">
+        <is>
+          <t>4a</t>
+        </is>
+      </c>
+      <c r="E158" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="F158" s="5" t="inlineStr">
+        <is>
+          <t>Aerial Jerk</t>
+        </is>
+      </c>
+      <c r="G158" s="5" t="inlineStr">
+        <is>
+          <t>x 6+6</t>
+        </is>
+      </c>
+      <c r="H158" s="5" t="inlineStr"/>
+      <c r="I158" s="5" t="inlineStr"/>
+      <c r="J158" s="5" t="inlineStr">
+        <is>
+          <t>AMRAP 12'</t>
+        </is>
+      </c>
+      <c r="K158" s="5" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/0uI_9_0qR7k</t>
+        </is>
+      </c>
+      <c r="L158" s="5" t="inlineStr"/>
+      <c r="M158" s="3" t="n"/>
+      <c r="N158" s="3" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="inlineStr">
+        <is>
+          <t>18 allenamento B</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>4b</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="n">
+        <v>205</v>
+      </c>
+      <c r="F159" s="5" t="inlineStr">
+        <is>
+          <t>Kick-through progression</t>
+        </is>
+      </c>
+      <c r="G159" s="5" t="inlineStr">
+        <is>
+          <t>x 10</t>
+        </is>
+      </c>
+      <c r="H159" s="5" t="inlineStr"/>
+      <c r="I159" s="5" t="inlineStr"/>
+      <c r="J159" s="5" t="inlineStr">
+        <is>
+          <t>AMRAP 12'</t>
+        </is>
+      </c>
+      <c r="K159" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/OGEUeBvoKc0?si=v7LIiDqSnd71NyM4</t>
+        </is>
+      </c>
+      <c r="L159" s="5" t="inlineStr"/>
+      <c r="M159" s="3" t="n"/>
+      <c r="N159" s="3" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="6" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B160" s="6" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="C160" s="6" t="inlineStr">
+        <is>
+          <t>18 allenamento B</t>
+        </is>
+      </c>
+      <c r="D160" s="6" t="inlineStr">
+        <is>
+          <t>4c</t>
+        </is>
+      </c>
+      <c r="E160" s="6" t="n">
+        <v>225</v>
+      </c>
+      <c r="F160" s="6" t="inlineStr">
+        <is>
+          <t>Ball over shoulder</t>
+        </is>
+      </c>
+      <c r="G160" s="6" t="inlineStr">
+        <is>
+          <t>x 8</t>
+        </is>
+      </c>
+      <c r="H160" s="6" t="inlineStr"/>
+      <c r="I160" s="6" t="inlineStr"/>
+      <c r="J160" s="6" t="inlineStr">
+        <is>
+          <t>AMRAP 12'</t>
+        </is>
+      </c>
+      <c r="K160" s="6" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Nwd-5fuLm3k?si=jGWxuH-RfvPTnkWN</t>
+        </is>
+      </c>
+      <c r="L160" s="6" t="inlineStr"/>
+      <c r="M160" s="3" t="n"/>
+      <c r="N160" s="3" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="n"/>
+      <c r="B161" s="3" t="n"/>
+      <c r="C161" s="3" t="n"/>
+      <c r="D161" s="3" t="n"/>
+      <c r="E161" s="3" t="n"/>
+      <c r="F161" s="3" t="n"/>
+      <c r="G161" s="3" t="n"/>
+      <c r="H161" s="3" t="n"/>
+      <c r="I161" s="3" t="n"/>
+      <c r="J161" s="3" t="n"/>
+      <c r="K161" s="3" t="n"/>
+      <c r="L161" s="3" t="n"/>
+      <c r="M161" s="3" t="n"/>
+      <c r="N161" s="3" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="n"/>
+      <c r="B162" s="3" t="n"/>
+      <c r="C162" s="3" t="n"/>
+      <c r="D162" s="3" t="n"/>
+      <c r="E162" s="3" t="n"/>
+      <c r="F162" s="3" t="n"/>
+      <c r="G162" s="3" t="n"/>
+      <c r="H162" s="3" t="n"/>
+      <c r="I162" s="3" t="n"/>
+      <c r="J162" s="3" t="n"/>
+      <c r="K162" s="3" t="n"/>
+      <c r="L162" s="3" t="n"/>
+      <c r="M162" s="3" t="n"/>
+      <c r="N162" s="3" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="n"/>
+      <c r="B163" s="3" t="n"/>
+      <c r="C163" s="3" t="n"/>
+      <c r="D163" s="3" t="n"/>
+      <c r="E163" s="3" t="n"/>
+      <c r="F163" s="3" t="n"/>
+      <c r="G163" s="3" t="n"/>
+      <c r="H163" s="3" t="n"/>
+      <c r="I163" s="3" t="n"/>
+      <c r="J163" s="3" t="n"/>
+      <c r="K163" s="3" t="n"/>
+      <c r="L163" s="3" t="n"/>
+      <c r="M163" s="3" t="n"/>
+      <c r="N163" s="3" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="n"/>
+      <c r="B164" s="3" t="n"/>
+      <c r="C164" s="3" t="n"/>
+      <c r="D164" s="3" t="n"/>
+      <c r="E164" s="3" t="n"/>
+      <c r="F164" s="3" t="n"/>
+      <c r="G164" s="3" t="n"/>
+      <c r="H164" s="3" t="n"/>
+      <c r="I164" s="3" t="n"/>
+      <c r="J164" s="3" t="n"/>
+      <c r="K164" s="3" t="n"/>
+      <c r="L164" s="3" t="n"/>
+      <c r="M164" s="3" t="n"/>
+      <c r="N164" s="3" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="n"/>
+      <c r="B165" s="3" t="n"/>
+      <c r="C165" s="3" t="n"/>
+      <c r="D165" s="3" t="n"/>
+      <c r="E165" s="3" t="n"/>
+      <c r="F165" s="3" t="n"/>
+      <c r="G165" s="3" t="n"/>
+      <c r="H165" s="3" t="n"/>
+      <c r="I165" s="3" t="n"/>
+      <c r="J165" s="3" t="n"/>
+      <c r="K165" s="3" t="n"/>
+      <c r="L165" s="3" t="n"/>
+      <c r="M165" s="3" t="n"/>
+      <c r="N165" s="3" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="n"/>
+      <c r="B166" s="3" t="n"/>
+      <c r="C166" s="3" t="n"/>
+      <c r="D166" s="3" t="n"/>
+      <c r="E166" s="3" t="n"/>
+      <c r="F166" s="3" t="n"/>
+      <c r="G166" s="3" t="n"/>
+      <c r="H166" s="3" t="n"/>
+      <c r="I166" s="3" t="n"/>
+      <c r="J166" s="3" t="n"/>
+      <c r="K166" s="3" t="n"/>
+      <c r="L166" s="3" t="n"/>
+      <c r="M166" s="3" t="n"/>
+      <c r="N166" s="3" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="n"/>
+      <c r="B167" s="3" t="n"/>
+      <c r="C167" s="3" t="n"/>
+      <c r="D167" s="3" t="n"/>
+      <c r="E167" s="3" t="n"/>
+      <c r="F167" s="3" t="n"/>
+      <c r="G167" s="3" t="n"/>
+      <c r="H167" s="3" t="n"/>
+      <c r="I167" s="3" t="n"/>
+      <c r="J167" s="3" t="n"/>
+      <c r="K167" s="3" t="n"/>
+      <c r="L167" s="3" t="n"/>
+      <c r="M167" s="3" t="n"/>
+      <c r="N167" s="3" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="n"/>
+      <c r="B168" s="3" t="n"/>
+      <c r="C168" s="3" t="n"/>
+      <c r="D168" s="3" t="n"/>
+      <c r="E168" s="3" t="n"/>
+      <c r="F168" s="3" t="n"/>
+      <c r="G168" s="3" t="n"/>
+      <c r="H168" s="3" t="n"/>
+      <c r="I168" s="3" t="n"/>
+      <c r="J168" s="3" t="n"/>
+      <c r="K168" s="3" t="n"/>
+      <c r="L168" s="3" t="n"/>
+      <c r="M168" s="3" t="n"/>
+      <c r="N168" s="3" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="n"/>
+      <c r="B169" s="3" t="n"/>
+      <c r="C169" s="3" t="n"/>
+      <c r="D169" s="3" t="n"/>
+      <c r="E169" s="3" t="n"/>
+      <c r="F169" s="3" t="n"/>
+      <c r="G169" s="3" t="n"/>
+      <c r="H169" s="3" t="n"/>
+      <c r="I169" s="3" t="n"/>
+      <c r="J169" s="3" t="n"/>
+      <c r="K169" s="3" t="n"/>
+      <c r="L169" s="3" t="n"/>
+      <c r="M169" s="3" t="n"/>
+      <c r="N169" s="3" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="n"/>
+      <c r="B170" s="3" t="n"/>
+      <c r="C170" s="3" t="n"/>
+      <c r="D170" s="3" t="n"/>
+      <c r="E170" s="3" t="n"/>
+      <c r="F170" s="3" t="n"/>
+      <c r="G170" s="3" t="n"/>
+      <c r="H170" s="3" t="n"/>
+      <c r="I170" s="3" t="n"/>
+      <c r="J170" s="3" t="n"/>
+      <c r="K170" s="3" t="n"/>
+      <c r="L170" s="3" t="n"/>
+      <c r="M170" s="3" t="n"/>
+      <c r="N170" s="3" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="n"/>
+      <c r="B171" s="3" t="n"/>
+      <c r="C171" s="3" t="n"/>
+      <c r="D171" s="3" t="n"/>
+      <c r="E171" s="3" t="n"/>
+      <c r="F171" s="3" t="n"/>
+      <c r="G171" s="3" t="n"/>
+      <c r="H171" s="3" t="n"/>
+      <c r="I171" s="3" t="n"/>
+      <c r="J171" s="3" t="n"/>
+      <c r="K171" s="3" t="n"/>
+      <c r="L171" s="3" t="n"/>
+      <c r="M171" s="3" t="n"/>
+      <c r="N171" s="3" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="n"/>
+      <c r="B172" s="3" t="n"/>
+      <c r="C172" s="3" t="n"/>
+      <c r="D172" s="3" t="n"/>
+      <c r="E172" s="3" t="n"/>
+      <c r="F172" s="3" t="n"/>
+      <c r="G172" s="3" t="n"/>
+      <c r="H172" s="3" t="n"/>
+      <c r="I172" s="3" t="n"/>
+      <c r="J172" s="3" t="n"/>
+      <c r="K172" s="3" t="n"/>
+      <c r="L172" s="3" t="n"/>
+      <c r="M172" s="3" t="n"/>
+      <c r="N172" s="3" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="n"/>
+      <c r="B173" s="3" t="n"/>
+      <c r="C173" s="3" t="n"/>
+      <c r="D173" s="3" t="n"/>
+      <c r="E173" s="3" t="n"/>
+      <c r="F173" s="3" t="n"/>
+      <c r="G173" s="3" t="n"/>
+      <c r="H173" s="3" t="n"/>
+      <c r="I173" s="3" t="n"/>
+      <c r="J173" s="3" t="n"/>
+      <c r="K173" s="3" t="n"/>
+      <c r="L173" s="3" t="n"/>
+      <c r="M173" s="3" t="n"/>
+      <c r="N173" s="3" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="n"/>
+      <c r="B174" s="3" t="n"/>
+      <c r="C174" s="3" t="n"/>
+      <c r="D174" s="3" t="n"/>
+      <c r="E174" s="3" t="n"/>
+      <c r="F174" s="3" t="n"/>
+      <c r="G174" s="3" t="n"/>
+      <c r="H174" s="3" t="n"/>
+      <c r="I174" s="3" t="n"/>
+      <c r="J174" s="3" t="n"/>
+      <c r="K174" s="3" t="n"/>
+      <c r="L174" s="3" t="n"/>
+      <c r="M174" s="3" t="n"/>
+      <c r="N174" s="3" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="n"/>
+      <c r="B175" s="3" t="n"/>
+      <c r="C175" s="3" t="n"/>
+      <c r="D175" s="3" t="n"/>
+      <c r="E175" s="3" t="n"/>
+      <c r="F175" s="3" t="n"/>
+      <c r="G175" s="3" t="n"/>
+      <c r="H175" s="3" t="n"/>
+      <c r="I175" s="3" t="n"/>
+      <c r="J175" s="3" t="n"/>
+      <c r="K175" s="3" t="n"/>
+      <c r="L175" s="3" t="n"/>
+      <c r="M175" s="3" t="n"/>
+      <c r="N175" s="3" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="n"/>
+      <c r="B176" s="3" t="n"/>
+      <c r="C176" s="3" t="n"/>
+      <c r="D176" s="3" t="n"/>
+      <c r="E176" s="3" t="n"/>
+      <c r="F176" s="3" t="n"/>
+      <c r="G176" s="3" t="n"/>
+      <c r="H176" s="3" t="n"/>
+      <c r="I176" s="3" t="n"/>
+      <c r="J176" s="3" t="n"/>
+      <c r="K176" s="3" t="n"/>
+      <c r="L176" s="3" t="n"/>
+      <c r="M176" s="3" t="n"/>
+      <c r="N176" s="3" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="n"/>
+      <c r="B177" s="3" t="n"/>
+      <c r="C177" s="3" t="n"/>
+      <c r="D177" s="3" t="n"/>
+      <c r="E177" s="3" t="n"/>
+      <c r="F177" s="3" t="n"/>
+      <c r="G177" s="3" t="n"/>
+      <c r="H177" s="3" t="n"/>
+      <c r="I177" s="3" t="n"/>
+      <c r="J177" s="3" t="n"/>
+      <c r="K177" s="3" t="n"/>
+      <c r="L177" s="3" t="n"/>
+      <c r="M177" s="3" t="n"/>
+      <c r="N177" s="3" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="n"/>
+      <c r="B178" s="3" t="n"/>
+      <c r="C178" s="3" t="n"/>
+      <c r="D178" s="3" t="n"/>
+      <c r="E178" s="3" t="n"/>
+      <c r="F178" s="3" t="n"/>
+      <c r="G178" s="3" t="n"/>
+      <c r="H178" s="3" t="n"/>
+      <c r="I178" s="3" t="n"/>
+      <c r="J178" s="3" t="n"/>
+      <c r="K178" s="3" t="n"/>
+      <c r="L178" s="3" t="n"/>
+      <c r="M178" s="3" t="n"/>
+      <c r="N178" s="3" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="n"/>
+      <c r="B179" s="3" t="n"/>
+      <c r="C179" s="3" t="n"/>
+      <c r="D179" s="3" t="n"/>
+      <c r="E179" s="3" t="n"/>
+      <c r="F179" s="3" t="n"/>
+      <c r="G179" s="3" t="n"/>
+      <c r="H179" s="3" t="n"/>
+      <c r="I179" s="3" t="n"/>
+      <c r="J179" s="3" t="n"/>
+      <c r="K179" s="3" t="n"/>
+      <c r="L179" s="3" t="n"/>
+      <c r="M179" s="3" t="n"/>
+      <c r="N179" s="3" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="n"/>
+      <c r="B180" s="3" t="n"/>
+      <c r="C180" s="3" t="n"/>
+      <c r="D180" s="3" t="n"/>
+      <c r="E180" s="3" t="n"/>
+      <c r="F180" s="3" t="n"/>
+      <c r="G180" s="3" t="n"/>
+      <c r="H180" s="3" t="n"/>
+      <c r="I180" s="3" t="n"/>
+      <c r="J180" s="3" t="n"/>
+      <c r="K180" s="3" t="n"/>
+      <c r="L180" s="3" t="n"/>
+      <c r="M180" s="3" t="n"/>
+      <c r="N180" s="3" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="n"/>
+      <c r="B181" s="3" t="n"/>
+      <c r="C181" s="3" t="n"/>
+      <c r="D181" s="3" t="n"/>
+      <c r="E181" s="3" t="n"/>
+      <c r="F181" s="3" t="n"/>
+      <c r="G181" s="3" t="n"/>
+      <c r="H181" s="3" t="n"/>
+      <c r="I181" s="3" t="n"/>
+      <c r="J181" s="3" t="n"/>
+      <c r="K181" s="3" t="n"/>
+      <c r="L181" s="3" t="n"/>
+      <c r="M181" s="3" t="n"/>
+      <c r="N181" s="3" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="n"/>
+      <c r="B182" s="3" t="n"/>
+      <c r="C182" s="3" t="n"/>
+      <c r="D182" s="3" t="n"/>
+      <c r="E182" s="3" t="n"/>
+      <c r="F182" s="3" t="n"/>
+      <c r="G182" s="3" t="n"/>
+      <c r="H182" s="3" t="n"/>
+      <c r="I182" s="3" t="n"/>
+      <c r="J182" s="3" t="n"/>
+      <c r="K182" s="3" t="n"/>
+      <c r="L182" s="3" t="n"/>
+      <c r="M182" s="3" t="n"/>
+      <c r="N182" s="3" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="n"/>
+      <c r="B183" s="3" t="n"/>
+      <c r="C183" s="3" t="n"/>
+      <c r="D183" s="3" t="n"/>
+      <c r="E183" s="3" t="n"/>
+      <c r="F183" s="3" t="n"/>
+      <c r="G183" s="3" t="n"/>
+      <c r="H183" s="3" t="n"/>
+      <c r="I183" s="3" t="n"/>
+      <c r="J183" s="3" t="n"/>
+      <c r="K183" s="3" t="n"/>
+      <c r="L183" s="3" t="n"/>
+      <c r="M183" s="3" t="n"/>
+      <c r="N183" s="3" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="n"/>
+      <c r="B184" s="3" t="n"/>
+      <c r="C184" s="3" t="n"/>
+      <c r="D184" s="3" t="n"/>
+      <c r="E184" s="3" t="n"/>
+      <c r="F184" s="3" t="n"/>
+      <c r="G184" s="3" t="n"/>
+      <c r="H184" s="3" t="n"/>
+      <c r="I184" s="3" t="n"/>
+      <c r="J184" s="3" t="n"/>
+      <c r="K184" s="3" t="n"/>
+      <c r="L184" s="3" t="n"/>
+      <c r="M184" s="3" t="n"/>
+      <c r="N184" s="3" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="n"/>
+      <c r="B185" s="3" t="n"/>
+      <c r="C185" s="3" t="n"/>
+      <c r="D185" s="3" t="n"/>
+      <c r="E185" s="3" t="n"/>
+      <c r="F185" s="3" t="n"/>
+      <c r="G185" s="3" t="n"/>
+      <c r="H185" s="3" t="n"/>
+      <c r="I185" s="3" t="n"/>
+      <c r="J185" s="3" t="n"/>
+      <c r="K185" s="3" t="n"/>
+      <c r="L185" s="3" t="n"/>
+      <c r="M185" s="3" t="n"/>
+      <c r="N185" s="3" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="n"/>
+      <c r="B186" s="3" t="n"/>
+      <c r="C186" s="3" t="n"/>
+      <c r="D186" s="3" t="n"/>
+      <c r="E186" s="3" t="n"/>
+      <c r="F186" s="3" t="n"/>
+      <c r="G186" s="3" t="n"/>
+      <c r="H186" s="3" t="n"/>
+      <c r="I186" s="3" t="n"/>
+      <c r="J186" s="3" t="n"/>
+      <c r="K186" s="3" t="n"/>
+      <c r="L186" s="3" t="n"/>
+      <c r="M186" s="3" t="n"/>
+      <c r="N186" s="3" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="n"/>
+      <c r="B187" s="3" t="n"/>
+      <c r="C187" s="3" t="n"/>
+      <c r="D187" s="3" t="n"/>
+      <c r="E187" s="3" t="n"/>
+      <c r="F187" s="3" t="n"/>
+      <c r="G187" s="3" t="n"/>
+      <c r="H187" s="3" t="n"/>
+      <c r="I187" s="3" t="n"/>
+      <c r="J187" s="3" t="n"/>
+      <c r="K187" s="3" t="n"/>
+      <c r="L187" s="3" t="n"/>
+      <c r="M187" s="3" t="n"/>
+      <c r="N187" s="3" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="n"/>
+      <c r="B188" s="3" t="n"/>
+      <c r="C188" s="3" t="n"/>
+      <c r="D188" s="3" t="n"/>
+      <c r="E188" s="3" t="n"/>
+      <c r="F188" s="3" t="n"/>
+      <c r="G188" s="3" t="n"/>
+      <c r="H188" s="3" t="n"/>
+      <c r="I188" s="3" t="n"/>
+      <c r="J188" s="3" t="n"/>
+      <c r="K188" s="3" t="n"/>
+      <c r="L188" s="3" t="n"/>
+      <c r="M188" s="3" t="n"/>
+      <c r="N188" s="3" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="n"/>
+      <c r="B189" s="3" t="n"/>
+      <c r="C189" s="3" t="n"/>
+      <c r="D189" s="3" t="n"/>
+      <c r="E189" s="3" t="n"/>
+      <c r="F189" s="3" t="n"/>
+      <c r="G189" s="3" t="n"/>
+      <c r="H189" s="3" t="n"/>
+      <c r="I189" s="3" t="n"/>
+      <c r="J189" s="3" t="n"/>
+      <c r="K189" s="3" t="n"/>
+      <c r="L189" s="3" t="n"/>
+      <c r="M189" s="3" t="n"/>
+      <c r="N189" s="3" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="3" t="n"/>
+      <c r="B190" s="3" t="n"/>
+      <c r="C190" s="3" t="n"/>
+      <c r="D190" s="3" t="n"/>
+      <c r="E190" s="3" t="n"/>
+      <c r="F190" s="3" t="n"/>
+      <c r="G190" s="3" t="n"/>
+      <c r="H190" s="3" t="n"/>
+      <c r="I190" s="3" t="n"/>
+      <c r="J190" s="3" t="n"/>
+      <c r="K190" s="3" t="n"/>
+      <c r="L190" s="3" t="n"/>
+      <c r="M190" s="3" t="n"/>
+      <c r="N190" s="3" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="n"/>
+      <c r="B191" s="3" t="n"/>
+      <c r="C191" s="3" t="n"/>
+      <c r="D191" s="3" t="n"/>
+      <c r="E191" s="3" t="n"/>
+      <c r="F191" s="3" t="n"/>
+      <c r="G191" s="3" t="n"/>
+      <c r="H191" s="3" t="n"/>
+      <c r="I191" s="3" t="n"/>
+      <c r="J191" s="3" t="n"/>
+      <c r="K191" s="3" t="n"/>
+      <c r="L191" s="3" t="n"/>
+      <c r="M191" s="3" t="n"/>
+      <c r="N191" s="3" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="n"/>
+      <c r="B192" s="3" t="n"/>
+      <c r="C192" s="3" t="n"/>
+      <c r="D192" s="3" t="n"/>
+      <c r="E192" s="3" t="n"/>
+      <c r="F192" s="3" t="n"/>
+      <c r="G192" s="3" t="n"/>
+      <c r="H192" s="3" t="n"/>
+      <c r="I192" s="3" t="n"/>
+      <c r="J192" s="3" t="n"/>
+      <c r="K192" s="3" t="n"/>
+      <c r="L192" s="3" t="n"/>
+      <c r="M192" s="3" t="n"/>
+      <c r="N192" s="3" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="3" t="n"/>
+      <c r="B193" s="3" t="n"/>
+      <c r="C193" s="3" t="n"/>
+      <c r="D193" s="3" t="n"/>
+      <c r="E193" s="3" t="n"/>
+      <c r="F193" s="3" t="n"/>
+      <c r="G193" s="3" t="n"/>
+      <c r="H193" s="3" t="n"/>
+      <c r="I193" s="3" t="n"/>
+      <c r="J193" s="3" t="n"/>
+      <c r="K193" s="3" t="n"/>
+      <c r="L193" s="3" t="n"/>
+      <c r="M193" s="3" t="n"/>
+      <c r="N193" s="3" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="n"/>
+      <c r="B194" s="3" t="n"/>
+      <c r="C194" s="3" t="n"/>
+      <c r="D194" s="3" t="n"/>
+      <c r="E194" s="3" t="n"/>
+      <c r="F194" s="3" t="n"/>
+      <c r="G194" s="3" t="n"/>
+      <c r="H194" s="3" t="n"/>
+      <c r="I194" s="3" t="n"/>
+      <c r="J194" s="3" t="n"/>
+      <c r="K194" s="3" t="n"/>
+      <c r="L194" s="3" t="n"/>
+      <c r="M194" s="3" t="n"/>
+      <c r="N194" s="3" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="3" t="n"/>
+      <c r="B195" s="3" t="n"/>
+      <c r="C195" s="3" t="n"/>
+      <c r="D195" s="3" t="n"/>
+      <c r="E195" s="3" t="n"/>
+      <c r="F195" s="3" t="n"/>
+      <c r="G195" s="3" t="n"/>
+      <c r="H195" s="3" t="n"/>
+      <c r="I195" s="3" t="n"/>
+      <c r="J195" s="3" t="n"/>
+      <c r="K195" s="3" t="n"/>
+      <c r="L195" s="3" t="n"/>
+      <c r="M195" s="3" t="n"/>
+      <c r="N195" s="3" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="n"/>
+      <c r="B196" s="3" t="n"/>
+      <c r="C196" s="3" t="n"/>
+      <c r="D196" s="3" t="n"/>
+      <c r="E196" s="3" t="n"/>
+      <c r="F196" s="3" t="n"/>
+      <c r="G196" s="3" t="n"/>
+      <c r="H196" s="3" t="n"/>
+      <c r="I196" s="3" t="n"/>
+      <c r="J196" s="3" t="n"/>
+      <c r="K196" s="3" t="n"/>
+      <c r="L196" s="3" t="n"/>
+      <c r="M196" s="3" t="n"/>
+      <c r="N196" s="3" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="n"/>
+      <c r="B197" s="3" t="n"/>
+      <c r="C197" s="3" t="n"/>
+      <c r="D197" s="3" t="n"/>
+      <c r="E197" s="3" t="n"/>
+      <c r="F197" s="3" t="n"/>
+      <c r="G197" s="3" t="n"/>
+      <c r="H197" s="3" t="n"/>
+      <c r="I197" s="3" t="n"/>
+      <c r="J197" s="3" t="n"/>
+      <c r="K197" s="3" t="n"/>
+      <c r="L197" s="3" t="n"/>
+      <c r="M197" s="3" t="n"/>
+      <c r="N197" s="3" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="3" t="n"/>
+      <c r="B198" s="3" t="n"/>
+      <c r="C198" s="3" t="n"/>
+      <c r="D198" s="3" t="n"/>
+      <c r="E198" s="3" t="n"/>
+      <c r="F198" s="3" t="n"/>
+      <c r="G198" s="3" t="n"/>
+      <c r="H198" s="3" t="n"/>
+      <c r="I198" s="3" t="n"/>
+      <c r="J198" s="3" t="n"/>
+      <c r="K198" s="3" t="n"/>
+      <c r="L198" s="3" t="n"/>
+      <c r="M198" s="3" t="n"/>
+      <c r="N198" s="3" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="3" t="n"/>
+      <c r="B199" s="3" t="n"/>
+      <c r="C199" s="3" t="n"/>
+      <c r="D199" s="3" t="n"/>
+      <c r="E199" s="3" t="n"/>
+      <c r="F199" s="3" t="n"/>
+      <c r="G199" s="3" t="n"/>
+      <c r="H199" s="3" t="n"/>
+      <c r="I199" s="3" t="n"/>
+      <c r="J199" s="3" t="n"/>
+      <c r="K199" s="3" t="n"/>
+      <c r="L199" s="3" t="n"/>
+      <c r="M199" s="3" t="n"/>
+      <c r="N199" s="3" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="n"/>
+      <c r="B200" s="3" t="n"/>
+      <c r="C200" s="3" t="n"/>
+      <c r="D200" s="3" t="n"/>
+      <c r="E200" s="3" t="n"/>
+      <c r="F200" s="3" t="n"/>
+      <c r="G200" s="3" t="n"/>
+      <c r="H200" s="3" t="n"/>
+      <c r="I200" s="3" t="n"/>
+      <c r="J200" s="3" t="n"/>
+      <c r="K200" s="3" t="n"/>
+      <c r="L200" s="3" t="n"/>
+      <c r="M200" s="3" t="n"/>
+      <c r="N200" s="3" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="3" t="n"/>
+      <c r="B201" s="3" t="n"/>
+      <c r="C201" s="3" t="n"/>
+      <c r="D201" s="3" t="n"/>
+      <c r="E201" s="3" t="n"/>
+      <c r="F201" s="3" t="n"/>
+      <c r="G201" s="3" t="n"/>
+      <c r="H201" s="3" t="n"/>
+      <c r="I201" s="3" t="n"/>
+      <c r="J201" s="3" t="n"/>
+      <c r="K201" s="3" t="n"/>
+      <c r="L201" s="3" t="n"/>
+      <c r="M201" s="3" t="n"/>
+      <c r="N201" s="3" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="3" t="n"/>
+      <c r="B202" s="3" t="n"/>
+      <c r="C202" s="3" t="n"/>
+      <c r="D202" s="3" t="n"/>
+      <c r="E202" s="3" t="n"/>
+      <c r="F202" s="3" t="n"/>
+      <c r="G202" s="3" t="n"/>
+      <c r="H202" s="3" t="n"/>
+      <c r="I202" s="3" t="n"/>
+      <c r="J202" s="3" t="n"/>
+      <c r="K202" s="3" t="n"/>
+      <c r="L202" s="3" t="n"/>
+      <c r="M202" s="3" t="n"/>
+      <c r="N202" s="3" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="3" t="n"/>
+      <c r="B203" s="3" t="n"/>
+      <c r="C203" s="3" t="n"/>
+      <c r="D203" s="3" t="n"/>
+      <c r="E203" s="3" t="n"/>
+      <c r="F203" s="3" t="n"/>
+      <c r="G203" s="3" t="n"/>
+      <c r="H203" s="3" t="n"/>
+      <c r="I203" s="3" t="n"/>
+      <c r="J203" s="3" t="n"/>
+      <c r="K203" s="3" t="n"/>
+      <c r="L203" s="3" t="n"/>
+      <c r="M203" s="3" t="n"/>
+      <c r="N203" s="3" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="n"/>
+      <c r="B204" s="3" t="n"/>
+      <c r="C204" s="3" t="n"/>
+      <c r="D204" s="3" t="n"/>
+      <c r="E204" s="3" t="n"/>
+      <c r="F204" s="3" t="n"/>
+      <c r="G204" s="3" t="n"/>
+      <c r="H204" s="3" t="n"/>
+      <c r="I204" s="3" t="n"/>
+      <c r="J204" s="3" t="n"/>
+      <c r="K204" s="3" t="n"/>
+      <c r="L204" s="3" t="n"/>
+      <c r="M204" s="3" t="n"/>
+      <c r="N204" s="3" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="n"/>
+      <c r="B205" s="3" t="n"/>
+      <c r="C205" s="3" t="n"/>
+      <c r="D205" s="3" t="n"/>
+      <c r="E205" s="3" t="n"/>
+      <c r="F205" s="3" t="n"/>
+      <c r="G205" s="3" t="n"/>
+      <c r="H205" s="3" t="n"/>
+      <c r="I205" s="3" t="n"/>
+      <c r="J205" s="3" t="n"/>
+      <c r="K205" s="3" t="n"/>
+      <c r="L205" s="3" t="n"/>
+      <c r="M205" s="3" t="n"/>
+      <c r="N205" s="3" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="3" t="n"/>
+      <c r="B206" s="3" t="n"/>
+      <c r="C206" s="3" t="n"/>
+      <c r="D206" s="3" t="n"/>
+      <c r="E206" s="3" t="n"/>
+      <c r="F206" s="3" t="n"/>
+      <c r="G206" s="3" t="n"/>
+      <c r="H206" s="3" t="n"/>
+      <c r="I206" s="3" t="n"/>
+      <c r="J206" s="3" t="n"/>
+      <c r="K206" s="3" t="n"/>
+      <c r="L206" s="3" t="n"/>
+      <c r="M206" s="3" t="n"/>
+      <c r="N206" s="3" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="n"/>
+      <c r="B207" s="3" t="n"/>
+      <c r="C207" s="3" t="n"/>
+      <c r="D207" s="3" t="n"/>
+      <c r="E207" s="3" t="n"/>
+      <c r="F207" s="3" t="n"/>
+      <c r="G207" s="3" t="n"/>
+      <c r="H207" s="3" t="n"/>
+      <c r="I207" s="3" t="n"/>
+      <c r="J207" s="3" t="n"/>
+      <c r="K207" s="3" t="n"/>
+      <c r="L207" s="3" t="n"/>
+      <c r="M207" s="3" t="n"/>
+      <c r="N207" s="3" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="n"/>
+      <c r="B208" s="3" t="n"/>
+      <c r="C208" s="3" t="n"/>
+      <c r="D208" s="3" t="n"/>
+      <c r="E208" s="3" t="n"/>
+      <c r="F208" s="3" t="n"/>
+      <c r="G208" s="3" t="n"/>
+      <c r="H208" s="3" t="n"/>
+      <c r="I208" s="3" t="n"/>
+      <c r="J208" s="3" t="n"/>
+      <c r="K208" s="3" t="n"/>
+      <c r="L208" s="3" t="n"/>
+      <c r="M208" s="3" t="n"/>
+      <c r="N208" s="3" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="n"/>
+      <c r="B209" s="3" t="n"/>
+      <c r="C209" s="3" t="n"/>
+      <c r="D209" s="3" t="n"/>
+      <c r="E209" s="3" t="n"/>
+      <c r="F209" s="3" t="n"/>
+      <c r="G209" s="3" t="n"/>
+      <c r="H209" s="3" t="n"/>
+      <c r="I209" s="3" t="n"/>
+      <c r="J209" s="3" t="n"/>
+      <c r="K209" s="3" t="n"/>
+      <c r="L209" s="3" t="n"/>
+      <c r="M209" s="3" t="n"/>
+      <c r="N209" s="3" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="n"/>
+      <c r="B210" s="3" t="n"/>
+      <c r="C210" s="3" t="n"/>
+      <c r="D210" s="3" t="n"/>
+      <c r="E210" s="3" t="n"/>
+      <c r="F210" s="3" t="n"/>
+      <c r="G210" s="3" t="n"/>
+      <c r="H210" s="3" t="n"/>
+      <c r="I210" s="3" t="n"/>
+      <c r="J210" s="3" t="n"/>
+      <c r="K210" s="3" t="n"/>
+      <c r="L210" s="3" t="n"/>
+      <c r="M210" s="3" t="n"/>
+      <c r="N210" s="3" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="3" t="n"/>
+      <c r="B211" s="3" t="n"/>
+      <c r="C211" s="3" t="n"/>
+      <c r="D211" s="3" t="n"/>
+      <c r="E211" s="3" t="n"/>
+      <c r="F211" s="3" t="n"/>
+      <c r="G211" s="3" t="n"/>
+      <c r="H211" s="3" t="n"/>
+      <c r="I211" s="3" t="n"/>
+      <c r="J211" s="3" t="n"/>
+      <c r="K211" s="3" t="n"/>
+      <c r="L211" s="3" t="n"/>
+      <c r="M211" s="3" t="n"/>
+      <c r="N211" s="3" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="3" t="n"/>
+      <c r="B212" s="3" t="n"/>
+      <c r="C212" s="3" t="n"/>
+      <c r="D212" s="3" t="n"/>
+      <c r="E212" s="3" t="n"/>
+      <c r="F212" s="3" t="n"/>
+      <c r="G212" s="3" t="n"/>
+      <c r="H212" s="3" t="n"/>
+      <c r="I212" s="3" t="n"/>
+      <c r="J212" s="3" t="n"/>
+      <c r="K212" s="3" t="n"/>
+      <c r="L212" s="3" t="n"/>
+      <c r="M212" s="3" t="n"/>
+      <c r="N212" s="3" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="3" t="n"/>
+      <c r="B213" s="3" t="n"/>
+      <c r="C213" s="3" t="n"/>
+      <c r="D213" s="3" t="n"/>
+      <c r="E213" s="3" t="n"/>
+      <c r="F213" s="3" t="n"/>
+      <c r="G213" s="3" t="n"/>
+      <c r="H213" s="3" t="n"/>
+      <c r="I213" s="3" t="n"/>
+      <c r="J213" s="3" t="n"/>
+      <c r="K213" s="3" t="n"/>
+      <c r="L213" s="3" t="n"/>
+      <c r="M213" s="3" t="n"/>
+      <c r="N213" s="3" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="3" t="n"/>
+      <c r="B214" s="3" t="n"/>
+      <c r="C214" s="3" t="n"/>
+      <c r="D214" s="3" t="n"/>
+      <c r="E214" s="3" t="n"/>
+      <c r="F214" s="3" t="n"/>
+      <c r="G214" s="3" t="n"/>
+      <c r="H214" s="3" t="n"/>
+      <c r="I214" s="3" t="n"/>
+      <c r="J214" s="3" t="n"/>
+      <c r="K214" s="3" t="n"/>
+      <c r="L214" s="3" t="n"/>
+      <c r="M214" s="3" t="n"/>
+      <c r="N214" s="3" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="3" t="n"/>
+      <c r="B215" s="3" t="n"/>
+      <c r="C215" s="3" t="n"/>
+      <c r="D215" s="3" t="n"/>
+      <c r="E215" s="3" t="n"/>
+      <c r="F215" s="3" t="n"/>
+      <c r="G215" s="3" t="n"/>
+      <c r="H215" s="3" t="n"/>
+      <c r="I215" s="3" t="n"/>
+      <c r="J215" s="3" t="n"/>
+      <c r="K215" s="3" t="n"/>
+      <c r="L215" s="3" t="n"/>
+      <c r="M215" s="3" t="n"/>
+      <c r="N215" s="3" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="3" t="n"/>
+      <c r="B216" s="3" t="n"/>
+      <c r="C216" s="3" t="n"/>
+      <c r="D216" s="3" t="n"/>
+      <c r="E216" s="3" t="n"/>
+      <c r="F216" s="3" t="n"/>
+      <c r="G216" s="3" t="n"/>
+      <c r="H216" s="3" t="n"/>
+      <c r="I216" s="3" t="n"/>
+      <c r="J216" s="3" t="n"/>
+      <c r="K216" s="3" t="n"/>
+      <c r="L216" s="3" t="n"/>
+      <c r="M216" s="3" t="n"/>
+      <c r="N216" s="3" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="3" t="n"/>
+      <c r="B217" s="3" t="n"/>
+      <c r="C217" s="3" t="n"/>
+      <c r="D217" s="3" t="n"/>
+      <c r="E217" s="3" t="n"/>
+      <c r="F217" s="3" t="n"/>
+      <c r="G217" s="3" t="n"/>
+      <c r="H217" s="3" t="n"/>
+      <c r="I217" s="3" t="n"/>
+      <c r="J217" s="3" t="n"/>
+      <c r="K217" s="3" t="n"/>
+      <c r="L217" s="3" t="n"/>
+      <c r="M217" s="3" t="n"/>
+      <c r="N217" s="3" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="3" t="n"/>
+      <c r="B218" s="3" t="n"/>
+      <c r="C218" s="3" t="n"/>
+      <c r="D218" s="3" t="n"/>
+      <c r="E218" s="3" t="n"/>
+      <c r="F218" s="3" t="n"/>
+      <c r="G218" s="3" t="n"/>
+      <c r="H218" s="3" t="n"/>
+      <c r="I218" s="3" t="n"/>
+      <c r="J218" s="3" t="n"/>
+      <c r="K218" s="3" t="n"/>
+      <c r="L218" s="3" t="n"/>
+      <c r="M218" s="3" t="n"/>
+      <c r="N218" s="3" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="3" t="n"/>
+      <c r="B219" s="3" t="n"/>
+      <c r="C219" s="3" t="n"/>
+      <c r="D219" s="3" t="n"/>
+      <c r="E219" s="3" t="n"/>
+      <c r="F219" s="3" t="n"/>
+      <c r="G219" s="3" t="n"/>
+      <c r="H219" s="3" t="n"/>
+      <c r="I219" s="3" t="n"/>
+      <c r="J219" s="3" t="n"/>
+      <c r="K219" s="3" t="n"/>
+      <c r="L219" s="3" t="n"/>
+      <c r="M219" s="3" t="n"/>
+      <c r="N219" s="3" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="3" t="n"/>
+      <c r="B220" s="3" t="n"/>
+      <c r="C220" s="3" t="n"/>
+      <c r="D220" s="3" t="n"/>
+      <c r="E220" s="3" t="n"/>
+      <c r="F220" s="3" t="n"/>
+      <c r="G220" s="3" t="n"/>
+      <c r="H220" s="3" t="n"/>
+      <c r="I220" s="3" t="n"/>
+      <c r="J220" s="3" t="n"/>
+      <c r="K220" s="3" t="n"/>
+      <c r="L220" s="3" t="n"/>
+      <c r="M220" s="3" t="n"/>
+      <c r="N220" s="3" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="3" t="n"/>
+      <c r="B221" s="3" t="n"/>
+      <c r="C221" s="3" t="n"/>
+      <c r="D221" s="3" t="n"/>
+      <c r="E221" s="3" t="n"/>
+      <c r="F221" s="3" t="n"/>
+      <c r="G221" s="3" t="n"/>
+      <c r="H221" s="3" t="n"/>
+      <c r="I221" s="3" t="n"/>
+      <c r="J221" s="3" t="n"/>
+      <c r="K221" s="3" t="n"/>
+      <c r="L221" s="3" t="n"/>
+      <c r="M221" s="3" t="n"/>
+      <c r="N221" s="3" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="3" t="n"/>
+      <c r="B222" s="3" t="n"/>
+      <c r="C222" s="3" t="n"/>
+      <c r="D222" s="3" t="n"/>
+      <c r="E222" s="3" t="n"/>
+      <c r="F222" s="3" t="n"/>
+      <c r="G222" s="3" t="n"/>
+      <c r="H222" s="3" t="n"/>
+      <c r="I222" s="3" t="n"/>
+      <c r="J222" s="3" t="n"/>
+      <c r="K222" s="3" t="n"/>
+      <c r="L222" s="3" t="n"/>
+      <c r="M222" s="3" t="n"/>
+      <c r="N222" s="3" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="3" t="n"/>
+      <c r="B223" s="3" t="n"/>
+      <c r="C223" s="3" t="n"/>
+      <c r="D223" s="3" t="n"/>
+      <c r="E223" s="3" t="n"/>
+      <c r="F223" s="3" t="n"/>
+      <c r="G223" s="3" t="n"/>
+      <c r="H223" s="3" t="n"/>
+      <c r="I223" s="3" t="n"/>
+      <c r="J223" s="3" t="n"/>
+      <c r="K223" s="3" t="n"/>
+      <c r="L223" s="3" t="n"/>
+      <c r="M223" s="3" t="n"/>
+      <c r="N223" s="3" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="3" t="n"/>
+      <c r="B224" s="3" t="n"/>
+      <c r="C224" s="3" t="n"/>
+      <c r="D224" s="3" t="n"/>
+      <c r="E224" s="3" t="n"/>
+      <c r="F224" s="3" t="n"/>
+      <c r="G224" s="3" t="n"/>
+      <c r="H224" s="3" t="n"/>
+      <c r="I224" s="3" t="n"/>
+      <c r="J224" s="3" t="n"/>
+      <c r="K224" s="3" t="n"/>
+      <c r="L224" s="3" t="n"/>
+      <c r="M224" s="3" t="n"/>
+      <c r="N224" s="3" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="3" t="n"/>
+      <c r="B225" s="3" t="n"/>
+      <c r="C225" s="3" t="n"/>
+      <c r="D225" s="3" t="n"/>
+      <c r="E225" s="3" t="n"/>
+      <c r="F225" s="3" t="n"/>
+      <c r="G225" s="3" t="n"/>
+      <c r="H225" s="3" t="n"/>
+      <c r="I225" s="3" t="n"/>
+      <c r="J225" s="3" t="n"/>
+      <c r="K225" s="3" t="n"/>
+      <c r="L225" s="3" t="n"/>
+      <c r="M225" s="3" t="n"/>
+      <c r="N225" s="3" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="3" t="n"/>
+      <c r="B226" s="3" t="n"/>
+      <c r="C226" s="3" t="n"/>
+      <c r="D226" s="3" t="n"/>
+      <c r="E226" s="3" t="n"/>
+      <c r="F226" s="3" t="n"/>
+      <c r="G226" s="3" t="n"/>
+      <c r="H226" s="3" t="n"/>
+      <c r="I226" s="3" t="n"/>
+      <c r="J226" s="3" t="n"/>
+      <c r="K226" s="3" t="n"/>
+      <c r="L226" s="3" t="n"/>
+      <c r="M226" s="3" t="n"/>
+      <c r="N226" s="3" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="3" t="n"/>
+      <c r="B227" s="3" t="n"/>
+      <c r="C227" s="3" t="n"/>
+      <c r="D227" s="3" t="n"/>
+      <c r="E227" s="3" t="n"/>
+      <c r="F227" s="3" t="n"/>
+      <c r="G227" s="3" t="n"/>
+      <c r="H227" s="3" t="n"/>
+      <c r="I227" s="3" t="n"/>
+      <c r="J227" s="3" t="n"/>
+      <c r="K227" s="3" t="n"/>
+      <c r="L227" s="3" t="n"/>
+      <c r="M227" s="3" t="n"/>
+      <c r="N227" s="3" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="3" t="n"/>
+      <c r="B228" s="3" t="n"/>
+      <c r="C228" s="3" t="n"/>
+      <c r="D228" s="3" t="n"/>
+      <c r="E228" s="3" t="n"/>
+      <c r="F228" s="3" t="n"/>
+      <c r="G228" s="3" t="n"/>
+      <c r="H228" s="3" t="n"/>
+      <c r="I228" s="3" t="n"/>
+      <c r="J228" s="3" t="n"/>
+      <c r="K228" s="3" t="n"/>
+      <c r="L228" s="3" t="n"/>
+      <c r="M228" s="3" t="n"/>
+      <c r="N228" s="3" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="3" t="n"/>
+      <c r="B229" s="3" t="n"/>
+      <c r="C229" s="3" t="n"/>
+      <c r="D229" s="3" t="n"/>
+      <c r="E229" s="3" t="n"/>
+      <c r="F229" s="3" t="n"/>
+      <c r="G229" s="3" t="n"/>
+      <c r="H229" s="3" t="n"/>
+      <c r="I229" s="3" t="n"/>
+      <c r="J229" s="3" t="n"/>
+      <c r="K229" s="3" t="n"/>
+      <c r="L229" s="3" t="n"/>
+      <c r="M229" s="3" t="n"/>
+      <c r="N229" s="3" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="3" t="n"/>
+      <c r="B230" s="3" t="n"/>
+      <c r="C230" s="3" t="n"/>
+      <c r="D230" s="3" t="n"/>
+      <c r="E230" s="3" t="n"/>
+      <c r="F230" s="3" t="n"/>
+      <c r="G230" s="3" t="n"/>
+      <c r="H230" s="3" t="n"/>
+      <c r="I230" s="3" t="n"/>
+      <c r="J230" s="3" t="n"/>
+      <c r="K230" s="3" t="n"/>
+      <c r="L230" s="3" t="n"/>
+      <c r="M230" s="3" t="n"/>
+      <c r="N230" s="3" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="3" t="n"/>
+      <c r="B231" s="3" t="n"/>
+      <c r="C231" s="3" t="n"/>
+      <c r="D231" s="3" t="n"/>
+      <c r="E231" s="3" t="n"/>
+      <c r="F231" s="3" t="n"/>
+      <c r="G231" s="3" t="n"/>
+      <c r="H231" s="3" t="n"/>
+      <c r="I231" s="3" t="n"/>
+      <c r="J231" s="3" t="n"/>
+      <c r="K231" s="3" t="n"/>
+      <c r="L231" s="3" t="n"/>
+      <c r="M231" s="3" t="n"/>
+      <c r="N231" s="3" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="3" t="n"/>
+      <c r="B232" s="3" t="n"/>
+      <c r="C232" s="3" t="n"/>
+      <c r="D232" s="3" t="n"/>
+      <c r="E232" s="3" t="n"/>
+      <c r="F232" s="3" t="n"/>
+      <c r="G232" s="3" t="n"/>
+      <c r="H232" s="3" t="n"/>
+      <c r="I232" s="3" t="n"/>
+      <c r="J232" s="3" t="n"/>
+      <c r="K232" s="3" t="n"/>
+      <c r="L232" s="3" t="n"/>
+      <c r="M232" s="3" t="n"/>
+      <c r="N232" s="3" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="3" t="n"/>
+      <c r="B233" s="3" t="n"/>
+      <c r="C233" s="3" t="n"/>
+      <c r="D233" s="3" t="n"/>
+      <c r="E233" s="3" t="n"/>
+      <c r="F233" s="3" t="n"/>
+      <c r="G233" s="3" t="n"/>
+      <c r="H233" s="3" t="n"/>
+      <c r="I233" s="3" t="n"/>
+      <c r="J233" s="3" t="n"/>
+      <c r="K233" s="3" t="n"/>
+      <c r="L233" s="3" t="n"/>
+      <c r="M233" s="3" t="n"/>
+      <c r="N233" s="3" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="3" t="n"/>
+      <c r="B234" s="3" t="n"/>
+      <c r="C234" s="3" t="n"/>
+      <c r="D234" s="3" t="n"/>
+      <c r="E234" s="3" t="n"/>
+      <c r="F234" s="3" t="n"/>
+      <c r="G234" s="3" t="n"/>
+      <c r="H234" s="3" t="n"/>
+      <c r="I234" s="3" t="n"/>
+      <c r="J234" s="3" t="n"/>
+      <c r="K234" s="3" t="n"/>
+      <c r="L234" s="3" t="n"/>
+      <c r="M234" s="3" t="n"/>
+      <c r="N234" s="3" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="3" t="n"/>
+      <c r="B235" s="3" t="n"/>
+      <c r="C235" s="3" t="n"/>
+      <c r="D235" s="3" t="n"/>
+      <c r="E235" s="3" t="n"/>
+      <c r="F235" s="3" t="n"/>
+      <c r="G235" s="3" t="n"/>
+      <c r="H235" s="3" t="n"/>
+      <c r="I235" s="3" t="n"/>
+      <c r="J235" s="3" t="n"/>
+      <c r="K235" s="3" t="n"/>
+      <c r="L235" s="3" t="n"/>
+      <c r="M235" s="3" t="n"/>
+      <c r="N235" s="3" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="3" t="n"/>
+      <c r="B236" s="3" t="n"/>
+      <c r="C236" s="3" t="n"/>
+      <c r="D236" s="3" t="n"/>
+      <c r="E236" s="3" t="n"/>
+      <c r="F236" s="3" t="n"/>
+      <c r="G236" s="3" t="n"/>
+      <c r="H236" s="3" t="n"/>
+      <c r="I236" s="3" t="n"/>
+      <c r="J236" s="3" t="n"/>
+      <c r="K236" s="3" t="n"/>
+      <c r="L236" s="3" t="n"/>
+      <c r="M236" s="3" t="n"/>
+      <c r="N236" s="3" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="3" t="n"/>
+      <c r="B237" s="3" t="n"/>
+      <c r="C237" s="3" t="n"/>
+      <c r="D237" s="3" t="n"/>
+      <c r="E237" s="3" t="n"/>
+      <c r="F237" s="3" t="n"/>
+      <c r="G237" s="3" t="n"/>
+      <c r="H237" s="3" t="n"/>
+      <c r="I237" s="3" t="n"/>
+      <c r="J237" s="3" t="n"/>
+      <c r="K237" s="3" t="n"/>
+      <c r="L237" s="3" t="n"/>
+      <c r="M237" s="3" t="n"/>
+      <c r="N237" s="3" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="3" t="n"/>
+      <c r="B238" s="3" t="n"/>
+      <c r="C238" s="3" t="n"/>
+      <c r="D238" s="3" t="n"/>
+      <c r="E238" s="3" t="n"/>
+      <c r="F238" s="3" t="n"/>
+      <c r="G238" s="3" t="n"/>
+      <c r="H238" s="3" t="n"/>
+      <c r="I238" s="3" t="n"/>
+      <c r="J238" s="3" t="n"/>
+      <c r="K238" s="3" t="n"/>
+      <c r="L238" s="3" t="n"/>
+      <c r="M238" s="3" t="n"/>
+      <c r="N238" s="3" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="3" t="n"/>
+      <c r="B239" s="3" t="n"/>
+      <c r="C239" s="3" t="n"/>
+      <c r="D239" s="3" t="n"/>
+      <c r="E239" s="3" t="n"/>
+      <c r="F239" s="3" t="n"/>
+      <c r="G239" s="3" t="n"/>
+      <c r="H239" s="3" t="n"/>
+      <c r="I239" s="3" t="n"/>
+      <c r="J239" s="3" t="n"/>
+      <c r="K239" s="3" t="n"/>
+      <c r="L239" s="3" t="n"/>
+      <c r="M239" s="3" t="n"/>
+      <c r="N239" s="3" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="3" t="n"/>
+      <c r="B240" s="3" t="n"/>
+      <c r="C240" s="3" t="n"/>
+      <c r="D240" s="3" t="n"/>
+      <c r="E240" s="3" t="n"/>
+      <c r="F240" s="3" t="n"/>
+      <c r="G240" s="3" t="n"/>
+      <c r="H240" s="3" t="n"/>
+      <c r="I240" s="3" t="n"/>
+      <c r="J240" s="3" t="n"/>
+      <c r="K240" s="3" t="n"/>
+      <c r="L240" s="3" t="n"/>
+      <c r="M240" s="3" t="n"/>
+      <c r="N240" s="3" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="3" t="n"/>
+      <c r="B241" s="3" t="n"/>
+      <c r="C241" s="3" t="n"/>
+      <c r="D241" s="3" t="n"/>
+      <c r="E241" s="3" t="n"/>
+      <c r="F241" s="3" t="n"/>
+      <c r="G241" s="3" t="n"/>
+      <c r="H241" s="3" t="n"/>
+      <c r="I241" s="3" t="n"/>
+      <c r="J241" s="3" t="n"/>
+      <c r="K241" s="3" t="n"/>
+      <c r="L241" s="3" t="n"/>
+      <c r="M241" s="3" t="n"/>
+      <c r="N241" s="3" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="3" t="n"/>
+      <c r="B242" s="3" t="n"/>
+      <c r="C242" s="3" t="n"/>
+      <c r="D242" s="3" t="n"/>
+      <c r="E242" s="3" t="n"/>
+      <c r="F242" s="3" t="n"/>
+      <c r="G242" s="3" t="n"/>
+      <c r="H242" s="3" t="n"/>
+      <c r="I242" s="3" t="n"/>
+      <c r="J242" s="3" t="n"/>
+      <c r="K242" s="3" t="n"/>
+      <c r="L242" s="3" t="n"/>
+      <c r="M242" s="3" t="n"/>
+      <c r="N242" s="3" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="3" t="n"/>
+      <c r="B243" s="3" t="n"/>
+      <c r="C243" s="3" t="n"/>
+      <c r="D243" s="3" t="n"/>
+      <c r="E243" s="3" t="n"/>
+      <c r="F243" s="3" t="n"/>
+      <c r="G243" s="3" t="n"/>
+      <c r="H243" s="3" t="n"/>
+      <c r="I243" s="3" t="n"/>
+      <c r="J243" s="3" t="n"/>
+      <c r="K243" s="3" t="n"/>
+      <c r="L243" s="3" t="n"/>
+      <c r="M243" s="3" t="n"/>
+      <c r="N243" s="3" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="3" t="n"/>
+      <c r="B244" s="3" t="n"/>
+      <c r="C244" s="3" t="n"/>
+      <c r="D244" s="3" t="n"/>
+      <c r="E244" s="3" t="n"/>
+      <c r="F244" s="3" t="n"/>
+      <c r="G244" s="3" t="n"/>
+      <c r="H244" s="3" t="n"/>
+      <c r="I244" s="3" t="n"/>
+      <c r="J244" s="3" t="n"/>
+      <c r="K244" s="3" t="n"/>
+      <c r="L244" s="3" t="n"/>
+      <c r="M244" s="3" t="n"/>
+      <c r="N244" s="3" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="3" t="n"/>
+      <c r="B245" s="3" t="n"/>
+      <c r="C245" s="3" t="n"/>
+      <c r="D245" s="3" t="n"/>
+      <c r="E245" s="3" t="n"/>
+      <c r="F245" s="3" t="n"/>
+      <c r="G245" s="3" t="n"/>
+      <c r="H245" s="3" t="n"/>
+      <c r="I245" s="3" t="n"/>
+      <c r="J245" s="3" t="n"/>
+      <c r="K245" s="3" t="n"/>
+      <c r="L245" s="3" t="n"/>
+      <c r="M245" s="3" t="n"/>
+      <c r="N245" s="3" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="3" t="n"/>
+      <c r="B246" s="3" t="n"/>
+      <c r="C246" s="3" t="n"/>
+      <c r="D246" s="3" t="n"/>
+      <c r="E246" s="3" t="n"/>
+      <c r="F246" s="3" t="n"/>
+      <c r="G246" s="3" t="n"/>
+      <c r="H246" s="3" t="n"/>
+      <c r="I246" s="3" t="n"/>
+      <c r="J246" s="3" t="n"/>
+      <c r="K246" s="3" t="n"/>
+      <c r="L246" s="3" t="n"/>
+      <c r="M246" s="3" t="n"/>
+      <c r="N246" s="3" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="3" t="n"/>
+      <c r="B247" s="3" t="n"/>
+      <c r="C247" s="3" t="n"/>
+      <c r="D247" s="3" t="n"/>
+      <c r="E247" s="3" t="n"/>
+      <c r="F247" s="3" t="n"/>
+      <c r="G247" s="3" t="n"/>
+      <c r="H247" s="3" t="n"/>
+      <c r="I247" s="3" t="n"/>
+      <c r="J247" s="3" t="n"/>
+      <c r="K247" s="3" t="n"/>
+      <c r="L247" s="3" t="n"/>
+      <c r="M247" s="3" t="n"/>
+      <c r="N247" s="3" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="3" t="n"/>
+      <c r="B248" s="3" t="n"/>
+      <c r="C248" s="3" t="n"/>
+      <c r="D248" s="3" t="n"/>
+      <c r="E248" s="3" t="n"/>
+      <c r="F248" s="3" t="n"/>
+      <c r="G248" s="3" t="n"/>
+      <c r="H248" s="3" t="n"/>
+      <c r="I248" s="3" t="n"/>
+      <c r="J248" s="3" t="n"/>
+      <c r="K248" s="3" t="n"/>
+      <c r="L248" s="3" t="n"/>
+      <c r="M248" s="3" t="n"/>
+      <c r="N248" s="3" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="3" t="n"/>
+      <c r="B249" s="3" t="n"/>
+      <c r="C249" s="3" t="n"/>
+      <c r="D249" s="3" t="n"/>
+      <c r="E249" s="3" t="n"/>
+      <c r="F249" s="3" t="n"/>
+      <c r="G249" s="3" t="n"/>
+      <c r="H249" s="3" t="n"/>
+      <c r="I249" s="3" t="n"/>
+      <c r="J249" s="3" t="n"/>
+      <c r="K249" s="3" t="n"/>
+      <c r="L249" s="3" t="n"/>
+      <c r="M249" s="3" t="n"/>
+      <c r="N249" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/PRO database esercizi.xlsx
+++ b/PRO database esercizi.xlsx
@@ -4247,7 +4247,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3">
         <f>== SEZIONE 1: STATO ATTUALE DELLA PERIODIZZAZIONE ===</f>
@@ -4348,7 +4347,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12">
         <f>== SEZIONE 2: GUARDRAILS E REGOLE METODOLOGICHE INVIOLABILI ===</f>
@@ -4439,7 +4437,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21">
         <f>== SEZIONE 3: STATO DEI PATTERN MOTORI (STAFFETTA DEL CARICO) ===</f>
@@ -4548,7 +4545,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="A29">
         <f>== SEZIONE 4: CONTATORE DI UTILIZZO DEL CATALOGO ESERCIZI ===</f>
@@ -4572,7 +4568,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -25160,7 +25155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N249"/>
+  <dimension ref="A1:N299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25268,7 +25263,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr"/>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/98n_uL3E4m8</t>
+        </is>
+      </c>
       <c r="L2" s="4" t="inlineStr"/>
       <c r="M2" s="3" t="n"/>
       <c r="N2" s="3" t="n"/>
@@ -25314,7 +25313,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr"/>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/K-8y_B7Ie5M</t>
+        </is>
+      </c>
       <c r="L3" s="4" t="inlineStr"/>
       <c r="M3" s="3" t="n"/>
       <c r="N3" s="3" t="n"/>
@@ -25364,7 +25367,11 @@
           <t>rpe 8</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/D8z_q4N4KjU</t>
+        </is>
+      </c>
       <c r="L4" s="4" t="inlineStr"/>
       <c r="M4" s="3" t="n"/>
       <c r="N4" s="3" t="n"/>
@@ -25414,7 +25421,11 @@
           <t>rpe 8</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/mF8y3rD4xLQ</t>
+        </is>
+      </c>
       <c r="L5" s="4" t="inlineStr"/>
       <c r="M5" s="3" t="n"/>
       <c r="N5" s="3" t="n"/>
@@ -25514,7 +25525,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/y_4qB8E_F7c</t>
+        </is>
+      </c>
       <c r="L7" s="4" t="inlineStr"/>
       <c r="M7" s="3" t="n"/>
       <c r="N7" s="3" t="n"/>
@@ -25560,7 +25575,11 @@
           <t>circuito</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/G8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L8" s="4" t="inlineStr"/>
       <c r="M8" s="3" t="n"/>
       <c r="N8" s="3" t="n"/>
@@ -25606,7 +25625,11 @@
           <t>circuito</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Q8z_4uD8xLQ</t>
+        </is>
+      </c>
       <c r="L9" s="4" t="inlineStr"/>
       <c r="M9" s="3" t="n"/>
       <c r="N9" s="3" t="n"/>
@@ -25656,7 +25679,11 @@
           <t>circuito</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/M8z_4uD8xLQ</t>
+        </is>
+      </c>
       <c r="L10" s="4" t="inlineStr"/>
       <c r="M10" s="3" t="n"/>
       <c r="N10" s="3" t="n"/>
@@ -25702,7 +25729,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/F8y3rD4xLQ8</t>
+        </is>
+      </c>
       <c r="L11" s="5" t="inlineStr"/>
       <c r="M11" s="3" t="n"/>
       <c r="N11" s="3" t="n"/>
@@ -25748,7 +25779,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/H8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L12" s="5" t="inlineStr"/>
       <c r="M12" s="3" t="n"/>
       <c r="N12" s="3" t="n"/>
@@ -25798,7 +25833,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/J8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L13" s="5" t="inlineStr"/>
       <c r="M13" s="3" t="n"/>
       <c r="N13" s="3" t="n"/>
@@ -25848,7 +25887,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/K8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L14" s="5" t="inlineStr"/>
       <c r="M14" s="3" t="n"/>
       <c r="N14" s="3" t="n"/>
@@ -25898,7 +25941,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/L8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L15" s="5" t="inlineStr"/>
       <c r="M15" s="3" t="n"/>
       <c r="N15" s="3" t="n"/>
@@ -25948,7 +25995,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/N8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L16" s="5" t="inlineStr"/>
       <c r="M16" s="3" t="n"/>
       <c r="N16" s="3" t="n"/>
@@ -26052,7 +26103,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/P8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L18" s="5" t="inlineStr"/>
       <c r="M18" s="3" t="n"/>
       <c r="N18" s="3" t="n"/>
@@ -26098,7 +26153,11 @@
           <t>AMRAP 10'</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Q8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L19" s="5" t="inlineStr"/>
       <c r="M19" s="3" t="n"/>
       <c r="N19" s="3" t="n"/>
@@ -26144,7 +26203,11 @@
           <t>AMRAP 10'</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/R8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L20" s="5" t="inlineStr"/>
       <c r="M20" s="3" t="n"/>
       <c r="N20" s="3" t="n"/>
@@ -26190,7 +26253,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/98n_uL3E4m8</t>
+        </is>
+      </c>
       <c r="L21" s="4" t="inlineStr"/>
       <c r="M21" s="3" t="n"/>
       <c r="N21" s="3" t="n"/>
@@ -26236,7 +26303,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/K-8y_B7Ie5M</t>
+        </is>
+      </c>
       <c r="L22" s="4" t="inlineStr"/>
       <c r="M22" s="3" t="n"/>
       <c r="N22" s="3" t="n"/>
@@ -26286,7 +26357,11 @@
           <t>rpe 8</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/D8z_q4N4KjU</t>
+        </is>
+      </c>
       <c r="L23" s="4" t="inlineStr"/>
       <c r="M23" s="3" t="n"/>
       <c r="N23" s="3" t="n"/>
@@ -26336,7 +26411,11 @@
           <t>rpe 8</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr"/>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/mF8y3rD4xLQ</t>
+        </is>
+      </c>
       <c r="L24" s="4" t="inlineStr"/>
       <c r="M24" s="3" t="n"/>
       <c r="N24" s="3" t="n"/>
@@ -26436,7 +26515,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr"/>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/y_4qB8E_F7c</t>
+        </is>
+      </c>
       <c r="L26" s="4" t="inlineStr"/>
       <c r="M26" s="3" t="n"/>
       <c r="N26" s="3" t="n"/>
@@ -26482,7 +26565,11 @@
           <t>circuito</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/G8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L27" s="4" t="inlineStr"/>
       <c r="M27" s="3" t="n"/>
       <c r="N27" s="3" t="n"/>
@@ -26528,7 +26615,11 @@
           <t>circuito</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr"/>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Q8z_4uD8xLQ</t>
+        </is>
+      </c>
       <c r="L28" s="4" t="inlineStr"/>
       <c r="M28" s="3" t="n"/>
       <c r="N28" s="3" t="n"/>
@@ -26578,7 +26669,11 @@
           <t>circuito</t>
         </is>
       </c>
-      <c r="K29" s="4" t="inlineStr"/>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/M8z_4uD8xLQ</t>
+        </is>
+      </c>
       <c r="L29" s="4" t="inlineStr"/>
       <c r="M29" s="3" t="n"/>
       <c r="N29" s="3" t="n"/>
@@ -26624,7 +26719,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/F8y3rD4xLQ8</t>
+        </is>
+      </c>
       <c r="L30" s="5" t="inlineStr"/>
       <c r="M30" s="3" t="n"/>
       <c r="N30" s="3" t="n"/>
@@ -26670,7 +26769,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/H8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L31" s="5" t="inlineStr"/>
       <c r="M31" s="3" t="n"/>
       <c r="N31" s="3" t="n"/>
@@ -26720,7 +26823,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/J8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L32" s="5" t="inlineStr"/>
       <c r="M32" s="3" t="n"/>
       <c r="N32" s="3" t="n"/>
@@ -26770,7 +26877,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr"/>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/K8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L33" s="5" t="inlineStr"/>
       <c r="M33" s="3" t="n"/>
       <c r="N33" s="3" t="n"/>
@@ -26820,7 +26931,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K34" s="5" t="inlineStr"/>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/L8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L34" s="5" t="inlineStr"/>
       <c r="M34" s="3" t="n"/>
       <c r="N34" s="3" t="n"/>
@@ -26870,7 +26985,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K35" s="5" t="inlineStr"/>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/N8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L35" s="5" t="inlineStr"/>
       <c r="M35" s="3" t="n"/>
       <c r="N35" s="3" t="n"/>
@@ -26974,7 +27093,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K37" s="5" t="inlineStr"/>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/P8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L37" s="5" t="inlineStr"/>
       <c r="M37" s="3" t="n"/>
       <c r="N37" s="3" t="n"/>
@@ -27020,7 +27143,11 @@
           <t>AMRAP 10'</t>
         </is>
       </c>
-      <c r="K38" s="5" t="inlineStr"/>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Q8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L38" s="5" t="inlineStr"/>
       <c r="M38" s="3" t="n"/>
       <c r="N38" s="3" t="n"/>
@@ -27066,7 +27193,11 @@
           <t>AMRAP 10'</t>
         </is>
       </c>
-      <c r="K39" s="5" t="inlineStr"/>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/R8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L39" s="5" t="inlineStr"/>
       <c r="M39" s="3" t="n"/>
       <c r="N39" s="3" t="n"/>
@@ -27112,7 +27243,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K40" s="4" t="inlineStr"/>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/98n_uL3E4m8</t>
+        </is>
+      </c>
       <c r="L40" s="4" t="inlineStr"/>
       <c r="M40" s="3" t="n"/>
       <c r="N40" s="3" t="n"/>
@@ -27158,7 +27293,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K41" s="4" t="inlineStr"/>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/K-8y_B7Ie5M</t>
+        </is>
+      </c>
       <c r="L41" s="4" t="inlineStr"/>
       <c r="M41" s="3" t="n"/>
       <c r="N41" s="3" t="n"/>
@@ -27208,7 +27347,11 @@
           <t>rpe 8</t>
         </is>
       </c>
-      <c r="K42" s="4" t="inlineStr"/>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/D8z_q4N4KjU</t>
+        </is>
+      </c>
       <c r="L42" s="4" t="inlineStr"/>
       <c r="M42" s="3" t="n"/>
       <c r="N42" s="3" t="n"/>
@@ -27258,7 +27401,11 @@
           <t>rpe 8</t>
         </is>
       </c>
-      <c r="K43" s="4" t="inlineStr"/>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/mF8y3rD4xLQ</t>
+        </is>
+      </c>
       <c r="L43" s="4" t="inlineStr"/>
       <c r="M43" s="3" t="n"/>
       <c r="N43" s="3" t="n"/>
@@ -27358,7 +27505,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K45" s="4" t="inlineStr"/>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/y_4qB8E_F7c</t>
+        </is>
+      </c>
       <c r="L45" s="4" t="inlineStr"/>
       <c r="M45" s="3" t="n"/>
       <c r="N45" s="3" t="n"/>
@@ -27404,7 +27555,11 @@
           <t>circuito</t>
         </is>
       </c>
-      <c r="K46" s="4" t="inlineStr"/>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/G8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L46" s="4" t="inlineStr"/>
       <c r="M46" s="3" t="n"/>
       <c r="N46" s="3" t="n"/>
@@ -27450,7 +27605,11 @@
           <t>circuito</t>
         </is>
       </c>
-      <c r="K47" s="4" t="inlineStr"/>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Q8z_4uD8xLQ</t>
+        </is>
+      </c>
       <c r="L47" s="4" t="inlineStr"/>
       <c r="M47" s="3" t="n"/>
       <c r="N47" s="3" t="n"/>
@@ -27500,7 +27659,11 @@
           <t>circuito</t>
         </is>
       </c>
-      <c r="K48" s="4" t="inlineStr"/>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/M8z_4uD8xLQ</t>
+        </is>
+      </c>
       <c r="L48" s="4" t="inlineStr"/>
       <c r="M48" s="3" t="n"/>
       <c r="N48" s="3" t="n"/>
@@ -27546,7 +27709,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K49" s="5" t="inlineStr"/>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/F8y3rD4xLQ8</t>
+        </is>
+      </c>
       <c r="L49" s="5" t="inlineStr"/>
       <c r="M49" s="3" t="n"/>
       <c r="N49" s="3" t="n"/>
@@ -27592,7 +27759,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K50" s="5" t="inlineStr"/>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/H8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L50" s="5" t="inlineStr"/>
       <c r="M50" s="3" t="n"/>
       <c r="N50" s="3" t="n"/>
@@ -27642,7 +27813,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K51" s="5" t="inlineStr"/>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/J8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L51" s="5" t="inlineStr"/>
       <c r="M51" s="3" t="n"/>
       <c r="N51" s="3" t="n"/>
@@ -27692,7 +27867,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K52" s="5" t="inlineStr"/>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/K8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L52" s="5" t="inlineStr"/>
       <c r="M52" s="3" t="n"/>
       <c r="N52" s="3" t="n"/>
@@ -27742,7 +27921,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K53" s="5" t="inlineStr"/>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/L8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L53" s="5" t="inlineStr"/>
       <c r="M53" s="3" t="n"/>
       <c r="N53" s="3" t="n"/>
@@ -27792,7 +27975,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K54" s="5" t="inlineStr"/>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/N8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L54" s="5" t="inlineStr"/>
       <c r="M54" s="3" t="n"/>
       <c r="N54" s="3" t="n"/>
@@ -27896,7 +28083,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K56" s="5" t="inlineStr"/>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/P8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L56" s="5" t="inlineStr"/>
       <c r="M56" s="3" t="n"/>
       <c r="N56" s="3" t="n"/>
@@ -27942,7 +28133,11 @@
           <t>AMRAP 10'</t>
         </is>
       </c>
-      <c r="K57" s="5" t="inlineStr"/>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Q8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L57" s="5" t="inlineStr"/>
       <c r="M57" s="3" t="n"/>
       <c r="N57" s="3" t="n"/>
@@ -27988,7 +28183,11 @@
           <t>AMRAP 10'</t>
         </is>
       </c>
-      <c r="K58" s="6" t="inlineStr"/>
+      <c r="K58" s="6" t="inlineStr">
+        <is>
+          <t>https://youtu.be/R8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L58" s="6" t="inlineStr"/>
       <c r="M58" s="3" t="n"/>
       <c r="N58" s="3" t="n"/>
@@ -28034,7 +28233,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K59" s="4" t="inlineStr"/>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/S8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L59" s="4" t="inlineStr"/>
       <c r="M59" s="3" t="n"/>
       <c r="N59" s="3" t="n"/>
@@ -28084,7 +28287,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K60" s="4" t="inlineStr"/>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/T8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L60" s="4" t="inlineStr"/>
       <c r="M60" s="3" t="n"/>
       <c r="N60" s="3" t="n"/>
@@ -28188,7 +28395,11 @@
           <t>jump set | RPE 8</t>
         </is>
       </c>
-      <c r="K62" s="4" t="inlineStr"/>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/y_4qB8E_F7c</t>
+        </is>
+      </c>
       <c r="L62" s="4" t="inlineStr"/>
       <c r="M62" s="3" t="n"/>
       <c r="N62" s="3" t="n"/>
@@ -28288,7 +28499,11 @@
           <t>circuito (4 round)</t>
         </is>
       </c>
-      <c r="K64" s="4" t="inlineStr"/>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/U8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L64" s="4" t="inlineStr"/>
       <c r="M64" s="3" t="n"/>
       <c r="N64" s="3" t="n"/>
@@ -28334,7 +28549,11 @@
           <t>circuito (4 round)</t>
         </is>
       </c>
-      <c r="K65" s="4" t="inlineStr"/>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/V8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L65" s="4" t="inlineStr"/>
       <c r="M65" s="3" t="n"/>
       <c r="N65" s="3" t="n"/>
@@ -28384,7 +28603,11 @@
           <t>circuito (4 round)</t>
         </is>
       </c>
-      <c r="K66" s="4" t="inlineStr"/>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/7n-hAJAXoYU</t>
+        </is>
+      </c>
       <c r="L66" s="4" t="inlineStr"/>
       <c r="M66" s="3" t="n"/>
       <c r="N66" s="3" t="n"/>
@@ -28430,7 +28653,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K67" s="5" t="inlineStr"/>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/W8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L67" s="5" t="inlineStr"/>
       <c r="M67" s="3" t="n"/>
       <c r="N67" s="3" t="n"/>
@@ -28480,7 +28707,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K68" s="5" t="inlineStr"/>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/X8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L68" s="5" t="inlineStr"/>
       <c r="M68" s="3" t="n"/>
       <c r="N68" s="3" t="n"/>
@@ -28530,7 +28761,11 @@
           <t>jump set | RPE 8</t>
         </is>
       </c>
-      <c r="K69" s="5" t="inlineStr"/>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Y8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L69" s="5" t="inlineStr"/>
       <c r="M69" s="3" t="n"/>
       <c r="N69" s="3" t="n"/>
@@ -28580,7 +28815,11 @@
           <t>jump set | RPE 8</t>
         </is>
       </c>
-      <c r="K70" s="5" t="inlineStr"/>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Z8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L70" s="5" t="inlineStr"/>
       <c r="M70" s="3" t="n"/>
       <c r="N70" s="3" t="n"/>
@@ -28630,7 +28869,11 @@
           <t>jump set | RPE 8</t>
         </is>
       </c>
-      <c r="K71" s="5" t="inlineStr"/>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/a8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L71" s="5" t="inlineStr"/>
       <c r="M71" s="3" t="n"/>
       <c r="N71" s="3" t="n"/>
@@ -28680,7 +28923,11 @@
           <t>jump set | RPE 8</t>
         </is>
       </c>
-      <c r="K72" s="5" t="inlineStr"/>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/N8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L72" s="5" t="inlineStr"/>
       <c r="M72" s="3" t="n"/>
       <c r="N72" s="3" t="n"/>
@@ -28726,7 +28973,11 @@
           <t>AMRAP 15'</t>
         </is>
       </c>
-      <c r="K73" s="5" t="inlineStr"/>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/b8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L73" s="5" t="inlineStr"/>
       <c r="M73" s="3" t="n"/>
       <c r="N73" s="3" t="n"/>
@@ -28772,7 +29023,11 @@
           <t>AMRAP 15'</t>
         </is>
       </c>
-      <c r="K74" s="5" t="inlineStr"/>
+      <c r="K74" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/P8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L74" s="5" t="inlineStr"/>
       <c r="M74" s="3" t="n"/>
       <c r="N74" s="3" t="n"/>
@@ -28818,7 +29073,11 @@
           <t>AMRAP 15'</t>
         </is>
       </c>
-      <c r="K75" s="5" t="inlineStr"/>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/c8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L75" s="5" t="inlineStr"/>
       <c r="M75" s="3" t="n"/>
       <c r="N75" s="3" t="n"/>
@@ -28864,7 +29123,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K76" s="4" t="inlineStr"/>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/S8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L76" s="4" t="inlineStr"/>
       <c r="M76" s="3" t="n"/>
       <c r="N76" s="3" t="n"/>
@@ -28914,7 +29177,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K77" s="4" t="inlineStr"/>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/T8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L77" s="4" t="inlineStr"/>
       <c r="M77" s="3" t="n"/>
       <c r="N77" s="3" t="n"/>
@@ -29018,7 +29285,11 @@
           <t>jump set | RPE 8</t>
         </is>
       </c>
-      <c r="K79" s="4" t="inlineStr"/>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/y_4qB8E_F7c</t>
+        </is>
+      </c>
       <c r="L79" s="4" t="inlineStr"/>
       <c r="M79" s="3" t="n"/>
       <c r="N79" s="3" t="n"/>
@@ -29118,7 +29389,11 @@
           <t>circuito (4 round)</t>
         </is>
       </c>
-      <c r="K81" s="4" t="inlineStr"/>
+      <c r="K81" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/U8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L81" s="4" t="inlineStr"/>
       <c r="M81" s="3" t="n"/>
       <c r="N81" s="3" t="n"/>
@@ -29164,7 +29439,11 @@
           <t>circuito (4 round)</t>
         </is>
       </c>
-      <c r="K82" s="4" t="inlineStr"/>
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/V8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L82" s="4" t="inlineStr"/>
       <c r="M82" s="3" t="n"/>
       <c r="N82" s="3" t="n"/>
@@ -29214,7 +29493,11 @@
           <t>circuito (4 round)</t>
         </is>
       </c>
-      <c r="K83" s="4" t="inlineStr"/>
+      <c r="K83" s="4" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/7n-hAJAXoYU</t>
+        </is>
+      </c>
       <c r="L83" s="4" t="inlineStr"/>
       <c r="M83" s="3" t="n"/>
       <c r="N83" s="3" t="n"/>
@@ -29260,7 +29543,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K84" s="5" t="inlineStr"/>
+      <c r="K84" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/W8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L84" s="5" t="inlineStr"/>
       <c r="M84" s="3" t="n"/>
       <c r="N84" s="3" t="n"/>
@@ -29310,7 +29597,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K85" s="5" t="inlineStr"/>
+      <c r="K85" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/X8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L85" s="5" t="inlineStr"/>
       <c r="M85" s="3" t="n"/>
       <c r="N85" s="3" t="n"/>
@@ -29360,7 +29651,11 @@
           <t>jump set | RPE 8</t>
         </is>
       </c>
-      <c r="K86" s="5" t="inlineStr"/>
+      <c r="K86" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Y8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L86" s="5" t="inlineStr"/>
       <c r="M86" s="3" t="n"/>
       <c r="N86" s="3" t="n"/>
@@ -29410,7 +29705,11 @@
           <t>jump set | RPE 8</t>
         </is>
       </c>
-      <c r="K87" s="5" t="inlineStr"/>
+      <c r="K87" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Z8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L87" s="5" t="inlineStr"/>
       <c r="M87" s="3" t="n"/>
       <c r="N87" s="3" t="n"/>
@@ -29460,7 +29759,11 @@
           <t>jump set | RPE 8</t>
         </is>
       </c>
-      <c r="K88" s="5" t="inlineStr"/>
+      <c r="K88" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/a8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L88" s="5" t="inlineStr"/>
       <c r="M88" s="3" t="n"/>
       <c r="N88" s="3" t="n"/>
@@ -29510,7 +29813,11 @@
           <t>jump set | RPE 8</t>
         </is>
       </c>
-      <c r="K89" s="5" t="inlineStr"/>
+      <c r="K89" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/N8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L89" s="5" t="inlineStr"/>
       <c r="M89" s="3" t="n"/>
       <c r="N89" s="3" t="n"/>
@@ -29556,7 +29863,11 @@
           <t>AMRAP 15'</t>
         </is>
       </c>
-      <c r="K90" s="5" t="inlineStr"/>
+      <c r="K90" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/b8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L90" s="5" t="inlineStr"/>
       <c r="M90" s="3" t="n"/>
       <c r="N90" s="3" t="n"/>
@@ -29602,7 +29913,11 @@
           <t>AMRAP 15'</t>
         </is>
       </c>
-      <c r="K91" s="5" t="inlineStr"/>
+      <c r="K91" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/P8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L91" s="5" t="inlineStr"/>
       <c r="M91" s="3" t="n"/>
       <c r="N91" s="3" t="n"/>
@@ -29648,7 +29963,11 @@
           <t>AMRAP 15'</t>
         </is>
       </c>
-      <c r="K92" s="5" t="inlineStr"/>
+      <c r="K92" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/c8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L92" s="5" t="inlineStr"/>
       <c r="M92" s="3" t="n"/>
       <c r="N92" s="3" t="n"/>
@@ -29694,7 +30013,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K93" s="4" t="inlineStr"/>
+      <c r="K93" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/S8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L93" s="4" t="inlineStr"/>
       <c r="M93" s="3" t="n"/>
       <c r="N93" s="3" t="n"/>
@@ -29744,7 +30067,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K94" s="4" t="inlineStr"/>
+      <c r="K94" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/T8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L94" s="4" t="inlineStr"/>
       <c r="M94" s="3" t="n"/>
       <c r="N94" s="3" t="n"/>
@@ -29848,7 +30175,11 @@
           <t>jump set | RPE 8</t>
         </is>
       </c>
-      <c r="K96" s="4" t="inlineStr"/>
+      <c r="K96" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/y_4qB8E_F7c</t>
+        </is>
+      </c>
       <c r="L96" s="4" t="inlineStr"/>
       <c r="M96" s="3" t="n"/>
       <c r="N96" s="3" t="n"/>
@@ -29948,7 +30279,11 @@
           <t>circuito (4 round)</t>
         </is>
       </c>
-      <c r="K98" s="4" t="inlineStr"/>
+      <c r="K98" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/U8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L98" s="4" t="inlineStr"/>
       <c r="M98" s="3" t="n"/>
       <c r="N98" s="3" t="n"/>
@@ -29994,7 +30329,11 @@
           <t>circuito (4 round)</t>
         </is>
       </c>
-      <c r="K99" s="4" t="inlineStr"/>
+      <c r="K99" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/V8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L99" s="4" t="inlineStr"/>
       <c r="M99" s="3" t="n"/>
       <c r="N99" s="3" t="n"/>
@@ -30044,7 +30383,11 @@
           <t>circuito (4 round)</t>
         </is>
       </c>
-      <c r="K100" s="4" t="inlineStr"/>
+      <c r="K100" s="4" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/7n-hAJAXoYU</t>
+        </is>
+      </c>
       <c r="L100" s="4" t="inlineStr"/>
       <c r="M100" s="3" t="n"/>
       <c r="N100" s="3" t="n"/>
@@ -30090,7 +30433,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K101" s="5" t="inlineStr"/>
+      <c r="K101" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/W8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L101" s="5" t="inlineStr"/>
       <c r="M101" s="3" t="n"/>
       <c r="N101" s="3" t="n"/>
@@ -30140,7 +30487,11 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K102" s="5" t="inlineStr"/>
+      <c r="K102" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/X8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L102" s="5" t="inlineStr"/>
       <c r="M102" s="3" t="n"/>
       <c r="N102" s="3" t="n"/>
@@ -30190,7 +30541,11 @@
           <t>jump set | RPE 8</t>
         </is>
       </c>
-      <c r="K103" s="5" t="inlineStr"/>
+      <c r="K103" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Y8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L103" s="5" t="inlineStr"/>
       <c r="M103" s="3" t="n"/>
       <c r="N103" s="3" t="n"/>
@@ -30240,7 +30595,11 @@
           <t>jump set | RPE 8</t>
         </is>
       </c>
-      <c r="K104" s="5" t="inlineStr"/>
+      <c r="K104" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Z8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L104" s="5" t="inlineStr"/>
       <c r="M104" s="3" t="n"/>
       <c r="N104" s="3" t="n"/>
@@ -30290,7 +30649,11 @@
           <t>jump set | RPE 8</t>
         </is>
       </c>
-      <c r="K105" s="5" t="inlineStr"/>
+      <c r="K105" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/a8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L105" s="5" t="inlineStr"/>
       <c r="M105" s="3" t="n"/>
       <c r="N105" s="3" t="n"/>
@@ -30340,7 +30703,11 @@
           <t>jump set | RPE 8</t>
         </is>
       </c>
-      <c r="K106" s="5" t="inlineStr"/>
+      <c r="K106" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/N8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L106" s="5" t="inlineStr"/>
       <c r="M106" s="3" t="n"/>
       <c r="N106" s="3" t="n"/>
@@ -30386,7 +30753,11 @@
           <t>AMRAP 15'</t>
         </is>
       </c>
-      <c r="K107" s="5" t="inlineStr"/>
+      <c r="K107" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/b8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L107" s="5" t="inlineStr"/>
       <c r="M107" s="3" t="n"/>
       <c r="N107" s="3" t="n"/>
@@ -30432,7 +30803,11 @@
           <t>AMRAP 15'</t>
         </is>
       </c>
-      <c r="K108" s="5" t="inlineStr"/>
+      <c r="K108" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/P8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L108" s="5" t="inlineStr"/>
       <c r="M108" s="3" t="n"/>
       <c r="N108" s="3" t="n"/>
@@ -30478,7 +30853,11 @@
           <t>AMRAP 15'</t>
         </is>
       </c>
-      <c r="K109" s="6" t="inlineStr"/>
+      <c r="K109" s="6" t="inlineStr">
+        <is>
+          <t>https://youtu.be/c8z_4uQ4x9U</t>
+        </is>
+      </c>
       <c r="L109" s="6" t="inlineStr"/>
       <c r="M109" s="3" t="n"/>
       <c r="N109" s="3" t="n"/>
@@ -33118,818 +33497,2648 @@
       <c r="N160" s="3" t="n"/>
     </row>
     <row r="161">
-      <c r="A161" s="3" t="n"/>
-      <c r="B161" s="3" t="n"/>
-      <c r="C161" s="3" t="n"/>
-      <c r="D161" s="3" t="n"/>
-      <c r="E161" s="3" t="n"/>
-      <c r="F161" s="3" t="n"/>
-      <c r="G161" s="3" t="n"/>
-      <c r="H161" s="3" t="n"/>
-      <c r="I161" s="3" t="n"/>
-      <c r="J161" s="3" t="n"/>
-      <c r="K161" s="3" t="n"/>
-      <c r="L161" s="3" t="n"/>
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t>19 allenamento A</t>
+        </is>
+      </c>
+      <c r="D161" s="4" t="inlineStr">
+        <is>
+          <t>1a</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="n">
+        <v>158</v>
+      </c>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>Bat around the head 90° e 180°</t>
+        </is>
+      </c>
+      <c r="G161" s="4" t="inlineStr">
+        <is>
+          <t>3x8+8</t>
+        </is>
+      </c>
+      <c r="H161" s="4" t="inlineStr"/>
+      <c r="I161" s="4" t="inlineStr"/>
+      <c r="J161" s="4" t="inlineStr">
+        <is>
+          <t>jump set</t>
+        </is>
+      </c>
+      <c r="K161" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/INNpiEJL9As?si=7-xSjR1LJL__jzU8</t>
+        </is>
+      </c>
+      <c r="L161" s="4" t="inlineStr"/>
       <c r="M161" s="3" t="n"/>
       <c r="N161" s="3" t="n"/>
     </row>
     <row r="162">
-      <c r="A162" s="3" t="n"/>
-      <c r="B162" s="3" t="n"/>
-      <c r="C162" s="3" t="n"/>
-      <c r="D162" s="3" t="n"/>
-      <c r="E162" s="3" t="n"/>
-      <c r="F162" s="3" t="n"/>
-      <c r="G162" s="3" t="n"/>
-      <c r="H162" s="3" t="n"/>
-      <c r="I162" s="3" t="n"/>
-      <c r="J162" s="3" t="n"/>
-      <c r="K162" s="3" t="n"/>
-      <c r="L162" s="3" t="n"/>
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t>19 allenamento A</t>
+        </is>
+      </c>
+      <c r="D162" s="4" t="inlineStr">
+        <is>
+          <t>1b</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="F162" s="4" t="inlineStr">
+        <is>
+          <t>Side move</t>
+        </is>
+      </c>
+      <c r="G162" s="4" t="inlineStr">
+        <is>
+          <t>3x10+10</t>
+        </is>
+      </c>
+      <c r="H162" s="4" t="inlineStr">
+        <is>
+          <t>45"</t>
+        </is>
+      </c>
+      <c r="I162" s="4" t="inlineStr"/>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>jump set</t>
+        </is>
+      </c>
+      <c r="K162" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/ISkSG5yXhrU?si=aQYlqWHqyaE5nWL_</t>
+        </is>
+      </c>
+      <c r="L162" s="4" t="inlineStr"/>
       <c r="M162" s="3" t="n"/>
       <c r="N162" s="3" t="n"/>
     </row>
     <row r="163">
-      <c r="A163" s="3" t="n"/>
-      <c r="B163" s="3" t="n"/>
-      <c r="C163" s="3" t="n"/>
-      <c r="D163" s="3" t="n"/>
-      <c r="E163" s="3" t="n"/>
-      <c r="F163" s="3" t="n"/>
-      <c r="G163" s="3" t="n"/>
-      <c r="H163" s="3" t="n"/>
-      <c r="I163" s="3" t="n"/>
-      <c r="J163" s="3" t="n"/>
-      <c r="K163" s="3" t="n"/>
-      <c r="L163" s="3" t="n"/>
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>19 allenamento A</t>
+        </is>
+      </c>
+      <c r="D163" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E163" s="4" t="n">
+        <v>127</v>
+      </c>
+      <c r="F163" s="4" t="inlineStr">
+        <is>
+          <t>COMBO: Landmine clean ALT. SCRD T/GO</t>
+        </is>
+      </c>
+      <c r="G163" s="4" t="inlineStr">
+        <is>
+          <t>4x6+6</t>
+        </is>
+      </c>
+      <c r="H163" s="4" t="inlineStr">
+        <is>
+          <t>RBS 60"</t>
+        </is>
+      </c>
+      <c r="I163" s="4" t="inlineStr"/>
+      <c r="J163" s="4" t="inlineStr">
+        <is>
+          <t>RPE 8</t>
+        </is>
+      </c>
+      <c r="K163" s="4" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/Zd7CQkHhnSo</t>
+        </is>
+      </c>
+      <c r="L163" s="4" t="inlineStr"/>
       <c r="M163" s="3" t="n"/>
       <c r="N163" s="3" t="n"/>
     </row>
     <row r="164">
-      <c r="A164" s="3" t="n"/>
-      <c r="B164" s="3" t="n"/>
-      <c r="C164" s="3" t="n"/>
-      <c r="D164" s="3" t="n"/>
-      <c r="E164" s="3" t="n"/>
-      <c r="F164" s="3" t="n"/>
-      <c r="G164" s="3" t="n"/>
-      <c r="H164" s="3" t="n"/>
-      <c r="I164" s="3" t="n"/>
-      <c r="J164" s="3" t="n"/>
-      <c r="K164" s="3" t="n"/>
-      <c r="L164" s="3" t="n"/>
+      <c r="A164" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C164" s="4" t="inlineStr">
+        <is>
+          <t>19 allenamento A</t>
+        </is>
+      </c>
+      <c r="D164" s="4" t="inlineStr">
+        <is>
+          <t>3a</t>
+        </is>
+      </c>
+      <c r="E164" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F164" s="4" t="inlineStr">
+        <is>
+          <t>Coiled Cable ROW</t>
+        </is>
+      </c>
+      <c r="G164" s="4" t="inlineStr">
+        <is>
+          <t>4x8+8</t>
+        </is>
+      </c>
+      <c r="H164" s="4" t="inlineStr"/>
+      <c r="I164" s="4" t="inlineStr"/>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>jump set | RPE 8</t>
+        </is>
+      </c>
+      <c r="K164" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/OdhNUbqajmM</t>
+        </is>
+      </c>
+      <c r="L164" s="4" t="inlineStr"/>
       <c r="M164" s="3" t="n"/>
       <c r="N164" s="3" t="n"/>
     </row>
     <row r="165">
-      <c r="A165" s="3" t="n"/>
-      <c r="B165" s="3" t="n"/>
-      <c r="C165" s="3" t="n"/>
-      <c r="D165" s="3" t="n"/>
-      <c r="E165" s="3" t="n"/>
-      <c r="F165" s="3" t="n"/>
-      <c r="G165" s="3" t="n"/>
-      <c r="H165" s="3" t="n"/>
-      <c r="I165" s="3" t="n"/>
-      <c r="J165" s="3" t="n"/>
-      <c r="K165" s="3" t="n"/>
-      <c r="L165" s="3" t="n"/>
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t>19 allenamento A</t>
+        </is>
+      </c>
+      <c r="D165" s="4" t="inlineStr">
+        <is>
+          <t>3b</t>
+        </is>
+      </c>
+      <c r="E165" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="F165" s="4" t="inlineStr">
+        <is>
+          <t>Kneeling Transition over head press</t>
+        </is>
+      </c>
+      <c r="G165" s="4" t="inlineStr">
+        <is>
+          <t>4x8+8</t>
+        </is>
+      </c>
+      <c r="H165" s="4" t="inlineStr">
+        <is>
+          <t>60"</t>
+        </is>
+      </c>
+      <c r="I165" s="4" t="inlineStr"/>
+      <c r="J165" s="4" t="inlineStr">
+        <is>
+          <t>jump set | RPE 8</t>
+        </is>
+      </c>
+      <c r="K165" s="4" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/Y-2AeFnKQLY</t>
+        </is>
+      </c>
+      <c r="L165" s="4" t="inlineStr"/>
       <c r="M165" s="3" t="n"/>
       <c r="N165" s="3" t="n"/>
     </row>
     <row r="166">
-      <c r="A166" s="3" t="n"/>
-      <c r="B166" s="3" t="n"/>
-      <c r="C166" s="3" t="n"/>
-      <c r="D166" s="3" t="n"/>
-      <c r="E166" s="3" t="n"/>
-      <c r="F166" s="3" t="n"/>
-      <c r="G166" s="3" t="n"/>
-      <c r="H166" s="3" t="n"/>
-      <c r="I166" s="3" t="n"/>
-      <c r="J166" s="3" t="n"/>
-      <c r="K166" s="3" t="n"/>
-      <c r="L166" s="3" t="n"/>
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B166" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C166" s="4" t="inlineStr">
+        <is>
+          <t>19 allenamento A</t>
+        </is>
+      </c>
+      <c r="D166" s="4" t="inlineStr">
+        <is>
+          <t>4a</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="n">
+        <v>201</v>
+      </c>
+      <c r="F166" s="4" t="inlineStr">
+        <is>
+          <t>Step Up esplosivo alternato</t>
+        </is>
+      </c>
+      <c r="G166" s="4" t="inlineStr">
+        <is>
+          <t>3x8+8</t>
+        </is>
+      </c>
+      <c r="H166" s="4" t="inlineStr"/>
+      <c r="I166" s="4" t="inlineStr"/>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>circuito (3 round)</t>
+        </is>
+      </c>
+      <c r="K166" s="4" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/bAH_uySHG0c?si=H7r8TS-7k3vxrCRf</t>
+        </is>
+      </c>
+      <c r="L166" s="4" t="inlineStr"/>
       <c r="M166" s="3" t="n"/>
       <c r="N166" s="3" t="n"/>
     </row>
     <row r="167">
-      <c r="A167" s="3" t="n"/>
-      <c r="B167" s="3" t="n"/>
-      <c r="C167" s="3" t="n"/>
-      <c r="D167" s="3" t="n"/>
-      <c r="E167" s="3" t="n"/>
-      <c r="F167" s="3" t="n"/>
-      <c r="G167" s="3" t="n"/>
-      <c r="H167" s="3" t="n"/>
-      <c r="I167" s="3" t="n"/>
-      <c r="J167" s="3" t="n"/>
-      <c r="K167" s="3" t="n"/>
-      <c r="L167" s="3" t="n"/>
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>19 allenamento A</t>
+        </is>
+      </c>
+      <c r="D167" s="4" t="inlineStr">
+        <is>
+          <t>4b</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="n">
+        <v>231</v>
+      </c>
+      <c r="F167" s="4" t="inlineStr">
+        <is>
+          <t>Banded hoock</t>
+        </is>
+      </c>
+      <c r="G167" s="4" t="inlineStr">
+        <is>
+          <t>3x10+10</t>
+        </is>
+      </c>
+      <c r="H167" s="4" t="inlineStr"/>
+      <c r="I167" s="4" t="inlineStr"/>
+      <c r="J167" s="4" t="inlineStr">
+        <is>
+          <t>circuito (3 round)</t>
+        </is>
+      </c>
+      <c r="K167" s="4" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/jEOtxSBwhCU</t>
+        </is>
+      </c>
+      <c r="L167" s="4" t="inlineStr"/>
       <c r="M167" s="3" t="n"/>
       <c r="N167" s="3" t="n"/>
     </row>
     <row r="168">
-      <c r="A168" s="3" t="n"/>
-      <c r="B168" s="3" t="n"/>
-      <c r="C168" s="3" t="n"/>
-      <c r="D168" s="3" t="n"/>
-      <c r="E168" s="3" t="n"/>
-      <c r="F168" s="3" t="n"/>
-      <c r="G168" s="3" t="n"/>
-      <c r="H168" s="3" t="n"/>
-      <c r="I168" s="3" t="n"/>
-      <c r="J168" s="3" t="n"/>
-      <c r="K168" s="3" t="n"/>
-      <c r="L168" s="3" t="n"/>
+      <c r="A168" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="inlineStr">
+        <is>
+          <t>19 allenamento A</t>
+        </is>
+      </c>
+      <c r="D168" s="4" t="inlineStr">
+        <is>
+          <t>4c</t>
+        </is>
+      </c>
+      <c r="E168" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F168" s="4" t="inlineStr">
+        <is>
+          <t>skierg pagaia mono</t>
+        </is>
+      </c>
+      <c r="G168" s="4" t="inlineStr">
+        <is>
+          <t>3x30"+30"</t>
+        </is>
+      </c>
+      <c r="H168" s="4" t="inlineStr">
+        <is>
+          <t>60"</t>
+        </is>
+      </c>
+      <c r="I168" s="4" t="inlineStr"/>
+      <c r="J168" s="4" t="inlineStr">
+        <is>
+          <t>circuito (3 round)</t>
+        </is>
+      </c>
+      <c r="K168" s="4" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/7n-hAJAXoYU</t>
+        </is>
+      </c>
+      <c r="L168" s="4" t="inlineStr"/>
       <c r="M168" s="3" t="n"/>
       <c r="N168" s="3" t="n"/>
     </row>
     <row r="169">
-      <c r="A169" s="3" t="n"/>
-      <c r="B169" s="3" t="n"/>
-      <c r="C169" s="3" t="n"/>
-      <c r="D169" s="3" t="n"/>
-      <c r="E169" s="3" t="n"/>
-      <c r="F169" s="3" t="n"/>
-      <c r="G169" s="3" t="n"/>
-      <c r="H169" s="3" t="n"/>
-      <c r="I169" s="3" t="n"/>
-      <c r="J169" s="3" t="n"/>
-      <c r="K169" s="3" t="n"/>
-      <c r="L169" s="3" t="n"/>
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B169" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C169" s="5" t="inlineStr">
+        <is>
+          <t>20 allenamento B</t>
+        </is>
+      </c>
+      <c r="D169" s="5" t="inlineStr">
+        <is>
+          <t>1a</t>
+        </is>
+      </c>
+      <c r="E169" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="F169" s="5" t="inlineStr">
+        <is>
+          <t>Cobra to Down dog</t>
+        </is>
+      </c>
+      <c r="G169" s="5" t="inlineStr">
+        <is>
+          <t>3x8</t>
+        </is>
+      </c>
+      <c r="H169" s="5" t="inlineStr"/>
+      <c r="I169" s="5" t="inlineStr"/>
+      <c r="J169" s="5" t="inlineStr">
+        <is>
+          <t>jump set</t>
+        </is>
+      </c>
+      <c r="K169" s="5" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/JNLhhxNDkZs?si=IxpjFs4F8j3EOv0m</t>
+        </is>
+      </c>
+      <c r="L169" s="5" t="inlineStr"/>
       <c r="M169" s="3" t="n"/>
       <c r="N169" s="3" t="n"/>
     </row>
     <row r="170">
-      <c r="A170" s="3" t="n"/>
-      <c r="B170" s="3" t="n"/>
-      <c r="C170" s="3" t="n"/>
-      <c r="D170" s="3" t="n"/>
-      <c r="E170" s="3" t="n"/>
-      <c r="F170" s="3" t="n"/>
-      <c r="G170" s="3" t="n"/>
-      <c r="H170" s="3" t="n"/>
-      <c r="I170" s="3" t="n"/>
-      <c r="J170" s="3" t="n"/>
-      <c r="K170" s="3" t="n"/>
-      <c r="L170" s="3" t="n"/>
+      <c r="A170" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B170" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C170" s="5" t="inlineStr">
+        <is>
+          <t>20 allenamento B</t>
+        </is>
+      </c>
+      <c r="D170" s="5" t="inlineStr">
+        <is>
+          <t>1b</t>
+        </is>
+      </c>
+      <c r="E170" s="5" t="n">
+        <v>147</v>
+      </c>
+      <c r="F170" s="5" t="inlineStr">
+        <is>
+          <t>Hurdle Step</t>
+        </is>
+      </c>
+      <c r="G170" s="5" t="inlineStr">
+        <is>
+          <t>3x10+10</t>
+        </is>
+      </c>
+      <c r="H170" s="5" t="inlineStr">
+        <is>
+          <t>45"</t>
+        </is>
+      </c>
+      <c r="I170" s="5" t="inlineStr"/>
+      <c r="J170" s="5" t="inlineStr">
+        <is>
+          <t>jump set</t>
+        </is>
+      </c>
+      <c r="K170" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/tZ28cg_Wi1c?si=bNZhGLkec-Fb_fZw</t>
+        </is>
+      </c>
+      <c r="L170" s="5" t="inlineStr"/>
       <c r="M170" s="3" t="n"/>
       <c r="N170" s="3" t="n"/>
     </row>
     <row r="171">
-      <c r="A171" s="3" t="n"/>
-      <c r="B171" s="3" t="n"/>
-      <c r="C171" s="3" t="n"/>
-      <c r="D171" s="3" t="n"/>
-      <c r="E171" s="3" t="n"/>
-      <c r="F171" s="3" t="n"/>
-      <c r="G171" s="3" t="n"/>
-      <c r="H171" s="3" t="n"/>
-      <c r="I171" s="3" t="n"/>
-      <c r="J171" s="3" t="n"/>
-      <c r="K171" s="3" t="n"/>
-      <c r="L171" s="3" t="n"/>
+      <c r="A171" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B171" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C171" s="5" t="inlineStr">
+        <is>
+          <t>20 allenamento B</t>
+        </is>
+      </c>
+      <c r="D171" s="5" t="inlineStr">
+        <is>
+          <t>2a</t>
+        </is>
+      </c>
+      <c r="E171" s="5" t="n">
+        <v>188</v>
+      </c>
+      <c r="F171" s="5" t="inlineStr">
+        <is>
+          <t>Kettlebell Snatch</t>
+        </is>
+      </c>
+      <c r="G171" s="5" t="inlineStr">
+        <is>
+          <t>4x6+6</t>
+        </is>
+      </c>
+      <c r="H171" s="5" t="inlineStr">
+        <is>
+          <t>RBS 60"</t>
+        </is>
+      </c>
+      <c r="I171" s="5" t="inlineStr"/>
+      <c r="J171" s="5" t="inlineStr">
+        <is>
+          <t>RPE 8</t>
+        </is>
+      </c>
+      <c r="K171" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/rE8lJ9TxbEQ</t>
+        </is>
+      </c>
+      <c r="L171" s="5" t="inlineStr"/>
       <c r="M171" s="3" t="n"/>
       <c r="N171" s="3" t="n"/>
     </row>
     <row r="172">
-      <c r="A172" s="3" t="n"/>
-      <c r="B172" s="3" t="n"/>
-      <c r="C172" s="3" t="n"/>
-      <c r="D172" s="3" t="n"/>
-      <c r="E172" s="3" t="n"/>
-      <c r="F172" s="3" t="n"/>
-      <c r="G172" s="3" t="n"/>
-      <c r="H172" s="3" t="n"/>
-      <c r="I172" s="3" t="n"/>
-      <c r="J172" s="3" t="n"/>
-      <c r="K172" s="3" t="n"/>
-      <c r="L172" s="3" t="n"/>
+      <c r="A172" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B172" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C172" s="5" t="inlineStr">
+        <is>
+          <t>20 allenamento B</t>
+        </is>
+      </c>
+      <c r="D172" s="5" t="inlineStr">
+        <is>
+          <t>2b</t>
+        </is>
+      </c>
+      <c r="E172" s="5" t="n">
+        <v>119</v>
+      </c>
+      <c r="F172" s="5" t="inlineStr">
+        <is>
+          <t>Super Mario Jump</t>
+        </is>
+      </c>
+      <c r="G172" s="5" t="inlineStr">
+        <is>
+          <t>4x6+6</t>
+        </is>
+      </c>
+      <c r="H172" s="5" t="inlineStr">
+        <is>
+          <t>RBS 60"</t>
+        </is>
+      </c>
+      <c r="I172" s="5" t="inlineStr"/>
+      <c r="J172" s="5" t="inlineStr">
+        <is>
+          <t>jump set | RPE 8</t>
+        </is>
+      </c>
+      <c r="K172" s="5" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/XluivIvnr4k</t>
+        </is>
+      </c>
+      <c r="L172" s="5" t="inlineStr"/>
       <c r="M172" s="3" t="n"/>
       <c r="N172" s="3" t="n"/>
     </row>
     <row r="173">
-      <c r="A173" s="3" t="n"/>
-      <c r="B173" s="3" t="n"/>
-      <c r="C173" s="3" t="n"/>
-      <c r="D173" s="3" t="n"/>
-      <c r="E173" s="3" t="n"/>
-      <c r="F173" s="3" t="n"/>
-      <c r="G173" s="3" t="n"/>
-      <c r="H173" s="3" t="n"/>
-      <c r="I173" s="3" t="n"/>
-      <c r="J173" s="3" t="n"/>
-      <c r="K173" s="3" t="n"/>
-      <c r="L173" s="3" t="n"/>
+      <c r="A173" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B173" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C173" s="5" t="inlineStr">
+        <is>
+          <t>20 allenamento B</t>
+        </is>
+      </c>
+      <c r="D173" s="5" t="inlineStr">
+        <is>
+          <t>3a</t>
+        </is>
+      </c>
+      <c r="E173" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="F173" s="5" t="inlineStr">
+        <is>
+          <t>Coiled Punch iso.</t>
+        </is>
+      </c>
+      <c r="G173" s="5" t="inlineStr">
+        <is>
+          <t>4x8+8</t>
+        </is>
+      </c>
+      <c r="H173" s="5" t="inlineStr"/>
+      <c r="I173" s="5" t="inlineStr"/>
+      <c r="J173" s="5" t="inlineStr">
+        <is>
+          <t>jump set | RPE 8</t>
+        </is>
+      </c>
+      <c r="K173" s="5" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/mifz_6oZJlw</t>
+        </is>
+      </c>
+      <c r="L173" s="5" t="inlineStr"/>
       <c r="M173" s="3" t="n"/>
       <c r="N173" s="3" t="n"/>
     </row>
     <row r="174">
-      <c r="A174" s="3" t="n"/>
-      <c r="B174" s="3" t="n"/>
-      <c r="C174" s="3" t="n"/>
-      <c r="D174" s="3" t="n"/>
-      <c r="E174" s="3" t="n"/>
-      <c r="F174" s="3" t="n"/>
-      <c r="G174" s="3" t="n"/>
-      <c r="H174" s="3" t="n"/>
-      <c r="I174" s="3" t="n"/>
-      <c r="J174" s="3" t="n"/>
-      <c r="K174" s="3" t="n"/>
-      <c r="L174" s="3" t="n"/>
+      <c r="A174" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B174" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C174" s="5" t="inlineStr">
+        <is>
+          <t>20 allenamento B</t>
+        </is>
+      </c>
+      <c r="D174" s="5" t="inlineStr">
+        <is>
+          <t>3b</t>
+        </is>
+      </c>
+      <c r="E174" s="5" t="n">
+        <v>192</v>
+      </c>
+      <c r="F174" s="5" t="inlineStr">
+        <is>
+          <t>Endless rope kneeling pull</t>
+        </is>
+      </c>
+      <c r="G174" s="5" t="inlineStr">
+        <is>
+          <t>4x20"</t>
+        </is>
+      </c>
+      <c r="H174" s="5" t="inlineStr">
+        <is>
+          <t>45"</t>
+        </is>
+      </c>
+      <c r="I174" s="5" t="inlineStr"/>
+      <c r="J174" s="5" t="inlineStr">
+        <is>
+          <t>jump set</t>
+        </is>
+      </c>
+      <c r="K174" s="5" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/sNkK5m4fYi0</t>
+        </is>
+      </c>
+      <c r="L174" s="5" t="inlineStr"/>
       <c r="M174" s="3" t="n"/>
       <c r="N174" s="3" t="n"/>
     </row>
     <row r="175">
-      <c r="A175" s="3" t="n"/>
-      <c r="B175" s="3" t="n"/>
-      <c r="C175" s="3" t="n"/>
-      <c r="D175" s="3" t="n"/>
-      <c r="E175" s="3" t="n"/>
-      <c r="F175" s="3" t="n"/>
-      <c r="G175" s="3" t="n"/>
-      <c r="H175" s="3" t="n"/>
-      <c r="I175" s="3" t="n"/>
-      <c r="J175" s="3" t="n"/>
-      <c r="K175" s="3" t="n"/>
-      <c r="L175" s="3" t="n"/>
+      <c r="A175" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B175" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C175" s="5" t="inlineStr">
+        <is>
+          <t>20 allenamento B</t>
+        </is>
+      </c>
+      <c r="D175" s="5" t="inlineStr">
+        <is>
+          <t>4a</t>
+        </is>
+      </c>
+      <c r="E175" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="F175" s="5" t="inlineStr">
+        <is>
+          <t>Dumbbell Coiled Thruster</t>
+        </is>
+      </c>
+      <c r="G175" s="5" t="inlineStr">
+        <is>
+          <t>x 6+6</t>
+        </is>
+      </c>
+      <c r="H175" s="5" t="inlineStr"/>
+      <c r="I175" s="5" t="inlineStr"/>
+      <c r="J175" s="5" t="inlineStr">
+        <is>
+          <t>AMRAP 12'</t>
+        </is>
+      </c>
+      <c r="K175" s="5" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/nQHKdic83T8</t>
+        </is>
+      </c>
+      <c r="L175" s="5" t="inlineStr"/>
       <c r="M175" s="3" t="n"/>
       <c r="N175" s="3" t="n"/>
     </row>
     <row r="176">
-      <c r="A176" s="3" t="n"/>
-      <c r="B176" s="3" t="n"/>
-      <c r="C176" s="3" t="n"/>
-      <c r="D176" s="3" t="n"/>
-      <c r="E176" s="3" t="n"/>
-      <c r="F176" s="3" t="n"/>
-      <c r="G176" s="3" t="n"/>
-      <c r="H176" s="3" t="n"/>
-      <c r="I176" s="3" t="n"/>
-      <c r="J176" s="3" t="n"/>
-      <c r="K176" s="3" t="n"/>
-      <c r="L176" s="3" t="n"/>
+      <c r="A176" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B176" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C176" s="5" t="inlineStr">
+        <is>
+          <t>20 allenamento B</t>
+        </is>
+      </c>
+      <c r="D176" s="5" t="inlineStr">
+        <is>
+          <t>4b</t>
+        </is>
+      </c>
+      <c r="E176" s="5" t="n">
+        <v>228</v>
+      </c>
+      <c r="F176" s="5" t="inlineStr">
+        <is>
+          <t>COMBO Side kick trough + Sprawl</t>
+        </is>
+      </c>
+      <c r="G176" s="5" t="inlineStr">
+        <is>
+          <t>x 8</t>
+        </is>
+      </c>
+      <c r="H176" s="5" t="inlineStr"/>
+      <c r="I176" s="5" t="inlineStr"/>
+      <c r="J176" s="5" t="inlineStr">
+        <is>
+          <t>AMRAP 12'</t>
+        </is>
+      </c>
+      <c r="K176" s="5" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/iRJEq6FnzxI</t>
+        </is>
+      </c>
+      <c r="L176" s="5" t="inlineStr"/>
       <c r="M176" s="3" t="n"/>
       <c r="N176" s="3" t="n"/>
     </row>
     <row r="177">
-      <c r="A177" s="3" t="n"/>
-      <c r="B177" s="3" t="n"/>
-      <c r="C177" s="3" t="n"/>
-      <c r="D177" s="3" t="n"/>
-      <c r="E177" s="3" t="n"/>
-      <c r="F177" s="3" t="n"/>
-      <c r="G177" s="3" t="n"/>
-      <c r="H177" s="3" t="n"/>
-      <c r="I177" s="3" t="n"/>
-      <c r="J177" s="3" t="n"/>
-      <c r="K177" s="3" t="n"/>
-      <c r="L177" s="3" t="n"/>
+      <c r="A177" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B177" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C177" s="5" t="inlineStr">
+        <is>
+          <t>20 allenamento B</t>
+        </is>
+      </c>
+      <c r="D177" s="5" t="inlineStr">
+        <is>
+          <t>4c</t>
+        </is>
+      </c>
+      <c r="E177" s="5" t="n">
+        <v>233</v>
+      </c>
+      <c r="F177" s="5" t="inlineStr">
+        <is>
+          <t>rotation slam</t>
+        </is>
+      </c>
+      <c r="G177" s="5" t="inlineStr">
+        <is>
+          <t>x 10</t>
+        </is>
+      </c>
+      <c r="H177" s="5" t="inlineStr"/>
+      <c r="I177" s="5" t="inlineStr"/>
+      <c r="J177" s="5" t="inlineStr">
+        <is>
+          <t>AMRAP 12'</t>
+        </is>
+      </c>
+      <c r="K177" s="5" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/HwYENrEDFqY</t>
+        </is>
+      </c>
+      <c r="L177" s="5" t="inlineStr"/>
       <c r="M177" s="3" t="n"/>
       <c r="N177" s="3" t="n"/>
     </row>
     <row r="178">
-      <c r="A178" s="3" t="n"/>
-      <c r="B178" s="3" t="n"/>
-      <c r="C178" s="3" t="n"/>
-      <c r="D178" s="3" t="n"/>
-      <c r="E178" s="3" t="n"/>
-      <c r="F178" s="3" t="n"/>
-      <c r="G178" s="3" t="n"/>
-      <c r="H178" s="3" t="n"/>
-      <c r="I178" s="3" t="n"/>
-      <c r="J178" s="3" t="n"/>
-      <c r="K178" s="3" t="n"/>
-      <c r="L178" s="3" t="n"/>
+      <c r="A178" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B178" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C178" s="4" t="inlineStr">
+        <is>
+          <t>21 allenamento A</t>
+        </is>
+      </c>
+      <c r="D178" s="4" t="inlineStr">
+        <is>
+          <t>1a</t>
+        </is>
+      </c>
+      <c r="E178" s="4" t="n">
+        <v>158</v>
+      </c>
+      <c r="F178" s="4" t="inlineStr">
+        <is>
+          <t>Bat around the head 90° e 180°</t>
+        </is>
+      </c>
+      <c r="G178" s="4" t="inlineStr">
+        <is>
+          <t>3x8+8</t>
+        </is>
+      </c>
+      <c r="H178" s="4" t="inlineStr"/>
+      <c r="I178" s="4" t="inlineStr"/>
+      <c r="J178" s="4" t="inlineStr">
+        <is>
+          <t>jump set</t>
+        </is>
+      </c>
+      <c r="K178" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/INNpiEJL9As?si=7-xSjR1LJL__jzU8</t>
+        </is>
+      </c>
+      <c r="L178" s="4" t="inlineStr"/>
       <c r="M178" s="3" t="n"/>
       <c r="N178" s="3" t="n"/>
     </row>
     <row r="179">
-      <c r="A179" s="3" t="n"/>
-      <c r="B179" s="3" t="n"/>
-      <c r="C179" s="3" t="n"/>
-      <c r="D179" s="3" t="n"/>
-      <c r="E179" s="3" t="n"/>
-      <c r="F179" s="3" t="n"/>
-      <c r="G179" s="3" t="n"/>
-      <c r="H179" s="3" t="n"/>
-      <c r="I179" s="3" t="n"/>
-      <c r="J179" s="3" t="n"/>
-      <c r="K179" s="3" t="n"/>
-      <c r="L179" s="3" t="n"/>
+      <c r="A179" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>21 allenamento A</t>
+        </is>
+      </c>
+      <c r="D179" s="4" t="inlineStr">
+        <is>
+          <t>1b</t>
+        </is>
+      </c>
+      <c r="E179" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="F179" s="4" t="inlineStr">
+        <is>
+          <t>Side move</t>
+        </is>
+      </c>
+      <c r="G179" s="4" t="inlineStr">
+        <is>
+          <t>3x10+10</t>
+        </is>
+      </c>
+      <c r="H179" s="4" t="inlineStr">
+        <is>
+          <t>45"</t>
+        </is>
+      </c>
+      <c r="I179" s="4" t="inlineStr"/>
+      <c r="J179" s="4" t="inlineStr">
+        <is>
+          <t>jump set</t>
+        </is>
+      </c>
+      <c r="K179" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/ISkSG5yXhrU?si=aQYlqWHqyaE5nWL_</t>
+        </is>
+      </c>
+      <c r="L179" s="4" t="inlineStr"/>
       <c r="M179" s="3" t="n"/>
       <c r="N179" s="3" t="n"/>
     </row>
     <row r="180">
-      <c r="A180" s="3" t="n"/>
-      <c r="B180" s="3" t="n"/>
-      <c r="C180" s="3" t="n"/>
-      <c r="D180" s="3" t="n"/>
-      <c r="E180" s="3" t="n"/>
-      <c r="F180" s="3" t="n"/>
-      <c r="G180" s="3" t="n"/>
-      <c r="H180" s="3" t="n"/>
-      <c r="I180" s="3" t="n"/>
-      <c r="J180" s="3" t="n"/>
-      <c r="K180" s="3" t="n"/>
-      <c r="L180" s="3" t="n"/>
+      <c r="A180" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C180" s="4" t="inlineStr">
+        <is>
+          <t>21 allenamento A</t>
+        </is>
+      </c>
+      <c r="D180" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E180" s="4" t="n">
+        <v>127</v>
+      </c>
+      <c r="F180" s="4" t="inlineStr">
+        <is>
+          <t>COMBO: Landmine clean ALT. SCRD T/GO</t>
+        </is>
+      </c>
+      <c r="G180" s="4" t="inlineStr">
+        <is>
+          <t>4x6+6</t>
+        </is>
+      </c>
+      <c r="H180" s="4" t="inlineStr">
+        <is>
+          <t>RBS 60"</t>
+        </is>
+      </c>
+      <c r="I180" s="4" t="inlineStr"/>
+      <c r="J180" s="4" t="inlineStr">
+        <is>
+          <t>RPE 8</t>
+        </is>
+      </c>
+      <c r="K180" s="4" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/Zd7CQkHhnSo</t>
+        </is>
+      </c>
+      <c r="L180" s="4" t="inlineStr"/>
       <c r="M180" s="3" t="n"/>
       <c r="N180" s="3" t="n"/>
     </row>
     <row r="181">
-      <c r="A181" s="3" t="n"/>
-      <c r="B181" s="3" t="n"/>
-      <c r="C181" s="3" t="n"/>
-      <c r="D181" s="3" t="n"/>
-      <c r="E181" s="3" t="n"/>
-      <c r="F181" s="3" t="n"/>
-      <c r="G181" s="3" t="n"/>
-      <c r="H181" s="3" t="n"/>
-      <c r="I181" s="3" t="n"/>
-      <c r="J181" s="3" t="n"/>
-      <c r="K181" s="3" t="n"/>
-      <c r="L181" s="3" t="n"/>
+      <c r="A181" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>21 allenamento A</t>
+        </is>
+      </c>
+      <c r="D181" s="4" t="inlineStr">
+        <is>
+          <t>3a</t>
+        </is>
+      </c>
+      <c r="E181" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F181" s="4" t="inlineStr">
+        <is>
+          <t>Coiled Cable ROW</t>
+        </is>
+      </c>
+      <c r="G181" s="4" t="inlineStr">
+        <is>
+          <t>4x8+8</t>
+        </is>
+      </c>
+      <c r="H181" s="4" t="inlineStr"/>
+      <c r="I181" s="4" t="inlineStr"/>
+      <c r="J181" s="4" t="inlineStr">
+        <is>
+          <t>jump set | RPE 8</t>
+        </is>
+      </c>
+      <c r="K181" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/OdhNUbqajmM</t>
+        </is>
+      </c>
+      <c r="L181" s="4" t="inlineStr"/>
       <c r="M181" s="3" t="n"/>
       <c r="N181" s="3" t="n"/>
     </row>
     <row r="182">
-      <c r="A182" s="3" t="n"/>
-      <c r="B182" s="3" t="n"/>
-      <c r="C182" s="3" t="n"/>
-      <c r="D182" s="3" t="n"/>
-      <c r="E182" s="3" t="n"/>
-      <c r="F182" s="3" t="n"/>
-      <c r="G182" s="3" t="n"/>
-      <c r="H182" s="3" t="n"/>
-      <c r="I182" s="3" t="n"/>
-      <c r="J182" s="3" t="n"/>
-      <c r="K182" s="3" t="n"/>
-      <c r="L182" s="3" t="n"/>
+      <c r="A182" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B182" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>21 allenamento A</t>
+        </is>
+      </c>
+      <c r="D182" s="4" t="inlineStr">
+        <is>
+          <t>3b</t>
+        </is>
+      </c>
+      <c r="E182" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="F182" s="4" t="inlineStr">
+        <is>
+          <t>Kneeling Transition over head press</t>
+        </is>
+      </c>
+      <c r="G182" s="4" t="inlineStr">
+        <is>
+          <t>4x8+8</t>
+        </is>
+      </c>
+      <c r="H182" s="4" t="inlineStr">
+        <is>
+          <t>60"</t>
+        </is>
+      </c>
+      <c r="I182" s="4" t="inlineStr"/>
+      <c r="J182" s="4" t="inlineStr">
+        <is>
+          <t>jump set | RPE 8</t>
+        </is>
+      </c>
+      <c r="K182" s="4" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/Y-2AeFnKQLY</t>
+        </is>
+      </c>
+      <c r="L182" s="4" t="inlineStr"/>
       <c r="M182" s="3" t="n"/>
       <c r="N182" s="3" t="n"/>
     </row>
     <row r="183">
-      <c r="A183" s="3" t="n"/>
-      <c r="B183" s="3" t="n"/>
-      <c r="C183" s="3" t="n"/>
-      <c r="D183" s="3" t="n"/>
-      <c r="E183" s="3" t="n"/>
-      <c r="F183" s="3" t="n"/>
-      <c r="G183" s="3" t="n"/>
-      <c r="H183" s="3" t="n"/>
-      <c r="I183" s="3" t="n"/>
-      <c r="J183" s="3" t="n"/>
-      <c r="K183" s="3" t="n"/>
-      <c r="L183" s="3" t="n"/>
+      <c r="A183" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B183" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C183" s="4" t="inlineStr">
+        <is>
+          <t>21 allenamento A</t>
+        </is>
+      </c>
+      <c r="D183" s="4" t="inlineStr">
+        <is>
+          <t>4a</t>
+        </is>
+      </c>
+      <c r="E183" s="4" t="n">
+        <v>201</v>
+      </c>
+      <c r="F183" s="4" t="inlineStr">
+        <is>
+          <t>Step Up esplosivo alternato</t>
+        </is>
+      </c>
+      <c r="G183" s="4" t="inlineStr">
+        <is>
+          <t>3x8+8</t>
+        </is>
+      </c>
+      <c r="H183" s="4" t="inlineStr"/>
+      <c r="I183" s="4" t="inlineStr"/>
+      <c r="J183" s="4" t="inlineStr">
+        <is>
+          <t>circuito (3 round)</t>
+        </is>
+      </c>
+      <c r="K183" s="4" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/bAH_uySHG0c?si=H7r8TS-7k3vxrCRf</t>
+        </is>
+      </c>
+      <c r="L183" s="4" t="inlineStr"/>
       <c r="M183" s="3" t="n"/>
       <c r="N183" s="3" t="n"/>
     </row>
     <row r="184">
-      <c r="A184" s="3" t="n"/>
-      <c r="B184" s="3" t="n"/>
-      <c r="C184" s="3" t="n"/>
-      <c r="D184" s="3" t="n"/>
-      <c r="E184" s="3" t="n"/>
-      <c r="F184" s="3" t="n"/>
-      <c r="G184" s="3" t="n"/>
-      <c r="H184" s="3" t="n"/>
-      <c r="I184" s="3" t="n"/>
-      <c r="J184" s="3" t="n"/>
-      <c r="K184" s="3" t="n"/>
-      <c r="L184" s="3" t="n"/>
+      <c r="A184" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B184" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C184" s="4" t="inlineStr">
+        <is>
+          <t>21 allenamento A</t>
+        </is>
+      </c>
+      <c r="D184" s="4" t="inlineStr">
+        <is>
+          <t>4b</t>
+        </is>
+      </c>
+      <c r="E184" s="4" t="n">
+        <v>231</v>
+      </c>
+      <c r="F184" s="4" t="inlineStr">
+        <is>
+          <t>Banded hoock</t>
+        </is>
+      </c>
+      <c r="G184" s="4" t="inlineStr">
+        <is>
+          <t>3x10+10</t>
+        </is>
+      </c>
+      <c r="H184" s="4" t="inlineStr"/>
+      <c r="I184" s="4" t="inlineStr"/>
+      <c r="J184" s="4" t="inlineStr">
+        <is>
+          <t>circuito (3 round)</t>
+        </is>
+      </c>
+      <c r="K184" s="4" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/jEOtxSBwhCU</t>
+        </is>
+      </c>
+      <c r="L184" s="4" t="inlineStr"/>
       <c r="M184" s="3" t="n"/>
       <c r="N184" s="3" t="n"/>
     </row>
     <row r="185">
-      <c r="A185" s="3" t="n"/>
-      <c r="B185" s="3" t="n"/>
-      <c r="C185" s="3" t="n"/>
-      <c r="D185" s="3" t="n"/>
-      <c r="E185" s="3" t="n"/>
-      <c r="F185" s="3" t="n"/>
-      <c r="G185" s="3" t="n"/>
-      <c r="H185" s="3" t="n"/>
-      <c r="I185" s="3" t="n"/>
-      <c r="J185" s="3" t="n"/>
-      <c r="K185" s="3" t="n"/>
-      <c r="L185" s="3" t="n"/>
+      <c r="A185" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B185" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="inlineStr">
+        <is>
+          <t>21 allenamento A</t>
+        </is>
+      </c>
+      <c r="D185" s="4" t="inlineStr">
+        <is>
+          <t>4c</t>
+        </is>
+      </c>
+      <c r="E185" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F185" s="4" t="inlineStr">
+        <is>
+          <t>skierg pagaia mono</t>
+        </is>
+      </c>
+      <c r="G185" s="4" t="inlineStr">
+        <is>
+          <t>3x30"+30"</t>
+        </is>
+      </c>
+      <c r="H185" s="4" t="inlineStr">
+        <is>
+          <t>60"</t>
+        </is>
+      </c>
+      <c r="I185" s="4" t="inlineStr"/>
+      <c r="J185" s="4" t="inlineStr">
+        <is>
+          <t>circuito (3 round)</t>
+        </is>
+      </c>
+      <c r="K185" s="4" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/7n-hAJAXoYU</t>
+        </is>
+      </c>
+      <c r="L185" s="4" t="inlineStr"/>
       <c r="M185" s="3" t="n"/>
       <c r="N185" s="3" t="n"/>
     </row>
     <row r="186">
-      <c r="A186" s="3" t="n"/>
-      <c r="B186" s="3" t="n"/>
-      <c r="C186" s="3" t="n"/>
-      <c r="D186" s="3" t="n"/>
-      <c r="E186" s="3" t="n"/>
-      <c r="F186" s="3" t="n"/>
-      <c r="G186" s="3" t="n"/>
-      <c r="H186" s="3" t="n"/>
-      <c r="I186" s="3" t="n"/>
-      <c r="J186" s="3" t="n"/>
-      <c r="K186" s="3" t="n"/>
-      <c r="L186" s="3" t="n"/>
+      <c r="A186" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B186" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C186" s="5" t="inlineStr">
+        <is>
+          <t>22 allenamento B</t>
+        </is>
+      </c>
+      <c r="D186" s="5" t="inlineStr">
+        <is>
+          <t>1a</t>
+        </is>
+      </c>
+      <c r="E186" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="F186" s="5" t="inlineStr">
+        <is>
+          <t>Cobra to Down dog</t>
+        </is>
+      </c>
+      <c r="G186" s="5" t="inlineStr">
+        <is>
+          <t>3x8</t>
+        </is>
+      </c>
+      <c r="H186" s="5" t="inlineStr"/>
+      <c r="I186" s="5" t="inlineStr"/>
+      <c r="J186" s="5" t="inlineStr">
+        <is>
+          <t>jump set</t>
+        </is>
+      </c>
+      <c r="K186" s="5" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/JNLhhxNDkZs?si=IxpjFs4F8j3EOv0m</t>
+        </is>
+      </c>
+      <c r="L186" s="5" t="inlineStr"/>
       <c r="M186" s="3" t="n"/>
       <c r="N186" s="3" t="n"/>
     </row>
     <row r="187">
-      <c r="A187" s="3" t="n"/>
-      <c r="B187" s="3" t="n"/>
-      <c r="C187" s="3" t="n"/>
-      <c r="D187" s="3" t="n"/>
-      <c r="E187" s="3" t="n"/>
-      <c r="F187" s="3" t="n"/>
-      <c r="G187" s="3" t="n"/>
-      <c r="H187" s="3" t="n"/>
-      <c r="I187" s="3" t="n"/>
-      <c r="J187" s="3" t="n"/>
-      <c r="K187" s="3" t="n"/>
-      <c r="L187" s="3" t="n"/>
+      <c r="A187" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B187" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C187" s="5" t="inlineStr">
+        <is>
+          <t>22 allenamento B</t>
+        </is>
+      </c>
+      <c r="D187" s="5" t="inlineStr">
+        <is>
+          <t>1b</t>
+        </is>
+      </c>
+      <c r="E187" s="5" t="n">
+        <v>147</v>
+      </c>
+      <c r="F187" s="5" t="inlineStr">
+        <is>
+          <t>Hurdle Step</t>
+        </is>
+      </c>
+      <c r="G187" s="5" t="inlineStr">
+        <is>
+          <t>3x10+10</t>
+        </is>
+      </c>
+      <c r="H187" s="5" t="inlineStr">
+        <is>
+          <t>45"</t>
+        </is>
+      </c>
+      <c r="I187" s="5" t="inlineStr"/>
+      <c r="J187" s="5" t="inlineStr">
+        <is>
+          <t>jump set</t>
+        </is>
+      </c>
+      <c r="K187" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/tZ28cg_Wi1c?si=bNZhGLkec-Fb_fZw</t>
+        </is>
+      </c>
+      <c r="L187" s="5" t="inlineStr"/>
       <c r="M187" s="3" t="n"/>
       <c r="N187" s="3" t="n"/>
     </row>
     <row r="188">
-      <c r="A188" s="3" t="n"/>
-      <c r="B188" s="3" t="n"/>
-      <c r="C188" s="3" t="n"/>
-      <c r="D188" s="3" t="n"/>
-      <c r="E188" s="3" t="n"/>
-      <c r="F188" s="3" t="n"/>
-      <c r="G188" s="3" t="n"/>
-      <c r="H188" s="3" t="n"/>
-      <c r="I188" s="3" t="n"/>
-      <c r="J188" s="3" t="n"/>
-      <c r="K188" s="3" t="n"/>
-      <c r="L188" s="3" t="n"/>
+      <c r="A188" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B188" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C188" s="5" t="inlineStr">
+        <is>
+          <t>22 allenamento B</t>
+        </is>
+      </c>
+      <c r="D188" s="5" t="inlineStr">
+        <is>
+          <t>2a</t>
+        </is>
+      </c>
+      <c r="E188" s="5" t="n">
+        <v>188</v>
+      </c>
+      <c r="F188" s="5" t="inlineStr">
+        <is>
+          <t>Kettlebell Snatch</t>
+        </is>
+      </c>
+      <c r="G188" s="5" t="inlineStr">
+        <is>
+          <t>4x6+6</t>
+        </is>
+      </c>
+      <c r="H188" s="5" t="inlineStr">
+        <is>
+          <t>RBS 60"</t>
+        </is>
+      </c>
+      <c r="I188" s="5" t="inlineStr"/>
+      <c r="J188" s="5" t="inlineStr">
+        <is>
+          <t>RPE 8</t>
+        </is>
+      </c>
+      <c r="K188" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/rE8lJ9TxbEQ</t>
+        </is>
+      </c>
+      <c r="L188" s="5" t="inlineStr"/>
       <c r="M188" s="3" t="n"/>
       <c r="N188" s="3" t="n"/>
     </row>
     <row r="189">
-      <c r="A189" s="3" t="n"/>
-      <c r="B189" s="3" t="n"/>
-      <c r="C189" s="3" t="n"/>
-      <c r="D189" s="3" t="n"/>
-      <c r="E189" s="3" t="n"/>
-      <c r="F189" s="3" t="n"/>
-      <c r="G189" s="3" t="n"/>
-      <c r="H189" s="3" t="n"/>
-      <c r="I189" s="3" t="n"/>
-      <c r="J189" s="3" t="n"/>
-      <c r="K189" s="3" t="n"/>
-      <c r="L189" s="3" t="n"/>
+      <c r="A189" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B189" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C189" s="5" t="inlineStr">
+        <is>
+          <t>22 allenamento B</t>
+        </is>
+      </c>
+      <c r="D189" s="5" t="inlineStr">
+        <is>
+          <t>2b</t>
+        </is>
+      </c>
+      <c r="E189" s="5" t="n">
+        <v>119</v>
+      </c>
+      <c r="F189" s="5" t="inlineStr">
+        <is>
+          <t>Super Mario Jump</t>
+        </is>
+      </c>
+      <c r="G189" s="5" t="inlineStr">
+        <is>
+          <t>4x6+6</t>
+        </is>
+      </c>
+      <c r="H189" s="5" t="inlineStr">
+        <is>
+          <t>RBS 60"</t>
+        </is>
+      </c>
+      <c r="I189" s="5" t="inlineStr"/>
+      <c r="J189" s="5" t="inlineStr">
+        <is>
+          <t>jump set | RPE 8</t>
+        </is>
+      </c>
+      <c r="K189" s="5" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/XluivIvnr4k</t>
+        </is>
+      </c>
+      <c r="L189" s="5" t="inlineStr"/>
       <c r="M189" s="3" t="n"/>
       <c r="N189" s="3" t="n"/>
     </row>
     <row r="190">
-      <c r="A190" s="3" t="n"/>
-      <c r="B190" s="3" t="n"/>
-      <c r="C190" s="3" t="n"/>
-      <c r="D190" s="3" t="n"/>
-      <c r="E190" s="3" t="n"/>
-      <c r="F190" s="3" t="n"/>
-      <c r="G190" s="3" t="n"/>
-      <c r="H190" s="3" t="n"/>
-      <c r="I190" s="3" t="n"/>
-      <c r="J190" s="3" t="n"/>
-      <c r="K190" s="3" t="n"/>
-      <c r="L190" s="3" t="n"/>
+      <c r="A190" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B190" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C190" s="5" t="inlineStr">
+        <is>
+          <t>22 allenamento B</t>
+        </is>
+      </c>
+      <c r="D190" s="5" t="inlineStr">
+        <is>
+          <t>3a</t>
+        </is>
+      </c>
+      <c r="E190" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="F190" s="5" t="inlineStr">
+        <is>
+          <t>Coiled Punch iso.</t>
+        </is>
+      </c>
+      <c r="G190" s="5" t="inlineStr">
+        <is>
+          <t>4x8+8</t>
+        </is>
+      </c>
+      <c r="H190" s="5" t="inlineStr"/>
+      <c r="I190" s="5" t="inlineStr"/>
+      <c r="J190" s="5" t="inlineStr">
+        <is>
+          <t>jump set | RPE 8</t>
+        </is>
+      </c>
+      <c r="K190" s="5" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/mifz_6oZJlw</t>
+        </is>
+      </c>
+      <c r="L190" s="5" t="inlineStr"/>
       <c r="M190" s="3" t="n"/>
       <c r="N190" s="3" t="n"/>
     </row>
     <row r="191">
-      <c r="A191" s="3" t="n"/>
-      <c r="B191" s="3" t="n"/>
-      <c r="C191" s="3" t="n"/>
-      <c r="D191" s="3" t="n"/>
-      <c r="E191" s="3" t="n"/>
-      <c r="F191" s="3" t="n"/>
-      <c r="G191" s="3" t="n"/>
-      <c r="H191" s="3" t="n"/>
-      <c r="I191" s="3" t="n"/>
-      <c r="J191" s="3" t="n"/>
-      <c r="K191" s="3" t="n"/>
-      <c r="L191" s="3" t="n"/>
+      <c r="A191" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B191" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C191" s="5" t="inlineStr">
+        <is>
+          <t>22 allenamento B</t>
+        </is>
+      </c>
+      <c r="D191" s="5" t="inlineStr">
+        <is>
+          <t>3b</t>
+        </is>
+      </c>
+      <c r="E191" s="5" t="n">
+        <v>192</v>
+      </c>
+      <c r="F191" s="5" t="inlineStr">
+        <is>
+          <t>Endless rope kneeling pull</t>
+        </is>
+      </c>
+      <c r="G191" s="5" t="inlineStr">
+        <is>
+          <t>4x20"</t>
+        </is>
+      </c>
+      <c r="H191" s="5" t="inlineStr">
+        <is>
+          <t>45"</t>
+        </is>
+      </c>
+      <c r="I191" s="5" t="inlineStr"/>
+      <c r="J191" s="5" t="inlineStr">
+        <is>
+          <t>jump set</t>
+        </is>
+      </c>
+      <c r="K191" s="5" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/sNkK5m4fYi0</t>
+        </is>
+      </c>
+      <c r="L191" s="5" t="inlineStr"/>
       <c r="M191" s="3" t="n"/>
       <c r="N191" s="3" t="n"/>
     </row>
     <row r="192">
-      <c r="A192" s="3" t="n"/>
-      <c r="B192" s="3" t="n"/>
-      <c r="C192" s="3" t="n"/>
-      <c r="D192" s="3" t="n"/>
-      <c r="E192" s="3" t="n"/>
-      <c r="F192" s="3" t="n"/>
-      <c r="G192" s="3" t="n"/>
-      <c r="H192" s="3" t="n"/>
-      <c r="I192" s="3" t="n"/>
-      <c r="J192" s="3" t="n"/>
-      <c r="K192" s="3" t="n"/>
-      <c r="L192" s="3" t="n"/>
+      <c r="A192" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B192" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C192" s="5" t="inlineStr">
+        <is>
+          <t>22 allenamento B</t>
+        </is>
+      </c>
+      <c r="D192" s="5" t="inlineStr">
+        <is>
+          <t>4a</t>
+        </is>
+      </c>
+      <c r="E192" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="F192" s="5" t="inlineStr">
+        <is>
+          <t>Dumbbell Coiled Thruster</t>
+        </is>
+      </c>
+      <c r="G192" s="5" t="inlineStr">
+        <is>
+          <t>x 6+6</t>
+        </is>
+      </c>
+      <c r="H192" s="5" t="inlineStr"/>
+      <c r="I192" s="5" t="inlineStr"/>
+      <c r="J192" s="5" t="inlineStr">
+        <is>
+          <t>AMRAP 12'</t>
+        </is>
+      </c>
+      <c r="K192" s="5" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/nQHKdic83T8</t>
+        </is>
+      </c>
+      <c r="L192" s="5" t="inlineStr"/>
       <c r="M192" s="3" t="n"/>
       <c r="N192" s="3" t="n"/>
     </row>
     <row r="193">
-      <c r="A193" s="3" t="n"/>
-      <c r="B193" s="3" t="n"/>
-      <c r="C193" s="3" t="n"/>
-      <c r="D193" s="3" t="n"/>
-      <c r="E193" s="3" t="n"/>
-      <c r="F193" s="3" t="n"/>
-      <c r="G193" s="3" t="n"/>
-      <c r="H193" s="3" t="n"/>
-      <c r="I193" s="3" t="n"/>
-      <c r="J193" s="3" t="n"/>
-      <c r="K193" s="3" t="n"/>
-      <c r="L193" s="3" t="n"/>
+      <c r="A193" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B193" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C193" s="5" t="inlineStr">
+        <is>
+          <t>22 allenamento B</t>
+        </is>
+      </c>
+      <c r="D193" s="5" t="inlineStr">
+        <is>
+          <t>4b</t>
+        </is>
+      </c>
+      <c r="E193" s="5" t="n">
+        <v>228</v>
+      </c>
+      <c r="F193" s="5" t="inlineStr">
+        <is>
+          <t>COMBO Side kick trough + Sprawl</t>
+        </is>
+      </c>
+      <c r="G193" s="5" t="inlineStr">
+        <is>
+          <t>x 8</t>
+        </is>
+      </c>
+      <c r="H193" s="5" t="inlineStr"/>
+      <c r="I193" s="5" t="inlineStr"/>
+      <c r="J193" s="5" t="inlineStr">
+        <is>
+          <t>AMRAP 12'</t>
+        </is>
+      </c>
+      <c r="K193" s="5" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/iRJEq6FnzxI</t>
+        </is>
+      </c>
+      <c r="L193" s="5" t="inlineStr"/>
       <c r="M193" s="3" t="n"/>
       <c r="N193" s="3" t="n"/>
     </row>
     <row r="194">
-      <c r="A194" s="3" t="n"/>
-      <c r="B194" s="3" t="n"/>
-      <c r="C194" s="3" t="n"/>
-      <c r="D194" s="3" t="n"/>
-      <c r="E194" s="3" t="n"/>
-      <c r="F194" s="3" t="n"/>
-      <c r="G194" s="3" t="n"/>
-      <c r="H194" s="3" t="n"/>
-      <c r="I194" s="3" t="n"/>
-      <c r="J194" s="3" t="n"/>
-      <c r="K194" s="3" t="n"/>
-      <c r="L194" s="3" t="n"/>
+      <c r="A194" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B194" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C194" s="5" t="inlineStr">
+        <is>
+          <t>22 allenamento B</t>
+        </is>
+      </c>
+      <c r="D194" s="5" t="inlineStr">
+        <is>
+          <t>4c</t>
+        </is>
+      </c>
+      <c r="E194" s="5" t="n">
+        <v>233</v>
+      </c>
+      <c r="F194" s="5" t="inlineStr">
+        <is>
+          <t>rotation slam</t>
+        </is>
+      </c>
+      <c r="G194" s="5" t="inlineStr">
+        <is>
+          <t>x 10</t>
+        </is>
+      </c>
+      <c r="H194" s="5" t="inlineStr"/>
+      <c r="I194" s="5" t="inlineStr"/>
+      <c r="J194" s="5" t="inlineStr">
+        <is>
+          <t>AMRAP 12'</t>
+        </is>
+      </c>
+      <c r="K194" s="5" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/HwYENrEDFqY</t>
+        </is>
+      </c>
+      <c r="L194" s="5" t="inlineStr"/>
       <c r="M194" s="3" t="n"/>
       <c r="N194" s="3" t="n"/>
     </row>
     <row r="195">
-      <c r="A195" s="3" t="n"/>
-      <c r="B195" s="3" t="n"/>
-      <c r="C195" s="3" t="n"/>
-      <c r="D195" s="3" t="n"/>
-      <c r="E195" s="3" t="n"/>
-      <c r="F195" s="3" t="n"/>
-      <c r="G195" s="3" t="n"/>
-      <c r="H195" s="3" t="n"/>
-      <c r="I195" s="3" t="n"/>
-      <c r="J195" s="3" t="n"/>
-      <c r="K195" s="3" t="n"/>
-      <c r="L195" s="3" t="n"/>
+      <c r="A195" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="inlineStr">
+        <is>
+          <t>23 allenamento A</t>
+        </is>
+      </c>
+      <c r="D195" s="4" t="inlineStr">
+        <is>
+          <t>1a</t>
+        </is>
+      </c>
+      <c r="E195" s="4" t="n">
+        <v>158</v>
+      </c>
+      <c r="F195" s="4" t="inlineStr">
+        <is>
+          <t>Bat around the head 90° e 180°</t>
+        </is>
+      </c>
+      <c r="G195" s="4" t="inlineStr">
+        <is>
+          <t>3x8+8</t>
+        </is>
+      </c>
+      <c r="H195" s="4" t="inlineStr"/>
+      <c r="I195" s="4" t="inlineStr"/>
+      <c r="J195" s="4" t="inlineStr">
+        <is>
+          <t>jump set</t>
+        </is>
+      </c>
+      <c r="K195" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/INNpiEJL9As?si=7-xSjR1LJL__jzU8</t>
+        </is>
+      </c>
+      <c r="L195" s="4" t="inlineStr"/>
       <c r="M195" s="3" t="n"/>
       <c r="N195" s="3" t="n"/>
     </row>
     <row r="196">
-      <c r="A196" s="3" t="n"/>
-      <c r="B196" s="3" t="n"/>
-      <c r="C196" s="3" t="n"/>
-      <c r="D196" s="3" t="n"/>
-      <c r="E196" s="3" t="n"/>
-      <c r="F196" s="3" t="n"/>
-      <c r="G196" s="3" t="n"/>
-      <c r="H196" s="3" t="n"/>
-      <c r="I196" s="3" t="n"/>
-      <c r="J196" s="3" t="n"/>
-      <c r="K196" s="3" t="n"/>
-      <c r="L196" s="3" t="n"/>
+      <c r="A196" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C196" s="4" t="inlineStr">
+        <is>
+          <t>23 allenamento A</t>
+        </is>
+      </c>
+      <c r="D196" s="4" t="inlineStr">
+        <is>
+          <t>1b</t>
+        </is>
+      </c>
+      <c r="E196" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="F196" s="4" t="inlineStr">
+        <is>
+          <t>Side move</t>
+        </is>
+      </c>
+      <c r="G196" s="4" t="inlineStr">
+        <is>
+          <t>3x10+10</t>
+        </is>
+      </c>
+      <c r="H196" s="4" t="inlineStr">
+        <is>
+          <t>45"</t>
+        </is>
+      </c>
+      <c r="I196" s="4" t="inlineStr"/>
+      <c r="J196" s="4" t="inlineStr">
+        <is>
+          <t>jump set</t>
+        </is>
+      </c>
+      <c r="K196" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/ISkSG5yXhrU?si=aQYlqWHqyaE5nWL_</t>
+        </is>
+      </c>
+      <c r="L196" s="4" t="inlineStr"/>
       <c r="M196" s="3" t="n"/>
       <c r="N196" s="3" t="n"/>
     </row>
     <row r="197">
-      <c r="A197" s="3" t="n"/>
-      <c r="B197" s="3" t="n"/>
-      <c r="C197" s="3" t="n"/>
-      <c r="D197" s="3" t="n"/>
-      <c r="E197" s="3" t="n"/>
-      <c r="F197" s="3" t="n"/>
-      <c r="G197" s="3" t="n"/>
-      <c r="H197" s="3" t="n"/>
-      <c r="I197" s="3" t="n"/>
-      <c r="J197" s="3" t="n"/>
-      <c r="K197" s="3" t="n"/>
-      <c r="L197" s="3" t="n"/>
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="inlineStr">
+        <is>
+          <t>23 allenamento A</t>
+        </is>
+      </c>
+      <c r="D197" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E197" s="4" t="n">
+        <v>127</v>
+      </c>
+      <c r="F197" s="4" t="inlineStr">
+        <is>
+          <t>COMBO: Landmine clean ALT. SCRD T/GO</t>
+        </is>
+      </c>
+      <c r="G197" s="4" t="inlineStr">
+        <is>
+          <t>4x6+6</t>
+        </is>
+      </c>
+      <c r="H197" s="4" t="inlineStr">
+        <is>
+          <t>RBS 60"</t>
+        </is>
+      </c>
+      <c r="I197" s="4" t="inlineStr"/>
+      <c r="J197" s="4" t="inlineStr">
+        <is>
+          <t>RPE 8</t>
+        </is>
+      </c>
+      <c r="K197" s="4" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/Zd7CQkHhnSo</t>
+        </is>
+      </c>
+      <c r="L197" s="4" t="inlineStr"/>
       <c r="M197" s="3" t="n"/>
       <c r="N197" s="3" t="n"/>
     </row>
     <row r="198">
-      <c r="A198" s="3" t="n"/>
-      <c r="B198" s="3" t="n"/>
-      <c r="C198" s="3" t="n"/>
-      <c r="D198" s="3" t="n"/>
-      <c r="E198" s="3" t="n"/>
-      <c r="F198" s="3" t="n"/>
-      <c r="G198" s="3" t="n"/>
-      <c r="H198" s="3" t="n"/>
-      <c r="I198" s="3" t="n"/>
-      <c r="J198" s="3" t="n"/>
-      <c r="K198" s="3" t="n"/>
-      <c r="L198" s="3" t="n"/>
+      <c r="A198" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B198" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C198" s="4" t="inlineStr">
+        <is>
+          <t>23 allenamento A</t>
+        </is>
+      </c>
+      <c r="D198" s="4" t="inlineStr">
+        <is>
+          <t>3a</t>
+        </is>
+      </c>
+      <c r="E198" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F198" s="4" t="inlineStr">
+        <is>
+          <t>Coiled Cable ROW</t>
+        </is>
+      </c>
+      <c r="G198" s="4" t="inlineStr">
+        <is>
+          <t>4x8+8</t>
+        </is>
+      </c>
+      <c r="H198" s="4" t="inlineStr"/>
+      <c r="I198" s="4" t="inlineStr"/>
+      <c r="J198" s="4" t="inlineStr">
+        <is>
+          <t>jump set | RPE 8</t>
+        </is>
+      </c>
+      <c r="K198" s="4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/OdhNUbqajmM</t>
+        </is>
+      </c>
+      <c r="L198" s="4" t="inlineStr"/>
       <c r="M198" s="3" t="n"/>
       <c r="N198" s="3" t="n"/>
     </row>
     <row r="199">
-      <c r="A199" s="3" t="n"/>
-      <c r="B199" s="3" t="n"/>
-      <c r="C199" s="3" t="n"/>
-      <c r="D199" s="3" t="n"/>
-      <c r="E199" s="3" t="n"/>
-      <c r="F199" s="3" t="n"/>
-      <c r="G199" s="3" t="n"/>
-      <c r="H199" s="3" t="n"/>
-      <c r="I199" s="3" t="n"/>
-      <c r="J199" s="3" t="n"/>
-      <c r="K199" s="3" t="n"/>
-      <c r="L199" s="3" t="n"/>
+      <c r="A199" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B199" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C199" s="4" t="inlineStr">
+        <is>
+          <t>23 allenamento A</t>
+        </is>
+      </c>
+      <c r="D199" s="4" t="inlineStr">
+        <is>
+          <t>3b</t>
+        </is>
+      </c>
+      <c r="E199" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="F199" s="4" t="inlineStr">
+        <is>
+          <t>Kneeling Transition over head press</t>
+        </is>
+      </c>
+      <c r="G199" s="4" t="inlineStr">
+        <is>
+          <t>4x8+8</t>
+        </is>
+      </c>
+      <c r="H199" s="4" t="inlineStr">
+        <is>
+          <t>60"</t>
+        </is>
+      </c>
+      <c r="I199" s="4" t="inlineStr"/>
+      <c r="J199" s="4" t="inlineStr">
+        <is>
+          <t>jump set | RPE 8</t>
+        </is>
+      </c>
+      <c r="K199" s="4" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/Y-2AeFnKQLY</t>
+        </is>
+      </c>
+      <c r="L199" s="4" t="inlineStr"/>
       <c r="M199" s="3" t="n"/>
       <c r="N199" s="3" t="n"/>
     </row>
     <row r="200">
-      <c r="A200" s="3" t="n"/>
-      <c r="B200" s="3" t="n"/>
-      <c r="C200" s="3" t="n"/>
-      <c r="D200" s="3" t="n"/>
-      <c r="E200" s="3" t="n"/>
-      <c r="F200" s="3" t="n"/>
-      <c r="G200" s="3" t="n"/>
-      <c r="H200" s="3" t="n"/>
-      <c r="I200" s="3" t="n"/>
-      <c r="J200" s="3" t="n"/>
-      <c r="K200" s="3" t="n"/>
-      <c r="L200" s="3" t="n"/>
+      <c r="A200" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B200" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C200" s="4" t="inlineStr">
+        <is>
+          <t>23 allenamento A</t>
+        </is>
+      </c>
+      <c r="D200" s="4" t="inlineStr">
+        <is>
+          <t>4a</t>
+        </is>
+      </c>
+      <c r="E200" s="4" t="n">
+        <v>201</v>
+      </c>
+      <c r="F200" s="4" t="inlineStr">
+        <is>
+          <t>Step Up esplosivo alternato</t>
+        </is>
+      </c>
+      <c r="G200" s="4" t="inlineStr">
+        <is>
+          <t>3x8+8</t>
+        </is>
+      </c>
+      <c r="H200" s="4" t="inlineStr"/>
+      <c r="I200" s="4" t="inlineStr"/>
+      <c r="J200" s="4" t="inlineStr">
+        <is>
+          <t>circuito (3 round)</t>
+        </is>
+      </c>
+      <c r="K200" s="4" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/bAH_uySHG0c?si=H7r8TS-7k3vxrCRf</t>
+        </is>
+      </c>
+      <c r="L200" s="4" t="inlineStr"/>
       <c r="M200" s="3" t="n"/>
       <c r="N200" s="3" t="n"/>
     </row>
     <row r="201">
-      <c r="A201" s="3" t="n"/>
-      <c r="B201" s="3" t="n"/>
-      <c r="C201" s="3" t="n"/>
-      <c r="D201" s="3" t="n"/>
-      <c r="E201" s="3" t="n"/>
-      <c r="F201" s="3" t="n"/>
-      <c r="G201" s="3" t="n"/>
-      <c r="H201" s="3" t="n"/>
-      <c r="I201" s="3" t="n"/>
-      <c r="J201" s="3" t="n"/>
-      <c r="K201" s="3" t="n"/>
-      <c r="L201" s="3" t="n"/>
+      <c r="A201" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B201" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C201" s="4" t="inlineStr">
+        <is>
+          <t>23 allenamento A</t>
+        </is>
+      </c>
+      <c r="D201" s="4" t="inlineStr">
+        <is>
+          <t>4b</t>
+        </is>
+      </c>
+      <c r="E201" s="4" t="n">
+        <v>231</v>
+      </c>
+      <c r="F201" s="4" t="inlineStr">
+        <is>
+          <t>Banded hoock</t>
+        </is>
+      </c>
+      <c r="G201" s="4" t="inlineStr">
+        <is>
+          <t>3x10+10</t>
+        </is>
+      </c>
+      <c r="H201" s="4" t="inlineStr"/>
+      <c r="I201" s="4" t="inlineStr"/>
+      <c r="J201" s="4" t="inlineStr">
+        <is>
+          <t>circuito (3 round)</t>
+        </is>
+      </c>
+      <c r="K201" s="4" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/jEOtxSBwhCU</t>
+        </is>
+      </c>
+      <c r="L201" s="4" t="inlineStr"/>
       <c r="M201" s="3" t="n"/>
       <c r="N201" s="3" t="n"/>
     </row>
     <row r="202">
-      <c r="A202" s="3" t="n"/>
-      <c r="B202" s="3" t="n"/>
-      <c r="C202" s="3" t="n"/>
-      <c r="D202" s="3" t="n"/>
-      <c r="E202" s="3" t="n"/>
-      <c r="F202" s="3" t="n"/>
-      <c r="G202" s="3" t="n"/>
-      <c r="H202" s="3" t="n"/>
-      <c r="I202" s="3" t="n"/>
-      <c r="J202" s="3" t="n"/>
-      <c r="K202" s="3" t="n"/>
-      <c r="L202" s="3" t="n"/>
+      <c r="A202" s="4" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B202" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C202" s="4" t="inlineStr">
+        <is>
+          <t>23 allenamento A</t>
+        </is>
+      </c>
+      <c r="D202" s="4" t="inlineStr">
+        <is>
+          <t>4c</t>
+        </is>
+      </c>
+      <c r="E202" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F202" s="4" t="inlineStr">
+        <is>
+          <t>skierg pagaia mono</t>
+        </is>
+      </c>
+      <c r="G202" s="4" t="inlineStr">
+        <is>
+          <t>3x30"+30"</t>
+        </is>
+      </c>
+      <c r="H202" s="4" t="inlineStr">
+        <is>
+          <t>60"</t>
+        </is>
+      </c>
+      <c r="I202" s="4" t="inlineStr"/>
+      <c r="J202" s="4" t="inlineStr">
+        <is>
+          <t>circuito (3 round)</t>
+        </is>
+      </c>
+      <c r="K202" s="4" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/7n-hAJAXoYU</t>
+        </is>
+      </c>
+      <c r="L202" s="4" t="inlineStr"/>
       <c r="M202" s="3" t="n"/>
       <c r="N202" s="3" t="n"/>
     </row>
     <row r="203">
-      <c r="A203" s="3" t="n"/>
-      <c r="B203" s="3" t="n"/>
-      <c r="C203" s="3" t="n"/>
-      <c r="D203" s="3" t="n"/>
-      <c r="E203" s="3" t="n"/>
-      <c r="F203" s="3" t="n"/>
-      <c r="G203" s="3" t="n"/>
-      <c r="H203" s="3" t="n"/>
-      <c r="I203" s="3" t="n"/>
-      <c r="J203" s="3" t="n"/>
-      <c r="K203" s="3" t="n"/>
-      <c r="L203" s="3" t="n"/>
+      <c r="A203" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B203" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C203" s="5" t="inlineStr">
+        <is>
+          <t>24 allenamento B</t>
+        </is>
+      </c>
+      <c r="D203" s="5" t="inlineStr">
+        <is>
+          <t>1a</t>
+        </is>
+      </c>
+      <c r="E203" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="F203" s="5" t="inlineStr">
+        <is>
+          <t>Cobra to Down dog</t>
+        </is>
+      </c>
+      <c r="G203" s="5" t="inlineStr">
+        <is>
+          <t>3x8</t>
+        </is>
+      </c>
+      <c r="H203" s="5" t="inlineStr"/>
+      <c r="I203" s="5" t="inlineStr"/>
+      <c r="J203" s="5" t="inlineStr">
+        <is>
+          <t>jump set</t>
+        </is>
+      </c>
+      <c r="K203" s="5" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/JNLhhxNDkZs?si=IxpjFs4F8j3EOv0m</t>
+        </is>
+      </c>
+      <c r="L203" s="5" t="inlineStr"/>
       <c r="M203" s="3" t="n"/>
       <c r="N203" s="3" t="n"/>
     </row>
     <row r="204">
-      <c r="A204" s="3" t="n"/>
-      <c r="B204" s="3" t="n"/>
-      <c r="C204" s="3" t="n"/>
-      <c r="D204" s="3" t="n"/>
-      <c r="E204" s="3" t="n"/>
-      <c r="F204" s="3" t="n"/>
-      <c r="G204" s="3" t="n"/>
-      <c r="H204" s="3" t="n"/>
-      <c r="I204" s="3" t="n"/>
-      <c r="J204" s="3" t="n"/>
-      <c r="K204" s="3" t="n"/>
-      <c r="L204" s="3" t="n"/>
+      <c r="A204" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B204" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C204" s="5" t="inlineStr">
+        <is>
+          <t>24 allenamento B</t>
+        </is>
+      </c>
+      <c r="D204" s="5" t="inlineStr">
+        <is>
+          <t>1b</t>
+        </is>
+      </c>
+      <c r="E204" s="5" t="n">
+        <v>147</v>
+      </c>
+      <c r="F204" s="5" t="inlineStr">
+        <is>
+          <t>Hurdle Step</t>
+        </is>
+      </c>
+      <c r="G204" s="5" t="inlineStr">
+        <is>
+          <t>3x10+10</t>
+        </is>
+      </c>
+      <c r="H204" s="5" t="inlineStr">
+        <is>
+          <t>45"</t>
+        </is>
+      </c>
+      <c r="I204" s="5" t="inlineStr"/>
+      <c r="J204" s="5" t="inlineStr">
+        <is>
+          <t>jump set</t>
+        </is>
+      </c>
+      <c r="K204" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/tZ28cg_Wi1c?si=bNZhGLkec-Fb_fZw</t>
+        </is>
+      </c>
+      <c r="L204" s="5" t="inlineStr"/>
       <c r="M204" s="3" t="n"/>
       <c r="N204" s="3" t="n"/>
     </row>
     <row r="205">
-      <c r="A205" s="3" t="n"/>
-      <c r="B205" s="3" t="n"/>
-      <c r="C205" s="3" t="n"/>
-      <c r="D205" s="3" t="n"/>
-      <c r="E205" s="3" t="n"/>
-      <c r="F205" s="3" t="n"/>
-      <c r="G205" s="3" t="n"/>
-      <c r="H205" s="3" t="n"/>
-      <c r="I205" s="3" t="n"/>
-      <c r="J205" s="3" t="n"/>
-      <c r="K205" s="3" t="n"/>
-      <c r="L205" s="3" t="n"/>
+      <c r="A205" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B205" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C205" s="5" t="inlineStr">
+        <is>
+          <t>24 allenamento B</t>
+        </is>
+      </c>
+      <c r="D205" s="5" t="inlineStr">
+        <is>
+          <t>2a</t>
+        </is>
+      </c>
+      <c r="E205" s="5" t="n">
+        <v>188</v>
+      </c>
+      <c r="F205" s="5" t="inlineStr">
+        <is>
+          <t>Kettlebell Snatch</t>
+        </is>
+      </c>
+      <c r="G205" s="5" t="inlineStr">
+        <is>
+          <t>4x6+6</t>
+        </is>
+      </c>
+      <c r="H205" s="5" t="inlineStr">
+        <is>
+          <t>RBS 60"</t>
+        </is>
+      </c>
+      <c r="I205" s="5" t="inlineStr"/>
+      <c r="J205" s="5" t="inlineStr">
+        <is>
+          <t>RPE 8</t>
+        </is>
+      </c>
+      <c r="K205" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/rE8lJ9TxbEQ</t>
+        </is>
+      </c>
+      <c r="L205" s="5" t="inlineStr"/>
       <c r="M205" s="3" t="n"/>
       <c r="N205" s="3" t="n"/>
     </row>
     <row r="206">
-      <c r="A206" s="3" t="n"/>
-      <c r="B206" s="3" t="n"/>
-      <c r="C206" s="3" t="n"/>
-      <c r="D206" s="3" t="n"/>
-      <c r="E206" s="3" t="n"/>
-      <c r="F206" s="3" t="n"/>
-      <c r="G206" s="3" t="n"/>
-      <c r="H206" s="3" t="n"/>
-      <c r="I206" s="3" t="n"/>
-      <c r="J206" s="3" t="n"/>
-      <c r="K206" s="3" t="n"/>
-      <c r="L206" s="3" t="n"/>
+      <c r="A206" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B206" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C206" s="5" t="inlineStr">
+        <is>
+          <t>24 allenamento B</t>
+        </is>
+      </c>
+      <c r="D206" s="5" t="inlineStr">
+        <is>
+          <t>2b</t>
+        </is>
+      </c>
+      <c r="E206" s="5" t="n">
+        <v>119</v>
+      </c>
+      <c r="F206" s="5" t="inlineStr">
+        <is>
+          <t>Super Mario Jump</t>
+        </is>
+      </c>
+      <c r="G206" s="5" t="inlineStr">
+        <is>
+          <t>4x6+6</t>
+        </is>
+      </c>
+      <c r="H206" s="5" t="inlineStr">
+        <is>
+          <t>RBS 60"</t>
+        </is>
+      </c>
+      <c r="I206" s="5" t="inlineStr"/>
+      <c r="J206" s="5" t="inlineStr">
+        <is>
+          <t>jump set | RPE 8</t>
+        </is>
+      </c>
+      <c r="K206" s="5" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/XluivIvnr4k</t>
+        </is>
+      </c>
+      <c r="L206" s="5" t="inlineStr"/>
       <c r="M206" s="3" t="n"/>
       <c r="N206" s="3" t="n"/>
     </row>
     <row r="207">
-      <c r="A207" s="3" t="n"/>
-      <c r="B207" s="3" t="n"/>
-      <c r="C207" s="3" t="n"/>
-      <c r="D207" s="3" t="n"/>
-      <c r="E207" s="3" t="n"/>
-      <c r="F207" s="3" t="n"/>
-      <c r="G207" s="3" t="n"/>
-      <c r="H207" s="3" t="n"/>
-      <c r="I207" s="3" t="n"/>
-      <c r="J207" s="3" t="n"/>
-      <c r="K207" s="3" t="n"/>
-      <c r="L207" s="3" t="n"/>
+      <c r="A207" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B207" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C207" s="5" t="inlineStr">
+        <is>
+          <t>24 allenamento B</t>
+        </is>
+      </c>
+      <c r="D207" s="5" t="inlineStr">
+        <is>
+          <t>3a</t>
+        </is>
+      </c>
+      <c r="E207" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="F207" s="5" t="inlineStr">
+        <is>
+          <t>Coiled Punch iso.</t>
+        </is>
+      </c>
+      <c r="G207" s="5" t="inlineStr">
+        <is>
+          <t>4x8+8</t>
+        </is>
+      </c>
+      <c r="H207" s="5" t="inlineStr"/>
+      <c r="I207" s="5" t="inlineStr"/>
+      <c r="J207" s="5" t="inlineStr">
+        <is>
+          <t>jump set | RPE 8</t>
+        </is>
+      </c>
+      <c r="K207" s="5" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/mifz_6oZJlw</t>
+        </is>
+      </c>
+      <c r="L207" s="5" t="inlineStr"/>
       <c r="M207" s="3" t="n"/>
       <c r="N207" s="3" t="n"/>
     </row>
     <row r="208">
-      <c r="A208" s="3" t="n"/>
-      <c r="B208" s="3" t="n"/>
-      <c r="C208" s="3" t="n"/>
-      <c r="D208" s="3" t="n"/>
-      <c r="E208" s="3" t="n"/>
-      <c r="F208" s="3" t="n"/>
-      <c r="G208" s="3" t="n"/>
-      <c r="H208" s="3" t="n"/>
-      <c r="I208" s="3" t="n"/>
-      <c r="J208" s="3" t="n"/>
-      <c r="K208" s="3" t="n"/>
-      <c r="L208" s="3" t="n"/>
+      <c r="A208" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B208" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C208" s="5" t="inlineStr">
+        <is>
+          <t>24 allenamento B</t>
+        </is>
+      </c>
+      <c r="D208" s="5" t="inlineStr">
+        <is>
+          <t>3b</t>
+        </is>
+      </c>
+      <c r="E208" s="5" t="n">
+        <v>192</v>
+      </c>
+      <c r="F208" s="5" t="inlineStr">
+        <is>
+          <t>Endless rope kneeling pull</t>
+        </is>
+      </c>
+      <c r="G208" s="5" t="inlineStr">
+        <is>
+          <t>4x20"</t>
+        </is>
+      </c>
+      <c r="H208" s="5" t="inlineStr">
+        <is>
+          <t>45"</t>
+        </is>
+      </c>
+      <c r="I208" s="5" t="inlineStr"/>
+      <c r="J208" s="5" t="inlineStr">
+        <is>
+          <t>jump set</t>
+        </is>
+      </c>
+      <c r="K208" s="5" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/sNkK5m4fYi0</t>
+        </is>
+      </c>
+      <c r="L208" s="5" t="inlineStr"/>
       <c r="M208" s="3" t="n"/>
       <c r="N208" s="3" t="n"/>
     </row>
     <row r="209">
-      <c r="A209" s="3" t="n"/>
-      <c r="B209" s="3" t="n"/>
-      <c r="C209" s="3" t="n"/>
-      <c r="D209" s="3" t="n"/>
-      <c r="E209" s="3" t="n"/>
-      <c r="F209" s="3" t="n"/>
-      <c r="G209" s="3" t="n"/>
-      <c r="H209" s="3" t="n"/>
-      <c r="I209" s="3" t="n"/>
-      <c r="J209" s="3" t="n"/>
-      <c r="K209" s="3" t="n"/>
-      <c r="L209" s="3" t="n"/>
+      <c r="A209" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B209" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C209" s="5" t="inlineStr">
+        <is>
+          <t>24 allenamento B</t>
+        </is>
+      </c>
+      <c r="D209" s="5" t="inlineStr">
+        <is>
+          <t>4a</t>
+        </is>
+      </c>
+      <c r="E209" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="F209" s="5" t="inlineStr">
+        <is>
+          <t>Dumbbell Coiled Thruster</t>
+        </is>
+      </c>
+      <c r="G209" s="5" t="inlineStr">
+        <is>
+          <t>x 6+6</t>
+        </is>
+      </c>
+      <c r="H209" s="5" t="inlineStr"/>
+      <c r="I209" s="5" t="inlineStr"/>
+      <c r="J209" s="5" t="inlineStr">
+        <is>
+          <t>AMRAP 12'</t>
+        </is>
+      </c>
+      <c r="K209" s="5" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/nQHKdic83T8</t>
+        </is>
+      </c>
+      <c r="L209" s="5" t="inlineStr"/>
       <c r="M209" s="3" t="n"/>
       <c r="N209" s="3" t="n"/>
     </row>
     <row r="210">
-      <c r="A210" s="3" t="n"/>
-      <c r="B210" s="3" t="n"/>
-      <c r="C210" s="3" t="n"/>
-      <c r="D210" s="3" t="n"/>
-      <c r="E210" s="3" t="n"/>
-      <c r="F210" s="3" t="n"/>
-      <c r="G210" s="3" t="n"/>
-      <c r="H210" s="3" t="n"/>
-      <c r="I210" s="3" t="n"/>
-      <c r="J210" s="3" t="n"/>
-      <c r="K210" s="3" t="n"/>
-      <c r="L210" s="3" t="n"/>
+      <c r="A210" s="5" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B210" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C210" s="5" t="inlineStr">
+        <is>
+          <t>24 allenamento B</t>
+        </is>
+      </c>
+      <c r="D210" s="5" t="inlineStr">
+        <is>
+          <t>4b</t>
+        </is>
+      </c>
+      <c r="E210" s="5" t="n">
+        <v>228</v>
+      </c>
+      <c r="F210" s="5" t="inlineStr">
+        <is>
+          <t>COMBO Side kick trough + Sprawl</t>
+        </is>
+      </c>
+      <c r="G210" s="5" t="inlineStr">
+        <is>
+          <t>x 8</t>
+        </is>
+      </c>
+      <c r="H210" s="5" t="inlineStr"/>
+      <c r="I210" s="5" t="inlineStr"/>
+      <c r="J210" s="5" t="inlineStr">
+        <is>
+          <t>AMRAP 12'</t>
+        </is>
+      </c>
+      <c r="K210" s="5" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/iRJEq6FnzxI</t>
+        </is>
+      </c>
+      <c r="L210" s="5" t="inlineStr"/>
       <c r="M210" s="3" t="n"/>
       <c r="N210" s="3" t="n"/>
     </row>
     <row r="211">
-      <c r="A211" s="3" t="n"/>
-      <c r="B211" s="3" t="n"/>
-      <c r="C211" s="3" t="n"/>
-      <c r="D211" s="3" t="n"/>
-      <c r="E211" s="3" t="n"/>
-      <c r="F211" s="3" t="n"/>
-      <c r="G211" s="3" t="n"/>
-      <c r="H211" s="3" t="n"/>
-      <c r="I211" s="3" t="n"/>
-      <c r="J211" s="3" t="n"/>
-      <c r="K211" s="3" t="n"/>
-      <c r="L211" s="3" t="n"/>
+      <c r="A211" s="6" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="B211" s="6" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="C211" s="6" t="inlineStr">
+        <is>
+          <t>24 allenamento B</t>
+        </is>
+      </c>
+      <c r="D211" s="6" t="inlineStr">
+        <is>
+          <t>4c</t>
+        </is>
+      </c>
+      <c r="E211" s="6" t="n">
+        <v>233</v>
+      </c>
+      <c r="F211" s="6" t="inlineStr">
+        <is>
+          <t>rotation slam</t>
+        </is>
+      </c>
+      <c r="G211" s="6" t="inlineStr">
+        <is>
+          <t>x 10</t>
+        </is>
+      </c>
+      <c r="H211" s="6" t="inlineStr"/>
+      <c r="I211" s="6" t="inlineStr"/>
+      <c r="J211" s="6" t="inlineStr">
+        <is>
+          <t>AMRAP 12'</t>
+        </is>
+      </c>
+      <c r="K211" s="6" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/HwYENrEDFqY</t>
+        </is>
+      </c>
+      <c r="L211" s="6" t="inlineStr"/>
       <c r="M211" s="3" t="n"/>
       <c r="N211" s="3" t="n"/>
     </row>
@@ -34541,6 +36750,806 @@
       <c r="M249" s="3" t="n"/>
       <c r="N249" s="3" t="n"/>
     </row>
+    <row r="250">
+      <c r="A250" s="3" t="n"/>
+      <c r="B250" s="3" t="n"/>
+      <c r="C250" s="3" t="n"/>
+      <c r="D250" s="3" t="n"/>
+      <c r="E250" s="3" t="n"/>
+      <c r="F250" s="3" t="n"/>
+      <c r="G250" s="3" t="n"/>
+      <c r="H250" s="3" t="n"/>
+      <c r="I250" s="3" t="n"/>
+      <c r="J250" s="3" t="n"/>
+      <c r="K250" s="3" t="n"/>
+      <c r="L250" s="3" t="n"/>
+      <c r="M250" s="3" t="n"/>
+      <c r="N250" s="3" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="3" t="n"/>
+      <c r="B251" s="3" t="n"/>
+      <c r="C251" s="3" t="n"/>
+      <c r="D251" s="3" t="n"/>
+      <c r="E251" s="3" t="n"/>
+      <c r="F251" s="3" t="n"/>
+      <c r="G251" s="3" t="n"/>
+      <c r="H251" s="3" t="n"/>
+      <c r="I251" s="3" t="n"/>
+      <c r="J251" s="3" t="n"/>
+      <c r="K251" s="3" t="n"/>
+      <c r="L251" s="3" t="n"/>
+      <c r="M251" s="3" t="n"/>
+      <c r="N251" s="3" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="3" t="n"/>
+      <c r="B252" s="3" t="n"/>
+      <c r="C252" s="3" t="n"/>
+      <c r="D252" s="3" t="n"/>
+      <c r="E252" s="3" t="n"/>
+      <c r="F252" s="3" t="n"/>
+      <c r="G252" s="3" t="n"/>
+      <c r="H252" s="3" t="n"/>
+      <c r="I252" s="3" t="n"/>
+      <c r="J252" s="3" t="n"/>
+      <c r="K252" s="3" t="n"/>
+      <c r="L252" s="3" t="n"/>
+      <c r="M252" s="3" t="n"/>
+      <c r="N252" s="3" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="3" t="n"/>
+      <c r="B253" s="3" t="n"/>
+      <c r="C253" s="3" t="n"/>
+      <c r="D253" s="3" t="n"/>
+      <c r="E253" s="3" t="n"/>
+      <c r="F253" s="3" t="n"/>
+      <c r="G253" s="3" t="n"/>
+      <c r="H253" s="3" t="n"/>
+      <c r="I253" s="3" t="n"/>
+      <c r="J253" s="3" t="n"/>
+      <c r="K253" s="3" t="n"/>
+      <c r="L253" s="3" t="n"/>
+      <c r="M253" s="3" t="n"/>
+      <c r="N253" s="3" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="3" t="n"/>
+      <c r="B254" s="3" t="n"/>
+      <c r="C254" s="3" t="n"/>
+      <c r="D254" s="3" t="n"/>
+      <c r="E254" s="3" t="n"/>
+      <c r="F254" s="3" t="n"/>
+      <c r="G254" s="3" t="n"/>
+      <c r="H254" s="3" t="n"/>
+      <c r="I254" s="3" t="n"/>
+      <c r="J254" s="3" t="n"/>
+      <c r="K254" s="3" t="n"/>
+      <c r="L254" s="3" t="n"/>
+      <c r="M254" s="3" t="n"/>
+      <c r="N254" s="3" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="3" t="n"/>
+      <c r="B255" s="3" t="n"/>
+      <c r="C255" s="3" t="n"/>
+      <c r="D255" s="3" t="n"/>
+      <c r="E255" s="3" t="n"/>
+      <c r="F255" s="3" t="n"/>
+      <c r="G255" s="3" t="n"/>
+      <c r="H255" s="3" t="n"/>
+      <c r="I255" s="3" t="n"/>
+      <c r="J255" s="3" t="n"/>
+      <c r="K255" s="3" t="n"/>
+      <c r="L255" s="3" t="n"/>
+      <c r="M255" s="3" t="n"/>
+      <c r="N255" s="3" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="3" t="n"/>
+      <c r="B256" s="3" t="n"/>
+      <c r="C256" s="3" t="n"/>
+      <c r="D256" s="3" t="n"/>
+      <c r="E256" s="3" t="n"/>
+      <c r="F256" s="3" t="n"/>
+      <c r="G256" s="3" t="n"/>
+      <c r="H256" s="3" t="n"/>
+      <c r="I256" s="3" t="n"/>
+      <c r="J256" s="3" t="n"/>
+      <c r="K256" s="3" t="n"/>
+      <c r="L256" s="3" t="n"/>
+      <c r="M256" s="3" t="n"/>
+      <c r="N256" s="3" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="3" t="n"/>
+      <c r="B257" s="3" t="n"/>
+      <c r="C257" s="3" t="n"/>
+      <c r="D257" s="3" t="n"/>
+      <c r="E257" s="3" t="n"/>
+      <c r="F257" s="3" t="n"/>
+      <c r="G257" s="3" t="n"/>
+      <c r="H257" s="3" t="n"/>
+      <c r="I257" s="3" t="n"/>
+      <c r="J257" s="3" t="n"/>
+      <c r="K257" s="3" t="n"/>
+      <c r="L257" s="3" t="n"/>
+      <c r="M257" s="3" t="n"/>
+      <c r="N257" s="3" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="3" t="n"/>
+      <c r="B258" s="3" t="n"/>
+      <c r="C258" s="3" t="n"/>
+      <c r="D258" s="3" t="n"/>
+      <c r="E258" s="3" t="n"/>
+      <c r="F258" s="3" t="n"/>
+      <c r="G258" s="3" t="n"/>
+      <c r="H258" s="3" t="n"/>
+      <c r="I258" s="3" t="n"/>
+      <c r="J258" s="3" t="n"/>
+      <c r="K258" s="3" t="n"/>
+      <c r="L258" s="3" t="n"/>
+      <c r="M258" s="3" t="n"/>
+      <c r="N258" s="3" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="3" t="n"/>
+      <c r="B259" s="3" t="n"/>
+      <c r="C259" s="3" t="n"/>
+      <c r="D259" s="3" t="n"/>
+      <c r="E259" s="3" t="n"/>
+      <c r="F259" s="3" t="n"/>
+      <c r="G259" s="3" t="n"/>
+      <c r="H259" s="3" t="n"/>
+      <c r="I259" s="3" t="n"/>
+      <c r="J259" s="3" t="n"/>
+      <c r="K259" s="3" t="n"/>
+      <c r="L259" s="3" t="n"/>
+      <c r="M259" s="3" t="n"/>
+      <c r="N259" s="3" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="3" t="n"/>
+      <c r="B260" s="3" t="n"/>
+      <c r="C260" s="3" t="n"/>
+      <c r="D260" s="3" t="n"/>
+      <c r="E260" s="3" t="n"/>
+      <c r="F260" s="3" t="n"/>
+      <c r="G260" s="3" t="n"/>
+      <c r="H260" s="3" t="n"/>
+      <c r="I260" s="3" t="n"/>
+      <c r="J260" s="3" t="n"/>
+      <c r="K260" s="3" t="n"/>
+      <c r="L260" s="3" t="n"/>
+      <c r="M260" s="3" t="n"/>
+      <c r="N260" s="3" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="3" t="n"/>
+      <c r="B261" s="3" t="n"/>
+      <c r="C261" s="3" t="n"/>
+      <c r="D261" s="3" t="n"/>
+      <c r="E261" s="3" t="n"/>
+      <c r="F261" s="3" t="n"/>
+      <c r="G261" s="3" t="n"/>
+      <c r="H261" s="3" t="n"/>
+      <c r="I261" s="3" t="n"/>
+      <c r="J261" s="3" t="n"/>
+      <c r="K261" s="3" t="n"/>
+      <c r="L261" s="3" t="n"/>
+      <c r="M261" s="3" t="n"/>
+      <c r="N261" s="3" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="3" t="n"/>
+      <c r="B262" s="3" t="n"/>
+      <c r="C262" s="3" t="n"/>
+      <c r="D262" s="3" t="n"/>
+      <c r="E262" s="3" t="n"/>
+      <c r="F262" s="3" t="n"/>
+      <c r="G262" s="3" t="n"/>
+      <c r="H262" s="3" t="n"/>
+      <c r="I262" s="3" t="n"/>
+      <c r="J262" s="3" t="n"/>
+      <c r="K262" s="3" t="n"/>
+      <c r="L262" s="3" t="n"/>
+      <c r="M262" s="3" t="n"/>
+      <c r="N262" s="3" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="3" t="n"/>
+      <c r="B263" s="3" t="n"/>
+      <c r="C263" s="3" t="n"/>
+      <c r="D263" s="3" t="n"/>
+      <c r="E263" s="3" t="n"/>
+      <c r="F263" s="3" t="n"/>
+      <c r="G263" s="3" t="n"/>
+      <c r="H263" s="3" t="n"/>
+      <c r="I263" s="3" t="n"/>
+      <c r="J263" s="3" t="n"/>
+      <c r="K263" s="3" t="n"/>
+      <c r="L263" s="3" t="n"/>
+      <c r="M263" s="3" t="n"/>
+      <c r="N263" s="3" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="3" t="n"/>
+      <c r="B264" s="3" t="n"/>
+      <c r="C264" s="3" t="n"/>
+      <c r="D264" s="3" t="n"/>
+      <c r="E264" s="3" t="n"/>
+      <c r="F264" s="3" t="n"/>
+      <c r="G264" s="3" t="n"/>
+      <c r="H264" s="3" t="n"/>
+      <c r="I264" s="3" t="n"/>
+      <c r="J264" s="3" t="n"/>
+      <c r="K264" s="3" t="n"/>
+      <c r="L264" s="3" t="n"/>
+      <c r="M264" s="3" t="n"/>
+      <c r="N264" s="3" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="3" t="n"/>
+      <c r="B265" s="3" t="n"/>
+      <c r="C265" s="3" t="n"/>
+      <c r="D265" s="3" t="n"/>
+      <c r="E265" s="3" t="n"/>
+      <c r="F265" s="3" t="n"/>
+      <c r="G265" s="3" t="n"/>
+      <c r="H265" s="3" t="n"/>
+      <c r="I265" s="3" t="n"/>
+      <c r="J265" s="3" t="n"/>
+      <c r="K265" s="3" t="n"/>
+      <c r="L265" s="3" t="n"/>
+      <c r="M265" s="3" t="n"/>
+      <c r="N265" s="3" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="3" t="n"/>
+      <c r="B266" s="3" t="n"/>
+      <c r="C266" s="3" t="n"/>
+      <c r="D266" s="3" t="n"/>
+      <c r="E266" s="3" t="n"/>
+      <c r="F266" s="3" t="n"/>
+      <c r="G266" s="3" t="n"/>
+      <c r="H266" s="3" t="n"/>
+      <c r="I266" s="3" t="n"/>
+      <c r="J266" s="3" t="n"/>
+      <c r="K266" s="3" t="n"/>
+      <c r="L266" s="3" t="n"/>
+      <c r="M266" s="3" t="n"/>
+      <c r="N266" s="3" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="3" t="n"/>
+      <c r="B267" s="3" t="n"/>
+      <c r="C267" s="3" t="n"/>
+      <c r="D267" s="3" t="n"/>
+      <c r="E267" s="3" t="n"/>
+      <c r="F267" s="3" t="n"/>
+      <c r="G267" s="3" t="n"/>
+      <c r="H267" s="3" t="n"/>
+      <c r="I267" s="3" t="n"/>
+      <c r="J267" s="3" t="n"/>
+      <c r="K267" s="3" t="n"/>
+      <c r="L267" s="3" t="n"/>
+      <c r="M267" s="3" t="n"/>
+      <c r="N267" s="3" t="n"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="3" t="n"/>
+      <c r="B268" s="3" t="n"/>
+      <c r="C268" s="3" t="n"/>
+      <c r="D268" s="3" t="n"/>
+      <c r="E268" s="3" t="n"/>
+      <c r="F268" s="3" t="n"/>
+      <c r="G268" s="3" t="n"/>
+      <c r="H268" s="3" t="n"/>
+      <c r="I268" s="3" t="n"/>
+      <c r="J268" s="3" t="n"/>
+      <c r="K268" s="3" t="n"/>
+      <c r="L268" s="3" t="n"/>
+      <c r="M268" s="3" t="n"/>
+      <c r="N268" s="3" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="3" t="n"/>
+      <c r="B269" s="3" t="n"/>
+      <c r="C269" s="3" t="n"/>
+      <c r="D269" s="3" t="n"/>
+      <c r="E269" s="3" t="n"/>
+      <c r="F269" s="3" t="n"/>
+      <c r="G269" s="3" t="n"/>
+      <c r="H269" s="3" t="n"/>
+      <c r="I269" s="3" t="n"/>
+      <c r="J269" s="3" t="n"/>
+      <c r="K269" s="3" t="n"/>
+      <c r="L269" s="3" t="n"/>
+      <c r="M269" s="3" t="n"/>
+      <c r="N269" s="3" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="3" t="n"/>
+      <c r="B270" s="3" t="n"/>
+      <c r="C270" s="3" t="n"/>
+      <c r="D270" s="3" t="n"/>
+      <c r="E270" s="3" t="n"/>
+      <c r="F270" s="3" t="n"/>
+      <c r="G270" s="3" t="n"/>
+      <c r="H270" s="3" t="n"/>
+      <c r="I270" s="3" t="n"/>
+      <c r="J270" s="3" t="n"/>
+      <c r="K270" s="3" t="n"/>
+      <c r="L270" s="3" t="n"/>
+      <c r="M270" s="3" t="n"/>
+      <c r="N270" s="3" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="3" t="n"/>
+      <c r="B271" s="3" t="n"/>
+      <c r="C271" s="3" t="n"/>
+      <c r="D271" s="3" t="n"/>
+      <c r="E271" s="3" t="n"/>
+      <c r="F271" s="3" t="n"/>
+      <c r="G271" s="3" t="n"/>
+      <c r="H271" s="3" t="n"/>
+      <c r="I271" s="3" t="n"/>
+      <c r="J271" s="3" t="n"/>
+      <c r="K271" s="3" t="n"/>
+      <c r="L271" s="3" t="n"/>
+      <c r="M271" s="3" t="n"/>
+      <c r="N271" s="3" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="3" t="n"/>
+      <c r="B272" s="3" t="n"/>
+      <c r="C272" s="3" t="n"/>
+      <c r="D272" s="3" t="n"/>
+      <c r="E272" s="3" t="n"/>
+      <c r="F272" s="3" t="n"/>
+      <c r="G272" s="3" t="n"/>
+      <c r="H272" s="3" t="n"/>
+      <c r="I272" s="3" t="n"/>
+      <c r="J272" s="3" t="n"/>
+      <c r="K272" s="3" t="n"/>
+      <c r="L272" s="3" t="n"/>
+      <c r="M272" s="3" t="n"/>
+      <c r="N272" s="3" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="3" t="n"/>
+      <c r="B273" s="3" t="n"/>
+      <c r="C273" s="3" t="n"/>
+      <c r="D273" s="3" t="n"/>
+      <c r="E273" s="3" t="n"/>
+      <c r="F273" s="3" t="n"/>
+      <c r="G273" s="3" t="n"/>
+      <c r="H273" s="3" t="n"/>
+      <c r="I273" s="3" t="n"/>
+      <c r="J273" s="3" t="n"/>
+      <c r="K273" s="3" t="n"/>
+      <c r="L273" s="3" t="n"/>
+      <c r="M273" s="3" t="n"/>
+      <c r="N273" s="3" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="3" t="n"/>
+      <c r="B274" s="3" t="n"/>
+      <c r="C274" s="3" t="n"/>
+      <c r="D274" s="3" t="n"/>
+      <c r="E274" s="3" t="n"/>
+      <c r="F274" s="3" t="n"/>
+      <c r="G274" s="3" t="n"/>
+      <c r="H274" s="3" t="n"/>
+      <c r="I274" s="3" t="n"/>
+      <c r="J274" s="3" t="n"/>
+      <c r="K274" s="3" t="n"/>
+      <c r="L274" s="3" t="n"/>
+      <c r="M274" s="3" t="n"/>
+      <c r="N274" s="3" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="3" t="n"/>
+      <c r="B275" s="3" t="n"/>
+      <c r="C275" s="3" t="n"/>
+      <c r="D275" s="3" t="n"/>
+      <c r="E275" s="3" t="n"/>
+      <c r="F275" s="3" t="n"/>
+      <c r="G275" s="3" t="n"/>
+      <c r="H275" s="3" t="n"/>
+      <c r="I275" s="3" t="n"/>
+      <c r="J275" s="3" t="n"/>
+      <c r="K275" s="3" t="n"/>
+      <c r="L275" s="3" t="n"/>
+      <c r="M275" s="3" t="n"/>
+      <c r="N275" s="3" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="3" t="n"/>
+      <c r="B276" s="3" t="n"/>
+      <c r="C276" s="3" t="n"/>
+      <c r="D276" s="3" t="n"/>
+      <c r="E276" s="3" t="n"/>
+      <c r="F276" s="3" t="n"/>
+      <c r="G276" s="3" t="n"/>
+      <c r="H276" s="3" t="n"/>
+      <c r="I276" s="3" t="n"/>
+      <c r="J276" s="3" t="n"/>
+      <c r="K276" s="3" t="n"/>
+      <c r="L276" s="3" t="n"/>
+      <c r="M276" s="3" t="n"/>
+      <c r="N276" s="3" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="3" t="n"/>
+      <c r="B277" s="3" t="n"/>
+      <c r="C277" s="3" t="n"/>
+      <c r="D277" s="3" t="n"/>
+      <c r="E277" s="3" t="n"/>
+      <c r="F277" s="3" t="n"/>
+      <c r="G277" s="3" t="n"/>
+      <c r="H277" s="3" t="n"/>
+      <c r="I277" s="3" t="n"/>
+      <c r="J277" s="3" t="n"/>
+      <c r="K277" s="3" t="n"/>
+      <c r="L277" s="3" t="n"/>
+      <c r="M277" s="3" t="n"/>
+      <c r="N277" s="3" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="3" t="n"/>
+      <c r="B278" s="3" t="n"/>
+      <c r="C278" s="3" t="n"/>
+      <c r="D278" s="3" t="n"/>
+      <c r="E278" s="3" t="n"/>
+      <c r="F278" s="3" t="n"/>
+      <c r="G278" s="3" t="n"/>
+      <c r="H278" s="3" t="n"/>
+      <c r="I278" s="3" t="n"/>
+      <c r="J278" s="3" t="n"/>
+      <c r="K278" s="3" t="n"/>
+      <c r="L278" s="3" t="n"/>
+      <c r="M278" s="3" t="n"/>
+      <c r="N278" s="3" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="3" t="n"/>
+      <c r="B279" s="3" t="n"/>
+      <c r="C279" s="3" t="n"/>
+      <c r="D279" s="3" t="n"/>
+      <c r="E279" s="3" t="n"/>
+      <c r="F279" s="3" t="n"/>
+      <c r="G279" s="3" t="n"/>
+      <c r="H279" s="3" t="n"/>
+      <c r="I279" s="3" t="n"/>
+      <c r="J279" s="3" t="n"/>
+      <c r="K279" s="3" t="n"/>
+      <c r="L279" s="3" t="n"/>
+      <c r="M279" s="3" t="n"/>
+      <c r="N279" s="3" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="3" t="n"/>
+      <c r="B280" s="3" t="n"/>
+      <c r="C280" s="3" t="n"/>
+      <c r="D280" s="3" t="n"/>
+      <c r="E280" s="3" t="n"/>
+      <c r="F280" s="3" t="n"/>
+      <c r="G280" s="3" t="n"/>
+      <c r="H280" s="3" t="n"/>
+      <c r="I280" s="3" t="n"/>
+      <c r="J280" s="3" t="n"/>
+      <c r="K280" s="3" t="n"/>
+      <c r="L280" s="3" t="n"/>
+      <c r="M280" s="3" t="n"/>
+      <c r="N280" s="3" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="3" t="n"/>
+      <c r="B281" s="3" t="n"/>
+      <c r="C281" s="3" t="n"/>
+      <c r="D281" s="3" t="n"/>
+      <c r="E281" s="3" t="n"/>
+      <c r="F281" s="3" t="n"/>
+      <c r="G281" s="3" t="n"/>
+      <c r="H281" s="3" t="n"/>
+      <c r="I281" s="3" t="n"/>
+      <c r="J281" s="3" t="n"/>
+      <c r="K281" s="3" t="n"/>
+      <c r="L281" s="3" t="n"/>
+      <c r="M281" s="3" t="n"/>
+      <c r="N281" s="3" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="3" t="n"/>
+      <c r="B282" s="3" t="n"/>
+      <c r="C282" s="3" t="n"/>
+      <c r="D282" s="3" t="n"/>
+      <c r="E282" s="3" t="n"/>
+      <c r="F282" s="3" t="n"/>
+      <c r="G282" s="3" t="n"/>
+      <c r="H282" s="3" t="n"/>
+      <c r="I282" s="3" t="n"/>
+      <c r="J282" s="3" t="n"/>
+      <c r="K282" s="3" t="n"/>
+      <c r="L282" s="3" t="n"/>
+      <c r="M282" s="3" t="n"/>
+      <c r="N282" s="3" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="3" t="n"/>
+      <c r="B283" s="3" t="n"/>
+      <c r="C283" s="3" t="n"/>
+      <c r="D283" s="3" t="n"/>
+      <c r="E283" s="3" t="n"/>
+      <c r="F283" s="3" t="n"/>
+      <c r="G283" s="3" t="n"/>
+      <c r="H283" s="3" t="n"/>
+      <c r="I283" s="3" t="n"/>
+      <c r="J283" s="3" t="n"/>
+      <c r="K283" s="3" t="n"/>
+      <c r="L283" s="3" t="n"/>
+      <c r="M283" s="3" t="n"/>
+      <c r="N283" s="3" t="n"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="3" t="n"/>
+      <c r="B284" s="3" t="n"/>
+      <c r="C284" s="3" t="n"/>
+      <c r="D284" s="3" t="n"/>
+      <c r="E284" s="3" t="n"/>
+      <c r="F284" s="3" t="n"/>
+      <c r="G284" s="3" t="n"/>
+      <c r="H284" s="3" t="n"/>
+      <c r="I284" s="3" t="n"/>
+      <c r="J284" s="3" t="n"/>
+      <c r="K284" s="3" t="n"/>
+      <c r="L284" s="3" t="n"/>
+      <c r="M284" s="3" t="n"/>
+      <c r="N284" s="3" t="n"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="3" t="n"/>
+      <c r="B285" s="3" t="n"/>
+      <c r="C285" s="3" t="n"/>
+      <c r="D285" s="3" t="n"/>
+      <c r="E285" s="3" t="n"/>
+      <c r="F285" s="3" t="n"/>
+      <c r="G285" s="3" t="n"/>
+      <c r="H285" s="3" t="n"/>
+      <c r="I285" s="3" t="n"/>
+      <c r="J285" s="3" t="n"/>
+      <c r="K285" s="3" t="n"/>
+      <c r="L285" s="3" t="n"/>
+      <c r="M285" s="3" t="n"/>
+      <c r="N285" s="3" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="3" t="n"/>
+      <c r="B286" s="3" t="n"/>
+      <c r="C286" s="3" t="n"/>
+      <c r="D286" s="3" t="n"/>
+      <c r="E286" s="3" t="n"/>
+      <c r="F286" s="3" t="n"/>
+      <c r="G286" s="3" t="n"/>
+      <c r="H286" s="3" t="n"/>
+      <c r="I286" s="3" t="n"/>
+      <c r="J286" s="3" t="n"/>
+      <c r="K286" s="3" t="n"/>
+      <c r="L286" s="3" t="n"/>
+      <c r="M286" s="3" t="n"/>
+      <c r="N286" s="3" t="n"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="3" t="n"/>
+      <c r="B287" s="3" t="n"/>
+      <c r="C287" s="3" t="n"/>
+      <c r="D287" s="3" t="n"/>
+      <c r="E287" s="3" t="n"/>
+      <c r="F287" s="3" t="n"/>
+      <c r="G287" s="3" t="n"/>
+      <c r="H287" s="3" t="n"/>
+      <c r="I287" s="3" t="n"/>
+      <c r="J287" s="3" t="n"/>
+      <c r="K287" s="3" t="n"/>
+      <c r="L287" s="3" t="n"/>
+      <c r="M287" s="3" t="n"/>
+      <c r="N287" s="3" t="n"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="3" t="n"/>
+      <c r="B288" s="3" t="n"/>
+      <c r="C288" s="3" t="n"/>
+      <c r="D288" s="3" t="n"/>
+      <c r="E288" s="3" t="n"/>
+      <c r="F288" s="3" t="n"/>
+      <c r="G288" s="3" t="n"/>
+      <c r="H288" s="3" t="n"/>
+      <c r="I288" s="3" t="n"/>
+      <c r="J288" s="3" t="n"/>
+      <c r="K288" s="3" t="n"/>
+      <c r="L288" s="3" t="n"/>
+      <c r="M288" s="3" t="n"/>
+      <c r="N288" s="3" t="n"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="3" t="n"/>
+      <c r="B289" s="3" t="n"/>
+      <c r="C289" s="3" t="n"/>
+      <c r="D289" s="3" t="n"/>
+      <c r="E289" s="3" t="n"/>
+      <c r="F289" s="3" t="n"/>
+      <c r="G289" s="3" t="n"/>
+      <c r="H289" s="3" t="n"/>
+      <c r="I289" s="3" t="n"/>
+      <c r="J289" s="3" t="n"/>
+      <c r="K289" s="3" t="n"/>
+      <c r="L289" s="3" t="n"/>
+      <c r="M289" s="3" t="n"/>
+      <c r="N289" s="3" t="n"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="3" t="n"/>
+      <c r="B290" s="3" t="n"/>
+      <c r="C290" s="3" t="n"/>
+      <c r="D290" s="3" t="n"/>
+      <c r="E290" s="3" t="n"/>
+      <c r="F290" s="3" t="n"/>
+      <c r="G290" s="3" t="n"/>
+      <c r="H290" s="3" t="n"/>
+      <c r="I290" s="3" t="n"/>
+      <c r="J290" s="3" t="n"/>
+      <c r="K290" s="3" t="n"/>
+      <c r="L290" s="3" t="n"/>
+      <c r="M290" s="3" t="n"/>
+      <c r="N290" s="3" t="n"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="3" t="n"/>
+      <c r="B291" s="3" t="n"/>
+      <c r="C291" s="3" t="n"/>
+      <c r="D291" s="3" t="n"/>
+      <c r="E291" s="3" t="n"/>
+      <c r="F291" s="3" t="n"/>
+      <c r="G291" s="3" t="n"/>
+      <c r="H291" s="3" t="n"/>
+      <c r="I291" s="3" t="n"/>
+      <c r="J291" s="3" t="n"/>
+      <c r="K291" s="3" t="n"/>
+      <c r="L291" s="3" t="n"/>
+      <c r="M291" s="3" t="n"/>
+      <c r="N291" s="3" t="n"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="3" t="n"/>
+      <c r="B292" s="3" t="n"/>
+      <c r="C292" s="3" t="n"/>
+      <c r="D292" s="3" t="n"/>
+      <c r="E292" s="3" t="n"/>
+      <c r="F292" s="3" t="n"/>
+      <c r="G292" s="3" t="n"/>
+      <c r="H292" s="3" t="n"/>
+      <c r="I292" s="3" t="n"/>
+      <c r="J292" s="3" t="n"/>
+      <c r="K292" s="3" t="n"/>
+      <c r="L292" s="3" t="n"/>
+      <c r="M292" s="3" t="n"/>
+      <c r="N292" s="3" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="3" t="n"/>
+      <c r="B293" s="3" t="n"/>
+      <c r="C293" s="3" t="n"/>
+      <c r="D293" s="3" t="n"/>
+      <c r="E293" s="3" t="n"/>
+      <c r="F293" s="3" t="n"/>
+      <c r="G293" s="3" t="n"/>
+      <c r="H293" s="3" t="n"/>
+      <c r="I293" s="3" t="n"/>
+      <c r="J293" s="3" t="n"/>
+      <c r="K293" s="3" t="n"/>
+      <c r="L293" s="3" t="n"/>
+      <c r="M293" s="3" t="n"/>
+      <c r="N293" s="3" t="n"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="3" t="n"/>
+      <c r="B294" s="3" t="n"/>
+      <c r="C294" s="3" t="n"/>
+      <c r="D294" s="3" t="n"/>
+      <c r="E294" s="3" t="n"/>
+      <c r="F294" s="3" t="n"/>
+      <c r="G294" s="3" t="n"/>
+      <c r="H294" s="3" t="n"/>
+      <c r="I294" s="3" t="n"/>
+      <c r="J294" s="3" t="n"/>
+      <c r="K294" s="3" t="n"/>
+      <c r="L294" s="3" t="n"/>
+      <c r="M294" s="3" t="n"/>
+      <c r="N294" s="3" t="n"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="3" t="n"/>
+      <c r="B295" s="3" t="n"/>
+      <c r="C295" s="3" t="n"/>
+      <c r="D295" s="3" t="n"/>
+      <c r="E295" s="3" t="n"/>
+      <c r="F295" s="3" t="n"/>
+      <c r="G295" s="3" t="n"/>
+      <c r="H295" s="3" t="n"/>
+      <c r="I295" s="3" t="n"/>
+      <c r="J295" s="3" t="n"/>
+      <c r="K295" s="3" t="n"/>
+      <c r="L295" s="3" t="n"/>
+      <c r="M295" s="3" t="n"/>
+      <c r="N295" s="3" t="n"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="3" t="n"/>
+      <c r="B296" s="3" t="n"/>
+      <c r="C296" s="3" t="n"/>
+      <c r="D296" s="3" t="n"/>
+      <c r="E296" s="3" t="n"/>
+      <c r="F296" s="3" t="n"/>
+      <c r="G296" s="3" t="n"/>
+      <c r="H296" s="3" t="n"/>
+      <c r="I296" s="3" t="n"/>
+      <c r="J296" s="3" t="n"/>
+      <c r="K296" s="3" t="n"/>
+      <c r="L296" s="3" t="n"/>
+      <c r="M296" s="3" t="n"/>
+      <c r="N296" s="3" t="n"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="3" t="n"/>
+      <c r="B297" s="3" t="n"/>
+      <c r="C297" s="3" t="n"/>
+      <c r="D297" s="3" t="n"/>
+      <c r="E297" s="3" t="n"/>
+      <c r="F297" s="3" t="n"/>
+      <c r="G297" s="3" t="n"/>
+      <c r="H297" s="3" t="n"/>
+      <c r="I297" s="3" t="n"/>
+      <c r="J297" s="3" t="n"/>
+      <c r="K297" s="3" t="n"/>
+      <c r="L297" s="3" t="n"/>
+      <c r="M297" s="3" t="n"/>
+      <c r="N297" s="3" t="n"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="3" t="n"/>
+      <c r="B298" s="3" t="n"/>
+      <c r="C298" s="3" t="n"/>
+      <c r="D298" s="3" t="n"/>
+      <c r="E298" s="3" t="n"/>
+      <c r="F298" s="3" t="n"/>
+      <c r="G298" s="3" t="n"/>
+      <c r="H298" s="3" t="n"/>
+      <c r="I298" s="3" t="n"/>
+      <c r="J298" s="3" t="n"/>
+      <c r="K298" s="3" t="n"/>
+      <c r="L298" s="3" t="n"/>
+      <c r="M298" s="3" t="n"/>
+      <c r="N298" s="3" t="n"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="3" t="n"/>
+      <c r="B299" s="3" t="n"/>
+      <c r="C299" s="3" t="n"/>
+      <c r="D299" s="3" t="n"/>
+      <c r="E299" s="3" t="n"/>
+      <c r="F299" s="3" t="n"/>
+      <c r="G299" s="3" t="n"/>
+      <c r="H299" s="3" t="n"/>
+      <c r="I299" s="3" t="n"/>
+      <c r="J299" s="3" t="n"/>
+      <c r="K299" s="3" t="n"/>
+      <c r="L299" s="3" t="n"/>
+      <c r="M299" s="3" t="n"/>
+      <c r="N299" s="3" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PRO database esercizi.xlsx
+++ b/PRO database esercizi.xlsx
@@ -36158,7 +36158,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>3x8+8</t>
+          <t>3x40"+40"</t>
         </is>
       </c>
       <c r="H212" s="3" t="inlineStr"/>
@@ -36199,32 +36199,28 @@
         </is>
       </c>
       <c r="E213" s="3" t="n">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>Push the wall squat</t>
+          <t>Dumbbell biker's squat</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>3x8</t>
-        </is>
-      </c>
-      <c r="H213" s="3" t="inlineStr">
-        <is>
-          <t>45"</t>
-        </is>
-      </c>
+          <t>3x12</t>
+        </is>
+      </c>
+      <c r="H213" s="3" t="inlineStr"/>
       <c r="I213" s="3" t="inlineStr"/>
       <c r="J213" s="3" t="inlineStr">
         <is>
-          <t>jump set</t>
+          <t>jump set | usare un manubrio di peso adeguato al riscaldamento</t>
         </is>
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/3a_ww0jGYsM</t>
+          <t>https://youtu.be/jqhow36DTdg</t>
         </is>
       </c>
       <c r="L213" s="3" t="inlineStr"/>
@@ -36262,7 +36258,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>4x5+5</t>
+          <t>4x10</t>
         </is>
       </c>
       <c r="H214" s="3" t="inlineStr">
@@ -36273,7 +36269,7 @@
       <c r="I214" s="3" t="inlineStr"/>
       <c r="J214" s="3" t="inlineStr">
         <is>
-          <t>RPE 8.5</t>
+          <t>RPE 8.5 | fare un corretto avvicinamento</t>
         </is>
       </c>
       <c r="K214" s="3" t="inlineStr">
@@ -36407,7 +36403,7 @@
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
-          <t>4a</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E217" s="3" t="n">
@@ -36420,14 +36416,14 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>3x6+6</t>
+          <t>studio progressivo 5-10 minuti</t>
         </is>
       </c>
       <c r="H217" s="3" t="inlineStr"/>
       <c r="I217" s="3" t="inlineStr"/>
       <c r="J217" s="3" t="inlineStr">
         <is>
-          <t>circuito (3 round)</t>
+          <t>Dal momento che è un esercizio di impatto e affrontato per la prima volta, viene richiesto un lavoro preventivo di studio progressivo fino a realizzare il movimento intero e proseguito.</t>
         </is>
       </c>
       <c r="K217" s="3" t="inlineStr">
@@ -36457,7 +36453,7 @@
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>4b</t>
+          <t>5a</t>
         </is>
       </c>
       <c r="E218" s="3" t="n">
@@ -36477,7 +36473,7 @@
       <c r="I218" s="3" t="inlineStr"/>
       <c r="J218" s="3" t="inlineStr">
         <is>
-          <t>circuito (3 round)</t>
+          <t>jump set</t>
         </is>
       </c>
       <c r="K218" s="3" t="inlineStr"/>
@@ -36503,7 +36499,7 @@
       </c>
       <c r="D219" s="3" t="inlineStr">
         <is>
-          <t>4c</t>
+          <t>5b</t>
         </is>
       </c>
       <c r="E219" s="3" t="n">
@@ -36527,7 +36523,7 @@
       <c r="I219" s="3" t="inlineStr"/>
       <c r="J219" s="3" t="inlineStr">
         <is>
-          <t>circuito (3 round)</t>
+          <t>jump set</t>
         </is>
       </c>
       <c r="K219" s="3" t="inlineStr">
@@ -37028,7 +37024,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>3x8+8</t>
+          <t>3x40"+40"</t>
         </is>
       </c>
       <c r="H229" s="3" t="inlineStr"/>
@@ -37069,32 +37065,28 @@
         </is>
       </c>
       <c r="E230" s="3" t="n">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>Push the wall squat</t>
+          <t>Dumbbell biker's squat</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>3x8</t>
-        </is>
-      </c>
-      <c r="H230" s="3" t="inlineStr">
-        <is>
-          <t>45"</t>
-        </is>
-      </c>
+          <t>3x12</t>
+        </is>
+      </c>
+      <c r="H230" s="3" t="inlineStr"/>
       <c r="I230" s="3" t="inlineStr"/>
       <c r="J230" s="3" t="inlineStr">
         <is>
-          <t>jump set</t>
+          <t>jump set | usare un manubrio di peso adeguato al riscaldamento</t>
         </is>
       </c>
       <c r="K230" s="3" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/3a_ww0jGYsM</t>
+          <t>https://youtu.be/jqhow36DTdg</t>
         </is>
       </c>
       <c r="L230" s="3" t="inlineStr"/>
@@ -37132,7 +37124,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>4x5+5</t>
+          <t>4x10</t>
         </is>
       </c>
       <c r="H231" s="3" t="inlineStr">
@@ -37143,7 +37135,7 @@
       <c r="I231" s="3" t="inlineStr"/>
       <c r="J231" s="3" t="inlineStr">
         <is>
-          <t>RPE 8.5</t>
+          <t>RPE 8.5 | fare un corretto avvicinamento</t>
         </is>
       </c>
       <c r="K231" s="3" t="inlineStr">
@@ -37290,14 +37282,14 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>3x6+6</t>
+          <t>3x5+5</t>
         </is>
       </c>
       <c r="H234" s="3" t="inlineStr"/>
       <c r="I234" s="3" t="inlineStr"/>
       <c r="J234" s="3" t="inlineStr">
         <is>
-          <t>circuito (3 round)</t>
+          <t>jump set</t>
         </is>
       </c>
       <c r="K234" s="3" t="inlineStr">
@@ -37331,26 +37323,34 @@
         </is>
       </c>
       <c r="E235" s="3" t="n">
-        <v>96</v>
+        <v>3</v>
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>coiled Ax Sit up</t>
+          <t>skierg pagaia alternato</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>3x8+8</t>
-        </is>
-      </c>
-      <c r="H235" s="3" t="inlineStr"/>
+          <t>3x30"+30"</t>
+        </is>
+      </c>
+      <c r="H235" s="3" t="inlineStr">
+        <is>
+          <t>60"</t>
+        </is>
+      </c>
       <c r="I235" s="3" t="inlineStr"/>
       <c r="J235" s="3" t="inlineStr">
         <is>
-          <t>circuito (3 round)</t>
-        </is>
-      </c>
-      <c r="K235" s="3" t="inlineStr"/>
+          <t>jump set</t>
+        </is>
+      </c>
+      <c r="K235" s="3" t="inlineStr">
+        <is>
+          <t>https://youtube.com/shorts/7n-hAJAXoYU</t>
+        </is>
+      </c>
       <c r="L235" s="3" t="inlineStr"/>
       <c r="M235" s="2" t="n"/>
       <c r="N235" s="2" t="n"/>
@@ -37373,38 +37373,30 @@
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
-          <t>4c</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E236" s="3" t="n">
-        <v>3</v>
+        <v>96</v>
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>skierg pagaia alternato</t>
+          <t>coiled Ax Sit up</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>3x30"+30"</t>
+          <t>3x8+8</t>
         </is>
       </c>
       <c r="H236" s="3" t="inlineStr">
         <is>
-          <t>60"</t>
+          <t>45"</t>
         </is>
       </c>
       <c r="I236" s="3" t="inlineStr"/>
-      <c r="J236" s="3" t="inlineStr">
-        <is>
-          <t>circuito (3 round)</t>
-        </is>
-      </c>
-      <c r="K236" s="3" t="inlineStr">
-        <is>
-          <t>https://youtube.com/shorts/7n-hAJAXoYU</t>
-        </is>
-      </c>
+      <c r="J236" s="3" t="inlineStr"/>
+      <c r="K236" s="3" t="inlineStr"/>
       <c r="L236" s="3" t="inlineStr"/>
       <c r="M236" s="2" t="n"/>
       <c r="N236" s="2" t="n"/>
@@ -37898,7 +37890,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>3x8+8</t>
+          <t>3x40"+40"</t>
         </is>
       </c>
       <c r="H246" s="3" t="inlineStr"/>
@@ -37939,32 +37931,28 @@
         </is>
       </c>
       <c r="E247" s="3" t="n">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>Push the wall squat</t>
+          <t>Dumbbell biker's squat</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>3x8</t>
-        </is>
-      </c>
-      <c r="H247" s="3" t="inlineStr">
-        <is>
-          <t>45"</t>
-        </is>
-      </c>
+          <t>3x12</t>
+        </is>
+      </c>
+      <c r="H247" s="3" t="inlineStr"/>
       <c r="I247" s="3" t="inlineStr"/>
       <c r="J247" s="3" t="inlineStr">
         <is>
-          <t>jump set</t>
+          <t>jump set | usare un manubrio di peso adeguato al riscaldamento</t>
         </is>
       </c>
       <c r="K247" s="3" t="inlineStr">
         <is>
-          <t>https://youtube.com/shorts/3a_ww0jGYsM</t>
+          <t>https://youtu.be/jqhow36DTdg</t>
         </is>
       </c>
       <c r="L247" s="3" t="inlineStr"/>
@@ -38002,7 +37990,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>4x5+5</t>
+          <t>4x10</t>
         </is>
       </c>
       <c r="H248" s="3" t="inlineStr">
@@ -38013,7 +38001,7 @@
       <c r="I248" s="3" t="inlineStr"/>
       <c r="J248" s="3" t="inlineStr">
         <is>
-          <t>RPE 8.5</t>
+          <t>RPE 8.5 | fare un corretto avvicinamento</t>
         </is>
       </c>
       <c r="K248" s="3" t="inlineStr">
@@ -38160,7 +38148,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>3x6+6</t>
+          <t>3x5+5</t>
         </is>
       </c>
       <c r="H251" s="3" t="inlineStr"/>

--- a/PRO database esercizi.xlsx
+++ b/PRO database esercizi.xlsx
@@ -7025,7 +7025,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>medball side kick thrue</t>
+          <t>medball side kick through</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>medball side kick thrue</t>
+          <t>medball side kick through</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -14328,7 +14328,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>medball side kick thrue</t>
+          <t>medball side kick through</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -17074,7 +17074,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>medball side kick thrue</t>
+          <t>medball side kick through</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -20008,7 +20008,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>medball side kick thrue</t>
+          <t>medball side kick through</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -22197,7 +22197,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>medball side kick thrue</t>
+          <t>medball side kick through</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -25115,7 +25115,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>medball side kick thrue</t>
+          <t>medball side kick through</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -36923,7 +36923,7 @@
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
-          <t>medball side kick thrue</t>
+          <t>medball side kick through</t>
         </is>
       </c>
       <c r="G227" s="4" t="inlineStr">
@@ -37789,7 +37789,7 @@
       </c>
       <c r="F244" s="4" t="inlineStr">
         <is>
-          <t>medball side kick thrue</t>
+          <t>medball side kick through</t>
         </is>
       </c>
       <c r="G244" s="4" t="inlineStr">
@@ -38655,7 +38655,7 @@
       </c>
       <c r="F261" s="4" t="inlineStr">
         <is>
-          <t>medball side kick thrue</t>
+          <t>medball side kick through</t>
         </is>
       </c>
       <c r="G261" s="4" t="inlineStr">

--- a/PRO database esercizi.xlsx
+++ b/PRO database esercizi.xlsx
@@ -36208,7 +36208,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>3x12</t>
+          <t>3 X 12+12</t>
         </is>
       </c>
       <c r="H213" s="3" t="inlineStr"/>
@@ -36416,7 +36416,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>studio progressivo 5-10 minuti</t>
+          <t>3 X 60"</t>
         </is>
       </c>
       <c r="H217" s="3" t="inlineStr"/>
@@ -36557,16 +36557,16 @@
         </is>
       </c>
       <c r="E220" s="4" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F220" s="4" t="inlineStr">
         <is>
-          <t>Cat-cow</t>
+          <t>Ground Stretch</t>
         </is>
       </c>
       <c r="G220" s="4" t="inlineStr">
         <is>
-          <t>3x12</t>
+          <t>3x10+10</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr"/>
@@ -36576,11 +36576,7 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K220" s="4" t="inlineStr">
-        <is>
-          <t>https://youtube.com/shorts/EBQD1Sha26k?si=VlMRufJ_KWHm-_V1</t>
-        </is>
-      </c>
+      <c r="K220" s="4" t="inlineStr"/>
       <c r="L220" s="4" t="inlineStr"/>
       <c r="M220" s="2" t="n"/>
       <c r="N220" s="2" t="n"/>
@@ -36675,7 +36671,7 @@
       </c>
       <c r="H222" s="4" t="inlineStr">
         <is>
-          <t>RBS 60"</t>
+          <t>Rec 60"</t>
         </is>
       </c>
       <c r="I222" s="4" t="inlineStr"/>
@@ -36724,12 +36720,12 @@
       </c>
       <c r="G223" s="4" t="inlineStr">
         <is>
-          <t>4x6+6</t>
+          <t>4x12</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr">
         <is>
-          <t>RBS 60"</t>
+          <t>Rec 60"</t>
         </is>
       </c>
       <c r="I223" s="4" t="inlineStr"/>
@@ -36778,7 +36774,7 @@
       </c>
       <c r="G224" s="4" t="inlineStr">
         <is>
-          <t>4x30"+30"</t>
+          <t>4x40"+40"</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -36928,7 +36924,7 @@
       </c>
       <c r="G227" s="4" t="inlineStr">
         <is>
-          <t>x 8</t>
+          <t>x 8+8</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr"/>
@@ -37074,14 +37070,14 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>3x12</t>
+          <t>3 X 12</t>
         </is>
       </c>
       <c r="H230" s="3" t="inlineStr"/>
       <c r="I230" s="3" t="inlineStr"/>
       <c r="J230" s="3" t="inlineStr">
         <is>
-          <t>jump set | usare un manubrio di peso adeguato al riscaldamento</t>
+          <t>jump set | usare un manubrio di peso adeguato al riscaldamento (alternato)</t>
         </is>
       </c>
       <c r="K230" s="3" t="inlineStr">
@@ -37282,7 +37278,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>3x5+5</t>
+          <t>3 X 50"</t>
         </is>
       </c>
       <c r="H234" s="3" t="inlineStr"/>
@@ -37423,16 +37419,16 @@
         </is>
       </c>
       <c r="E237" s="4" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F237" s="4" t="inlineStr">
         <is>
-          <t>Cat-cow</t>
+          <t>Ground Stretch</t>
         </is>
       </c>
       <c r="G237" s="4" t="inlineStr">
         <is>
-          <t>3x12</t>
+          <t>3x10+10</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr"/>
@@ -37442,11 +37438,7 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K237" s="4" t="inlineStr">
-        <is>
-          <t>https://youtube.com/shorts/EBQD1Sha26k?si=VlMRufJ_KWHm-_V1</t>
-        </is>
-      </c>
+      <c r="K237" s="4" t="inlineStr"/>
       <c r="L237" s="4" t="inlineStr"/>
       <c r="M237" s="2" t="n"/>
       <c r="N237" s="2" t="n"/>
@@ -37541,7 +37533,7 @@
       </c>
       <c r="H239" s="4" t="inlineStr">
         <is>
-          <t>RBS 60"</t>
+          <t>Rec 60"</t>
         </is>
       </c>
       <c r="I239" s="4" t="inlineStr"/>
@@ -37590,12 +37582,12 @@
       </c>
       <c r="G240" s="4" t="inlineStr">
         <is>
-          <t>4x6+6</t>
+          <t>4x12</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr">
         <is>
-          <t>RBS 60"</t>
+          <t>Rec 60"</t>
         </is>
       </c>
       <c r="I240" s="4" t="inlineStr"/>
@@ -37644,7 +37636,7 @@
       </c>
       <c r="G241" s="4" t="inlineStr">
         <is>
-          <t>4x30"+30"</t>
+          <t>4x40"+40"</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr"/>
@@ -37794,7 +37786,7 @@
       </c>
       <c r="G244" s="4" t="inlineStr">
         <is>
-          <t>x 8</t>
+          <t>x 8+8</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr"/>
@@ -37940,14 +37932,14 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>3x12</t>
+          <t>3 X 12</t>
         </is>
       </c>
       <c r="H247" s="3" t="inlineStr"/>
       <c r="I247" s="3" t="inlineStr"/>
       <c r="J247" s="3" t="inlineStr">
         <is>
-          <t>jump set | usare un manubrio di peso adeguato al riscaldamento</t>
+          <t>jump set | usare un manubrio di peso adeguato al riscaldamento (alternato)</t>
         </is>
       </c>
       <c r="K247" s="3" t="inlineStr">
@@ -38148,7 +38140,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>3x5+5</t>
+          <t>3 X 45"</t>
         </is>
       </c>
       <c r="H251" s="3" t="inlineStr"/>
@@ -38289,16 +38281,16 @@
         </is>
       </c>
       <c r="E254" s="4" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F254" s="4" t="inlineStr">
         <is>
-          <t>Cat-cow</t>
+          <t>Ground Stretch</t>
         </is>
       </c>
       <c r="G254" s="4" t="inlineStr">
         <is>
-          <t>3x12</t>
+          <t>3x10+10</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr"/>
@@ -38308,11 +38300,7 @@
           <t>jump set</t>
         </is>
       </c>
-      <c r="K254" s="4" t="inlineStr">
-        <is>
-          <t>https://youtube.com/shorts/EBQD1Sha26k?si=VlMRufJ_KWHm-_V1</t>
-        </is>
-      </c>
+      <c r="K254" s="4" t="inlineStr"/>
       <c r="L254" s="4" t="inlineStr"/>
       <c r="M254" s="2" t="n"/>
       <c r="N254" s="2" t="n"/>
@@ -38407,7 +38395,7 @@
       </c>
       <c r="H256" s="4" t="inlineStr">
         <is>
-          <t>RBS 60"</t>
+          <t>Rec 60"</t>
         </is>
       </c>
       <c r="I256" s="4" t="inlineStr"/>
@@ -38456,12 +38444,12 @@
       </c>
       <c r="G257" s="4" t="inlineStr">
         <is>
-          <t>4x6+6</t>
+          <t>4x12</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr">
         <is>
-          <t>RBS 60"</t>
+          <t>Rec 60"</t>
         </is>
       </c>
       <c r="I257" s="4" t="inlineStr"/>
@@ -38510,7 +38498,7 @@
       </c>
       <c r="G258" s="4" t="inlineStr">
         <is>
-          <t>4x30"+30"</t>
+          <t>4x40"+40"</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr"/>
@@ -38660,7 +38648,7 @@
       </c>
       <c r="G261" s="4" t="inlineStr">
         <is>
-          <t>x 8</t>
+          <t>x 8+8</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr"/>
